--- a/outputs/generated/nitro_bioisostere_campaign/mol2mol_similarity/curriculum_learning/mol2mol_similarity_cl_generated_optimal.xlsx
+++ b/outputs/generated/nitro_bioisostere_campaign/mol2mol_similarity/curriculum_learning/mol2mol_similarity_cl_generated_optimal.xlsx
@@ -1466,82 +1466,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1638300</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="38" name="Picture 37" descr="mol_37.png"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId37"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="19050" y="42043350"/>
-          <a:ext cx="1619250" cy="1143000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1638300</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="39" name="Picture 38" descr="mol_38.png"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId38"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="19050" y="43205400"/>
-          <a:ext cx="1619250" cy="1143000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1830,7 +1754,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BF39"/>
+  <dimension ref="A1:BF37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.7109375" customWidth="1"/>
@@ -2173,7 +2097,7 @@
     <row r="2" ht="92" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>O=C(c1cc([N+](=O)[O-])cc([N+](=O)[O-])c1)N1CC2(CCN(c3cncc(C#CC4CC4)c3)C2)C1</t>
+          <t>N#Cc1cc(C(=O)N2CC3(CCN(c4cncc(C#CC5CC5)c4)CC3)C2)cc([N+](=O)[O-])c1</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -2185,10 +2109,10 @@
         <v>1</v>
       </c>
       <c r="E2" s="3">
-        <v>0.7232142857142857</v>
+        <v>0.515625</v>
       </c>
       <c r="F2" s="3">
-        <v>9.18</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="G2" s="3">
         <v>5</v>
@@ -2199,55 +2123,55 @@
         </is>
       </c>
       <c r="I2" s="3">
-        <v>-0.1077625557954573</v>
+        <v>0.4117324146840131</v>
       </c>
       <c r="J2" s="3">
-        <v>0.7802565878921076</v>
+        <v>2.58066965215522</v>
       </c>
       <c r="K2" s="3">
-        <v>6.107762555795457</v>
+        <v>5.588267585315987</v>
       </c>
       <c r="L2" s="3">
-        <v>0.1260039099671743</v>
+        <v>0.906578148545373</v>
       </c>
       <c r="M2" s="3">
-        <v>0.1964032441848079</v>
+        <v>0.4475486543519156</v>
       </c>
       <c r="N2" s="3">
-        <v>1.483226727875655</v>
+        <v>12.55290187512538</v>
       </c>
       <c r="O2" s="3">
-        <v>0.6936795727134542</v>
+        <v>9.710139830384909</v>
       </c>
       <c r="P2" s="3">
-        <v>5.873996090032826</v>
+        <v>5.093421851454627</v>
       </c>
       <c r="Q2" s="3">
-        <v>0.1964032441848079</v>
+        <v>0.4475486543519156</v>
       </c>
       <c r="R2" s="3">
-        <v>0.5508756188032885</v>
+        <v>1.069997556760918</v>
       </c>
       <c r="S2" s="3">
-        <v>3.243054660202117</v>
+        <v>60.78179354644233</v>
       </c>
       <c r="T2" s="3">
-        <v>5.489045731430602</v>
+        <v>4.216226488924873</v>
       </c>
       <c r="U2" s="3">
-        <v>6.258946448635049</v>
+        <v>5.970617213984382</v>
       </c>
       <c r="V2" s="3">
-        <v>0.1964032441848079</v>
+        <v>0.4475486543519156</v>
       </c>
       <c r="W2" s="3">
-        <v>3.012000000000001</v>
+        <v>3.365580000000002</v>
       </c>
       <c r="X2" s="3">
-        <v>-5.073293876546985</v>
+        <v>-5.299567744929393</v>
       </c>
       <c r="Y2" s="3">
-        <v>8.447070589372393E-06</v>
+        <v>5.016863156547127E-06</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -2255,13 +2179,13 @@
         </is>
       </c>
       <c r="AA2" s="3">
-        <v>27.39243125915527</v>
+        <v>23.10389</v>
       </c>
       <c r="AB2" s="3">
-        <v>11.22435569763184</v>
+        <v>18.739658</v>
       </c>
       <c r="AC2" s="3">
-        <v>46.60781097412109</v>
+        <v>44.578938</v>
       </c>
       <c r="AD2" s="3">
         <v>0</v>
@@ -2273,79 +2197,79 @@
         <v>0</v>
       </c>
       <c r="AG2" s="3">
-        <v>0.8201842308044434</v>
+        <v>0.5334422599999999</v>
       </c>
       <c r="AH2" s="3">
-        <v>0.07281869649887085</v>
+        <v>0.17125244</v>
       </c>
       <c r="AI2" s="3">
-        <v>0.9605488777160645</v>
+        <v>0.91199607</v>
       </c>
       <c r="AJ2" s="3">
-        <v>0.1055731326341629</v>
+        <v>0.07755528</v>
       </c>
       <c r="AK2" s="3">
-        <v>0.6796711087226868</v>
+        <v>0.7042548</v>
       </c>
       <c r="AL2" s="3">
-        <v>0.04355539381504059</v>
+        <v>0.051000565</v>
       </c>
       <c r="AM2" s="3">
-        <v>0.5586081743240356</v>
+        <v>0.31617016</v>
       </c>
       <c r="AN2" s="3">
-        <v>0.5840002298355103</v>
+        <v>0.5149404400000001</v>
       </c>
       <c r="AO2" s="3">
-        <v>0.1242875009775162</v>
+        <v>0.06639437400000001</v>
       </c>
       <c r="AP2" s="3">
-        <v>0.9126684069633484</v>
+        <v>0.9267763</v>
       </c>
       <c r="AQ2" s="3">
-        <v>0.999782919883728</v>
+        <v>0.999557</v>
       </c>
       <c r="AR2" s="3">
-        <v>0.6728485822677612</v>
+        <v>0.7322213</v>
       </c>
       <c r="AS2" s="3">
-        <v>0.9221254587173462</v>
+        <v>0.9077922</v>
       </c>
       <c r="AT2" s="3">
-        <v>0.8560682535171509</v>
+        <v>0.8503741</v>
       </c>
       <c r="AU2" s="3">
-        <v>-4.64142894744873</v>
+        <v>-4.583415</v>
       </c>
       <c r="AV2" s="3">
-        <v>95.0521240234375</v>
+        <v>93.71975999999999</v>
       </c>
       <c r="AW2" s="3">
-        <v>5.566031455993652</v>
+        <v>5.3420143</v>
       </c>
       <c r="AX2" s="3">
-        <v>447.4510000000003</v>
+        <v>441.4910000000003</v>
       </c>
       <c r="AY2" s="3">
-        <v>3.012000000000001</v>
+        <v>3.365580000000002</v>
       </c>
       <c r="AZ2" s="3">
-        <v>0.4009478688079749</v>
+        <v>0.4110187535194017</v>
       </c>
       <c r="BA2" s="3">
         <v>4</v>
       </c>
       <c r="BB2" s="3">
-        <v>3.54376368153487</v>
+        <v>3.522395729220705</v>
       </c>
       <c r="BC2" s="3">
-        <v>0.7173595909405701</v>
+        <v>0.7197338078643661</v>
       </c>
       <c r="BD2" s="3">
         <v>3</v>
       </c>
       <c r="BE2" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF2" s="3">
         <v>1</v>
@@ -2354,22 +2278,22 @@
     <row r="3" ht="92" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>O=[N+]([O-])c1cc(CN2CC3(CCN(c4cncc(C#CC5CC5)c4)C3)C2)cc([N+](=O)[O-])c1</t>
+          <t>O=C(c1cc(F)cc([N+](=O)[O-])c1)N1CC2(CCN(c3cncc(C#CC4CC4)c3)C2)C1</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(Cc4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
+          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="D3" s="3">
         <v>1</v>
       </c>
       <c r="E3" s="3">
-        <v>0.7181818181818181</v>
+        <v>0.5932203389830508</v>
       </c>
       <c r="F3" s="3">
-        <v>9.74</v>
+        <v>6.7</v>
       </c>
       <c r="G3" s="3">
         <v>5</v>
@@ -2380,55 +2304,55 @@
         </is>
       </c>
       <c r="I3" s="3">
-        <v>0.1157269050045981</v>
+        <v>0.4207212335521988</v>
       </c>
       <c r="J3" s="3">
-        <v>1.305349794110473</v>
+        <v>2.634639711281976</v>
       </c>
       <c r="K3" s="3">
-        <v>5.884273094995402</v>
+        <v>5.579278766447802</v>
       </c>
       <c r="L3" s="3">
-        <v>0.198129864438462</v>
+        <v>0.8726582777150437</v>
       </c>
       <c r="M3" s="3">
-        <v>0.1521528385707531</v>
+        <v>0.4343912362366834</v>
       </c>
       <c r="N3" s="3">
-        <v>1.6884141116919</v>
+        <v>11.90470126439118</v>
       </c>
       <c r="O3" s="3">
-        <v>0.6838130867894727</v>
+        <v>11.13613992602521</v>
       </c>
       <c r="P3" s="3">
-        <v>5.801870135561538</v>
+        <v>5.127341722284957</v>
       </c>
       <c r="Q3" s="3">
-        <v>0.1521528385707531</v>
+        <v>0.4343912362366834</v>
       </c>
       <c r="R3" s="3">
-        <v>0.7941641911524214</v>
+        <v>1.050150285291231</v>
       </c>
       <c r="S3" s="3">
-        <v>3.13580774220638</v>
+        <v>52.9742846388216</v>
       </c>
       <c r="T3" s="3">
-        <v>5.503650571962861</v>
+        <v>4.275934899261057</v>
       </c>
       <c r="U3" s="3">
-        <v>6.100089699160214</v>
+        <v>5.978748545308855</v>
       </c>
       <c r="V3" s="3">
-        <v>0.1521528385707531</v>
+        <v>0.4343912362366834</v>
       </c>
       <c r="W3" s="3">
-        <v>3.371800000000002</v>
+        <v>3.242900000000002</v>
       </c>
       <c r="X3" s="3">
-        <v>-5.249058400108637</v>
+        <v>-5.079376714187515</v>
       </c>
       <c r="Y3" s="3">
-        <v>5.635618678787396E-06</v>
+        <v>8.329583493722114E-06</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -2436,13 +2360,13 @@
         </is>
       </c>
       <c r="AA3" s="3">
-        <v>24.31335067749023</v>
+        <v>33.43278</v>
       </c>
       <c r="AB3" s="3">
-        <v>11.85210418701172</v>
+        <v>32.67581</v>
       </c>
       <c r="AC3" s="3">
-        <v>57.372802734375</v>
+        <v>46.762466</v>
       </c>
       <c r="AD3" s="3">
         <v>0</v>
@@ -2454,79 +2378,79 @@
         <v>0</v>
       </c>
       <c r="AG3" s="3">
-        <v>0.7899720072746277</v>
+        <v>0.5444437</v>
       </c>
       <c r="AH3" s="3">
-        <v>0.3467926681041718</v>
+        <v>0.15939347</v>
       </c>
       <c r="AI3" s="3">
-        <v>0.8383261561393738</v>
+        <v>0.87861204</v>
       </c>
       <c r="AJ3" s="3">
-        <v>0.1977224349975586</v>
+        <v>0.07835977500000001</v>
       </c>
       <c r="AK3" s="3">
-        <v>0.9073472023010254</v>
+        <v>0.7173141</v>
       </c>
       <c r="AL3" s="3">
-        <v>0.1440775096416473</v>
+        <v>0.119241536</v>
       </c>
       <c r="AM3" s="3">
-        <v>0.6598395109176636</v>
+        <v>0.5052238999999999</v>
       </c>
       <c r="AN3" s="3">
-        <v>0.62095707654953</v>
+        <v>0.5596098</v>
       </c>
       <c r="AO3" s="3">
-        <v>0.4613286852836609</v>
+        <v>0.12150214</v>
       </c>
       <c r="AP3" s="3">
-        <v>0.9274924993515015</v>
+        <v>0.919333</v>
       </c>
       <c r="AQ3" s="3">
-        <v>0.9997690320014954</v>
+        <v>0.99988383</v>
       </c>
       <c r="AR3" s="3">
-        <v>0.68180912733078</v>
+        <v>0.73302203</v>
       </c>
       <c r="AS3" s="3">
-        <v>0.8865957260131836</v>
+        <v>0.9446642</v>
       </c>
       <c r="AT3" s="3">
-        <v>0.8694384694099426</v>
+        <v>0.8055361</v>
       </c>
       <c r="AU3" s="3">
-        <v>-4.790995597839355</v>
+        <v>-4.466086</v>
       </c>
       <c r="AV3" s="3">
-        <v>95.04631805419922</v>
+        <v>95.18449</v>
       </c>
       <c r="AW3" s="3">
-        <v>9.456762313842773</v>
+        <v>6.629981</v>
       </c>
       <c r="AX3" s="3">
-        <v>433.4680000000002</v>
+        <v>420.4440000000002</v>
       </c>
       <c r="AY3" s="3">
-        <v>3.371800000000002</v>
+        <v>3.242900000000002</v>
       </c>
       <c r="AZ3" s="3">
-        <v>0.4042662802246572</v>
+        <v>0.4327273065047823</v>
       </c>
       <c r="BA3" s="3">
         <v>4</v>
       </c>
       <c r="BB3" s="3">
-        <v>3.572658659469141</v>
+        <v>3.502066721471357</v>
       </c>
       <c r="BC3" s="3">
-        <v>0.7141490378367621</v>
+        <v>0.7219925865031824</v>
       </c>
       <c r="BD3" s="3">
         <v>3</v>
       </c>
       <c r="BE3" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF3" s="3">
         <v>1</v>
@@ -2535,7 +2459,7 @@
     <row r="4" ht="92" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>N#Cc1cc(C(=O)N2CC3(CCN(c4cncc(C#CC5CC5)c4)CC3)C2)cc([N+](=O)[O-])c1</t>
+          <t>O=C(Nc1cccc([N+](=O)[O-])c1)N1CC2(CCN(c3cncc(C#CC4CC4)c3)C2)C1</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -2547,10 +2471,10 @@
         <v>1</v>
       </c>
       <c r="E4" s="3">
-        <v>0.515625</v>
+        <v>0.4651162790697674</v>
       </c>
       <c r="F4" s="3">
-        <v>9.779999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="G4" s="3">
         <v>5</v>
@@ -2561,55 +2485,55 @@
         </is>
       </c>
       <c r="I4" s="3">
-        <v>0.4117324146840131</v>
+        <v>0.4207212335521988</v>
       </c>
       <c r="J4" s="3">
-        <v>2.58066965215522</v>
+        <v>2.634639711281976</v>
       </c>
       <c r="K4" s="3">
-        <v>5.588267585315987</v>
+        <v>5.579278766447802</v>
       </c>
       <c r="L4" s="3">
-        <v>0.906578148545373</v>
+        <v>1.302534866702132</v>
       </c>
       <c r="M4" s="3">
-        <v>0.4475486543519157</v>
+        <v>0.6252454707121891</v>
       </c>
       <c r="N4" s="3">
-        <v>12.55290187512538</v>
+        <v>53.12221394895862</v>
       </c>
       <c r="O4" s="3">
-        <v>9.710139830384909</v>
+        <v>74.13786945297711</v>
       </c>
       <c r="P4" s="3">
-        <v>5.093421851454627</v>
+        <v>4.697465133297868</v>
       </c>
       <c r="Q4" s="3">
-        <v>0.4475486543519157</v>
+        <v>0.6252454707121891</v>
       </c>
       <c r="R4" s="3">
-        <v>1.069997556760918</v>
+        <v>1.194135870086208</v>
       </c>
       <c r="S4" s="3">
-        <v>60.78179354644233</v>
+        <v>337.2997266996212</v>
       </c>
       <c r="T4" s="3">
-        <v>4.216226488924873</v>
+        <v>3.471984010701977</v>
       </c>
       <c r="U4" s="3">
-        <v>5.970617213984382</v>
+        <v>5.922946255893758</v>
       </c>
       <c r="V4" s="3">
-        <v>0.4475486543519157</v>
+        <v>0.6252454707121891</v>
       </c>
       <c r="W4" s="3">
-        <v>3.365580000000002</v>
+        <v>3.495500000000002</v>
       </c>
       <c r="X4" s="3">
-        <v>-5.299567744929393</v>
+        <v>-5.247047247346574</v>
       </c>
       <c r="Y4" s="3">
-        <v>5.016863156547127E-06</v>
+        <v>5.661776906301673E-06</v>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
@@ -2617,13 +2541,13 @@
         </is>
       </c>
       <c r="AA4" s="3">
-        <v>23.10388946533203</v>
+        <v>33.463398</v>
       </c>
       <c r="AB4" s="3">
-        <v>18.73965835571289</v>
+        <v>31.66836</v>
       </c>
       <c r="AC4" s="3">
-        <v>44.57893753051758</v>
+        <v>49.93486</v>
       </c>
       <c r="AD4" s="3">
         <v>0</v>
@@ -2635,73 +2559,73 @@
         <v>0</v>
       </c>
       <c r="AG4" s="3">
-        <v>0.5334422588348389</v>
+        <v>0.58538926</v>
       </c>
       <c r="AH4" s="3">
-        <v>0.1712524443864822</v>
+        <v>0.21523619</v>
       </c>
       <c r="AI4" s="3">
-        <v>0.911996066570282</v>
+        <v>0.90966624</v>
       </c>
       <c r="AJ4" s="3">
-        <v>0.07755527645349503</v>
+        <v>0.10510699</v>
       </c>
       <c r="AK4" s="3">
-        <v>0.7042548060417175</v>
+        <v>0.7597822</v>
       </c>
       <c r="AL4" s="3">
-        <v>0.05100056529045105</v>
+        <v>0.19702777</v>
       </c>
       <c r="AM4" s="3">
-        <v>0.3161701560020447</v>
+        <v>0.5736011</v>
       </c>
       <c r="AN4" s="3">
-        <v>0.5149404406547546</v>
+        <v>0.64569354</v>
       </c>
       <c r="AO4" s="3">
-        <v>0.0663943737745285</v>
+        <v>0.15836537</v>
       </c>
       <c r="AP4" s="3">
-        <v>0.9267762899398804</v>
+        <v>0.9019536</v>
       </c>
       <c r="AQ4" s="3">
-        <v>0.9995570182800293</v>
+        <v>0.99939156</v>
       </c>
       <c r="AR4" s="3">
-        <v>0.7322213053703308</v>
+        <v>0.77697235</v>
       </c>
       <c r="AS4" s="3">
-        <v>0.9077922105789185</v>
+        <v>0.9346789</v>
       </c>
       <c r="AT4" s="3">
-        <v>0.8503741025924683</v>
+        <v>0.76722854</v>
       </c>
       <c r="AU4" s="3">
-        <v>-4.583415031433105</v>
+        <v>-4.74271</v>
       </c>
       <c r="AV4" s="3">
-        <v>93.71975708007812</v>
+        <v>97.84730999999999</v>
       </c>
       <c r="AW4" s="3">
-        <v>5.342014312744141</v>
+        <v>5.5594726</v>
       </c>
       <c r="AX4" s="3">
-        <v>441.4910000000003</v>
+        <v>417.4690000000002</v>
       </c>
       <c r="AY4" s="3">
-        <v>3.365580000000002</v>
+        <v>3.495500000000002</v>
       </c>
       <c r="AZ4" s="3">
-        <v>0.4110187535194017</v>
+        <v>0.4688932813754169</v>
       </c>
       <c r="BA4" s="3">
         <v>4</v>
       </c>
       <c r="BB4" s="3">
-        <v>3.522395729220705</v>
+        <v>3.394533522773505</v>
       </c>
       <c r="BC4" s="3">
-        <v>0.7197338078643661</v>
+        <v>0.7339407196918327</v>
       </c>
       <c r="BD4" s="3">
         <v>3</v>
@@ -2716,7 +2640,7 @@
     <row r="5" ht="92" customHeight="1">
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>O=C(c1cc(F)cc([N+](=O)[O-])c1)N1CC2(CCN(c3cncc(C#CC4CC4)c3)C2)C1</t>
+          <t>Nc1cc(C(=O)N2CC3(CCN(c4cncc(C#CC5CC5)c4)C3)C2)cc([N+](=O)[O-])c1</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -2731,7 +2655,7 @@
         <v>0.5932203389830508</v>
       </c>
       <c r="F5" s="3">
-        <v>6.7</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="G5" s="3">
         <v>5</v>
@@ -2751,46 +2675,46 @@
         <v>5.579278766447802</v>
       </c>
       <c r="L5" s="3">
-        <v>0.8726582777150437</v>
+        <v>1.063257200855837</v>
       </c>
       <c r="M5" s="3">
-        <v>0.4343912362366834</v>
+        <v>0.7350957384445835</v>
       </c>
       <c r="N5" s="3">
-        <v>11.90470126439118</v>
+        <v>47.06496027030688</v>
       </c>
       <c r="O5" s="3">
-        <v>11.13613992602521</v>
+        <v>76.70270667776236</v>
       </c>
       <c r="P5" s="3">
-        <v>5.127341722284957</v>
+        <v>4.936742799144163</v>
       </c>
       <c r="Q5" s="3">
-        <v>0.4343912362366834</v>
+        <v>0.7350957384445835</v>
       </c>
       <c r="R5" s="3">
-        <v>1.050150285291231</v>
+        <v>0.419246604099984</v>
       </c>
       <c r="S5" s="3">
-        <v>52.9742846388216</v>
+        <v>319.1867452062806</v>
       </c>
       <c r="T5" s="3">
-        <v>4.275934899261057</v>
+        <v>3.495955151792779</v>
       </c>
       <c r="U5" s="3">
-        <v>5.978748545308855</v>
+        <v>6.377530446495546</v>
       </c>
       <c r="V5" s="3">
-        <v>0.4343912362366834</v>
+        <v>0.7350957384445835</v>
       </c>
       <c r="W5" s="3">
-        <v>3.242900000000002</v>
+        <v>2.686000000000001</v>
       </c>
       <c r="X5" s="3">
-        <v>-5.079376714187515</v>
+        <v>-4.646662182926614</v>
       </c>
       <c r="Y5" s="3">
-        <v>8.329583493722114E-06</v>
+        <v>2.255993360034212E-05</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
@@ -2798,94 +2722,94 @@
         </is>
       </c>
       <c r="AA5" s="3">
-        <v>33.43278121948242</v>
+        <v>15.104546</v>
       </c>
       <c r="AB5" s="3">
-        <v>32.67581176757812</v>
+        <v>15.9073925</v>
       </c>
       <c r="AC5" s="3">
-        <v>46.76246643066406</v>
+        <v>43.130665</v>
       </c>
       <c r="AD5" s="3">
         <v>0</v>
       </c>
       <c r="AE5" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF5" s="3">
         <v>0</v>
       </c>
       <c r="AG5" s="3">
-        <v>0.5444437265396118</v>
+        <v>0.6553272</v>
       </c>
       <c r="AH5" s="3">
-        <v>0.1593934744596481</v>
+        <v>0.20781446</v>
       </c>
       <c r="AI5" s="3">
-        <v>0.8786120414733887</v>
+        <v>0.9159778</v>
       </c>
       <c r="AJ5" s="3">
-        <v>0.07835977524518967</v>
+        <v>0.06549107</v>
       </c>
       <c r="AK5" s="3">
-        <v>0.7173141241073608</v>
+        <v>0.7860152</v>
       </c>
       <c r="AL5" s="3">
-        <v>0.1192415356636047</v>
+        <v>0.11830562</v>
       </c>
       <c r="AM5" s="3">
-        <v>0.5052238702774048</v>
+        <v>0.5261588</v>
       </c>
       <c r="AN5" s="3">
-        <v>0.5596097707748413</v>
+        <v>0.6298332</v>
       </c>
       <c r="AO5" s="3">
-        <v>0.1215021386742592</v>
+        <v>0.11490868</v>
       </c>
       <c r="AP5" s="3">
-        <v>0.9193329811096191</v>
+        <v>0.9475306</v>
       </c>
       <c r="AQ5" s="3">
-        <v>0.9998838305473328</v>
+        <v>0.99981564</v>
       </c>
       <c r="AR5" s="3">
-        <v>0.7330220341682434</v>
+        <v>0.7480128</v>
       </c>
       <c r="AS5" s="3">
-        <v>0.9446641802787781</v>
+        <v>0.93032295</v>
       </c>
       <c r="AT5" s="3">
-        <v>0.8055360913276672</v>
+        <v>0.7847223</v>
       </c>
       <c r="AU5" s="3">
-        <v>-4.466085910797119</v>
+        <v>-4.8313723</v>
       </c>
       <c r="AV5" s="3">
-        <v>95.18448638916016</v>
+        <v>92.10420000000001</v>
       </c>
       <c r="AW5" s="3">
-        <v>6.62998104095459</v>
+        <v>6.9422407</v>
       </c>
       <c r="AX5" s="3">
-        <v>420.4440000000002</v>
+        <v>417.4690000000002</v>
       </c>
       <c r="AY5" s="3">
-        <v>3.242900000000002</v>
+        <v>2.686000000000001</v>
       </c>
       <c r="AZ5" s="3">
-        <v>0.4327273065047823</v>
+        <v>0.3562486782899815</v>
       </c>
       <c r="BA5" s="3">
         <v>4</v>
       </c>
       <c r="BB5" s="3">
-        <v>3.502066721471357</v>
+        <v>3.557279453566848</v>
       </c>
       <c r="BC5" s="3">
-        <v>0.7219925865031824</v>
+        <v>0.7158578384925725</v>
       </c>
       <c r="BD5" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BE5" s="3">
         <v>0</v>
@@ -2897,22 +2821,22 @@
     <row r="6" ht="92" customHeight="1">
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>O=C(Nc1cccc([N+](=O)[O-])c1)N1CC2(CCN(c3cncc(C#CC4CC4)c3)C2)C1</t>
+          <t>N#Cc1cc(CN2CC3(CCN(c4cncc(C#CC5CC5)c4)C3)C2)cc([N+](=O)[O-])c1</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
+          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(Cc4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="D6" s="3">
         <v>1</v>
       </c>
       <c r="E6" s="3">
-        <v>0.4651162790697674</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="F6" s="3">
-        <v>8.43</v>
+        <v>7.85</v>
       </c>
       <c r="G6" s="3">
         <v>5</v>
@@ -2923,55 +2847,55 @@
         </is>
       </c>
       <c r="I6" s="3">
-        <v>0.4207212335521988</v>
+        <v>0.4207212335521989</v>
       </c>
       <c r="J6" s="3">
         <v>2.634639711281976</v>
       </c>
       <c r="K6" s="3">
-        <v>5.579278766447802</v>
+        <v>5.579278766447801</v>
       </c>
       <c r="L6" s="3">
-        <v>1.302534866702132</v>
+        <v>0.8927844962086805</v>
       </c>
       <c r="M6" s="3">
-        <v>0.6252454707121891</v>
+        <v>0.4957384099384128</v>
       </c>
       <c r="N6" s="3">
-        <v>53.12221394895862</v>
+        <v>13.2736928524462</v>
       </c>
       <c r="O6" s="3">
-        <v>74.13786945297711</v>
+        <v>11.40764986921003</v>
       </c>
       <c r="P6" s="3">
-        <v>4.697465133297868</v>
+        <v>5.10721550379132</v>
       </c>
       <c r="Q6" s="3">
-        <v>0.6252454707121891</v>
+        <v>0.4957384099384128</v>
       </c>
       <c r="R6" s="3">
-        <v>1.194135870086208</v>
+        <v>0.8339446227892051</v>
       </c>
       <c r="S6" s="3">
-        <v>337.2997266996212</v>
+        <v>73.18663503541805</v>
       </c>
       <c r="T6" s="3">
-        <v>3.471984010701977</v>
+        <v>4.13556822031203</v>
       </c>
       <c r="U6" s="3">
-        <v>5.922946255893758</v>
+        <v>6.078862787270609</v>
       </c>
       <c r="V6" s="3">
-        <v>0.6252454707121891</v>
+        <v>0.4957384099384128</v>
       </c>
       <c r="W6" s="3">
-        <v>3.495500000000002</v>
+        <v>3.335280000000002</v>
       </c>
       <c r="X6" s="3">
-        <v>-5.247047247346574</v>
+        <v>-5.098388528658376</v>
       </c>
       <c r="Y6" s="3">
-        <v>5.661776906301673E-06</v>
+        <v>7.97281104264379E-06</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
@@ -2979,13 +2903,13 @@
         </is>
       </c>
       <c r="AA6" s="3">
-        <v>33.46339797973633</v>
+        <v>23.97931</v>
       </c>
       <c r="AB6" s="3">
-        <v>31.66835975646973</v>
+        <v>23.716982</v>
       </c>
       <c r="AC6" s="3">
-        <v>49.93486022949219</v>
+        <v>49.541664</v>
       </c>
       <c r="AD6" s="3">
         <v>0</v>
@@ -2997,73 +2921,73 @@
         <v>0</v>
       </c>
       <c r="AG6" s="3">
-        <v>0.585389256477356</v>
+        <v>0.55360895</v>
       </c>
       <c r="AH6" s="3">
-        <v>0.2152361869812012</v>
+        <v>0.47432575</v>
       </c>
       <c r="AI6" s="3">
-        <v>0.9096662402153015</v>
+        <v>0.77981585</v>
       </c>
       <c r="AJ6" s="3">
-        <v>0.1051069870591164</v>
+        <v>0.12944366</v>
       </c>
       <c r="AK6" s="3">
-        <v>0.7597821950912476</v>
+        <v>0.8830212</v>
       </c>
       <c r="AL6" s="3">
-        <v>0.1970277726650238</v>
+        <v>0.13539223</v>
       </c>
       <c r="AM6" s="3">
-        <v>0.5736011266708374</v>
+        <v>0.4238152</v>
       </c>
       <c r="AN6" s="3">
-        <v>0.6456935405731201</v>
+        <v>0.5433621</v>
       </c>
       <c r="AO6" s="3">
-        <v>0.1583653688430786</v>
+        <v>0.3357931</v>
       </c>
       <c r="AP6" s="3">
-        <v>0.9019535779953003</v>
+        <v>0.92910635</v>
       </c>
       <c r="AQ6" s="3">
-        <v>0.9993915557861328</v>
+        <v>0.9991945</v>
       </c>
       <c r="AR6" s="3">
-        <v>0.7769723534584045</v>
+        <v>0.70547885</v>
       </c>
       <c r="AS6" s="3">
-        <v>0.9346789121627808</v>
+        <v>0.84448755</v>
       </c>
       <c r="AT6" s="3">
-        <v>0.7672285437583923</v>
+        <v>0.8291238</v>
       </c>
       <c r="AU6" s="3">
-        <v>-4.742710113525391</v>
+        <v>-4.7362967</v>
       </c>
       <c r="AV6" s="3">
-        <v>97.84731292724609</v>
+        <v>94.65166000000001</v>
       </c>
       <c r="AW6" s="3">
-        <v>5.559472560882568</v>
+        <v>7.238927</v>
       </c>
       <c r="AX6" s="3">
-        <v>417.4690000000002</v>
+        <v>413.4810000000002</v>
       </c>
       <c r="AY6" s="3">
-        <v>3.495500000000002</v>
+        <v>3.335280000000002</v>
       </c>
       <c r="AZ6" s="3">
-        <v>0.4688932813754169</v>
+        <v>0.4341256933267933</v>
       </c>
       <c r="BA6" s="3">
         <v>4</v>
       </c>
       <c r="BB6" s="3">
-        <v>3.394533522773505</v>
+        <v>3.622692963332944</v>
       </c>
       <c r="BC6" s="3">
-        <v>0.7339407196918327</v>
+        <v>0.7085896707407839</v>
       </c>
       <c r="BD6" s="3">
         <v>3</v>
@@ -3078,7 +3002,7 @@
     <row r="7" ht="92" customHeight="1">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Nc1cc(C(=O)N2CC3(CCN(c4cncc(C#CC5CC5)c4)C3)C2)cc([N+](=O)[O-])c1</t>
+          <t>CCCC#Cc1cncc(N2CCC3(CCN(C(=O)c4cc(N)cc([N+](=O)[O-])c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -3090,10 +3014,10 @@
         <v>1</v>
       </c>
       <c r="E7" s="3">
-        <v>0.5932203389830508</v>
+        <v>0.6551724137931034</v>
       </c>
       <c r="F7" s="3">
-        <v>9.050000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="G7" s="3">
         <v>5</v>
@@ -3104,55 +3028,55 @@
         </is>
       </c>
       <c r="I7" s="3">
-        <v>0.4207212335521988</v>
+        <v>0.4207212335521989</v>
       </c>
       <c r="J7" s="3">
         <v>2.634639711281976</v>
       </c>
       <c r="K7" s="3">
-        <v>5.579278766447802</v>
+        <v>5.579278766447801</v>
       </c>
       <c r="L7" s="3">
-        <v>1.063257200855837</v>
+        <v>1.132762662406212</v>
       </c>
       <c r="M7" s="3">
-        <v>0.7350957384445835</v>
+        <v>0.633349876618885</v>
       </c>
       <c r="N7" s="3">
-        <v>47.06496027030688</v>
+        <v>46.57444147848943</v>
       </c>
       <c r="O7" s="3">
-        <v>76.70270667776236</v>
+        <v>76.8017237462029</v>
       </c>
       <c r="P7" s="3">
-        <v>4.936742799144163</v>
+        <v>4.867237337593788</v>
       </c>
       <c r="Q7" s="3">
-        <v>0.7350957384445835</v>
+        <v>0.633349876618885</v>
       </c>
       <c r="R7" s="3">
-        <v>0.419246604099984</v>
+        <v>0.7787479281499307</v>
       </c>
       <c r="S7" s="3">
-        <v>319.1867452062806</v>
+        <v>236.6619401756978</v>
       </c>
       <c r="T7" s="3">
-        <v>3.495955151792779</v>
+        <v>3.625871579420773</v>
       </c>
       <c r="U7" s="3">
-        <v>6.377530446495546</v>
+        <v>6.108603095766802</v>
       </c>
       <c r="V7" s="3">
-        <v>0.7350957384445835</v>
+        <v>0.633349876618885</v>
       </c>
       <c r="W7" s="3">
-        <v>2.686000000000001</v>
+        <v>3.466200000000001</v>
       </c>
       <c r="X7" s="3">
-        <v>-4.646662182926614</v>
+        <v>-5.322814977705624</v>
       </c>
       <c r="Y7" s="3">
-        <v>2.255993360034212E-05</v>
+        <v>4.755377759510836E-06</v>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
@@ -3160,13 +3084,13 @@
         </is>
       </c>
       <c r="AA7" s="3">
-        <v>15.10454559326172</v>
+        <v>33.096546</v>
       </c>
       <c r="AB7" s="3">
-        <v>15.90739250183105</v>
+        <v>27.93637</v>
       </c>
       <c r="AC7" s="3">
-        <v>43.13066482543945</v>
+        <v>42.595848</v>
       </c>
       <c r="AD7" s="3">
         <v>0</v>
@@ -3178,73 +3102,73 @@
         <v>0</v>
       </c>
       <c r="AG7" s="3">
-        <v>0.6553272008895874</v>
+        <v>0.5997941</v>
       </c>
       <c r="AH7" s="3">
-        <v>0.2078144550323486</v>
+        <v>0.28147942</v>
       </c>
       <c r="AI7" s="3">
-        <v>0.9159777760505676</v>
+        <v>0.9014804</v>
       </c>
       <c r="AJ7" s="3">
-        <v>0.06549107283353806</v>
+        <v>0.06442964</v>
       </c>
       <c r="AK7" s="3">
-        <v>0.7860152125358582</v>
+        <v>0.8834075</v>
       </c>
       <c r="AL7" s="3">
-        <v>0.1183056235313416</v>
+        <v>0.2646338</v>
       </c>
       <c r="AM7" s="3">
-        <v>0.5261588096618652</v>
+        <v>0.66785395</v>
       </c>
       <c r="AN7" s="3">
-        <v>0.6298332214355469</v>
+        <v>0.7659068999999999</v>
       </c>
       <c r="AO7" s="3">
-        <v>0.1149086803197861</v>
+        <v>0.15353025</v>
       </c>
       <c r="AP7" s="3">
-        <v>0.9475306272506714</v>
+        <v>0.9828761</v>
       </c>
       <c r="AQ7" s="3">
-        <v>0.9998156428337097</v>
+        <v>0.9999558</v>
       </c>
       <c r="AR7" s="3">
-        <v>0.7480127811431885</v>
+        <v>0.76664793</v>
       </c>
       <c r="AS7" s="3">
-        <v>0.9303229451179504</v>
+        <v>0.95948</v>
       </c>
       <c r="AT7" s="3">
-        <v>0.7847223281860352</v>
+        <v>0.8880172</v>
       </c>
       <c r="AU7" s="3">
-        <v>-4.831372261047363</v>
+        <v>-4.8425827</v>
       </c>
       <c r="AV7" s="3">
-        <v>92.10420227050781</v>
+        <v>94.57998000000001</v>
       </c>
       <c r="AW7" s="3">
-        <v>6.942240715026855</v>
+        <v>8.963029000000001</v>
       </c>
       <c r="AX7" s="3">
-        <v>417.4690000000002</v>
+        <v>433.5120000000002</v>
       </c>
       <c r="AY7" s="3">
-        <v>2.686000000000001</v>
+        <v>3.466200000000001</v>
       </c>
       <c r="AZ7" s="3">
-        <v>0.3562486782899815</v>
+        <v>0.3425547491471555</v>
       </c>
       <c r="BA7" s="3">
         <v>4</v>
       </c>
       <c r="BB7" s="3">
-        <v>3.557279453566848</v>
+        <v>3.894879972146741</v>
       </c>
       <c r="BC7" s="3">
-        <v>0.7158578384925725</v>
+        <v>0.6783466697614732</v>
       </c>
       <c r="BD7" s="3">
         <v>4</v>
@@ -3259,22 +3183,22 @@
     <row r="8" ht="92" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>N#Cc1cc(CN2CC3(CCN(c4cncc(C#CC5CC5)c4)C3)C2)cc([N+](=O)[O-])c1</t>
+          <t>CNc1cc(C(=O)N2CC3(CCN(c4cncc(C#CCCCCO)c4)C3)C2)cc([N+](=O)[O-])c1</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(Cc4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
+          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="D8" s="3">
         <v>1</v>
       </c>
       <c r="E8" s="3">
-        <v>0.5714285714285714</v>
+        <v>0.7280701754385965</v>
       </c>
       <c r="F8" s="3">
-        <v>7.85</v>
+        <v>9.84</v>
       </c>
       <c r="G8" s="3">
         <v>5</v>
@@ -3294,46 +3218,46 @@
         <v>5.579278766447801</v>
       </c>
       <c r="L8" s="3">
-        <v>0.8927844962086805</v>
+        <v>1.21237860812196</v>
       </c>
       <c r="M8" s="3">
-        <v>0.4957384099384128</v>
+        <v>0.6616915480785701</v>
       </c>
       <c r="N8" s="3">
-        <v>13.2736928524462</v>
+        <v>50.52233649007206</v>
       </c>
       <c r="O8" s="3">
-        <v>11.40764986921003</v>
+        <v>75.29376864008364</v>
       </c>
       <c r="P8" s="3">
-        <v>5.10721550379132</v>
+        <v>4.78762139187804</v>
       </c>
       <c r="Q8" s="3">
-        <v>0.4957384099384128</v>
+        <v>0.6616915480785701</v>
       </c>
       <c r="R8" s="3">
-        <v>0.8339446227892051</v>
+        <v>0.823120037287316</v>
       </c>
       <c r="S8" s="3">
-        <v>73.18663503541805</v>
+        <v>323.0680738167517</v>
       </c>
       <c r="T8" s="3">
-        <v>4.13556822031203</v>
+        <v>3.490705957644042</v>
       </c>
       <c r="U8" s="3">
-        <v>6.078862787270609</v>
+        <v>6.084536826112037</v>
       </c>
       <c r="V8" s="3">
-        <v>0.4957384099384128</v>
+        <v>0.6616915480785701</v>
       </c>
       <c r="W8" s="3">
-        <v>3.335280000000002</v>
+        <v>2.898100000000001</v>
       </c>
       <c r="X8" s="3">
-        <v>-5.098388528658376</v>
+        <v>-5.080301334570364</v>
       </c>
       <c r="Y8" s="3">
-        <v>7.97281104264379E-06</v>
+        <v>8.311868532362252E-06</v>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
@@ -3341,94 +3265,94 @@
         </is>
       </c>
       <c r="AA8" s="3">
-        <v>23.97930908203125</v>
+        <v>26.097233</v>
       </c>
       <c r="AB8" s="3">
-        <v>23.71698188781738</v>
+        <v>27.409801</v>
       </c>
       <c r="AC8" s="3">
-        <v>49.54166412353516</v>
+        <v>41.994904</v>
       </c>
       <c r="AD8" s="3">
         <v>0</v>
       </c>
       <c r="AE8" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF8" s="3">
         <v>0</v>
       </c>
       <c r="AG8" s="3">
-        <v>0.5536089539527893</v>
+        <v>0.57045406</v>
       </c>
       <c r="AH8" s="3">
-        <v>0.4743257462978363</v>
+        <v>0.26881593</v>
       </c>
       <c r="AI8" s="3">
-        <v>0.7798158526420593</v>
+        <v>0.91209286</v>
       </c>
       <c r="AJ8" s="3">
-        <v>0.1294436603784561</v>
+        <v>0.08498739</v>
       </c>
       <c r="AK8" s="3">
-        <v>0.8830211758613586</v>
+        <v>0.85277015</v>
       </c>
       <c r="AL8" s="3">
-        <v>0.1353922337293625</v>
+        <v>0.06141494</v>
       </c>
       <c r="AM8" s="3">
-        <v>0.4238151907920837</v>
+        <v>0.5452275</v>
       </c>
       <c r="AN8" s="3">
-        <v>0.5433620810508728</v>
+        <v>0.6899304000000001</v>
       </c>
       <c r="AO8" s="3">
-        <v>0.3357931077480316</v>
+        <v>0.13291647</v>
       </c>
       <c r="AP8" s="3">
-        <v>0.9291063547134399</v>
+        <v>0.96948373</v>
       </c>
       <c r="AQ8" s="3">
-        <v>0.9991945028305054</v>
+        <v>0.99963206</v>
       </c>
       <c r="AR8" s="3">
-        <v>0.705478847026825</v>
+        <v>0.7670266</v>
       </c>
       <c r="AS8" s="3">
-        <v>0.8444875478744507</v>
+        <v>0.9187334</v>
       </c>
       <c r="AT8" s="3">
-        <v>0.8291237950325012</v>
+        <v>0.8780092</v>
       </c>
       <c r="AU8" s="3">
-        <v>-4.736296653747559</v>
+        <v>-5.1576014</v>
       </c>
       <c r="AV8" s="3">
-        <v>94.65165710449219</v>
+        <v>90.42838999999999</v>
       </c>
       <c r="AW8" s="3">
-        <v>7.238926887512207</v>
+        <v>12.174445</v>
       </c>
       <c r="AX8" s="3">
-        <v>413.4810000000002</v>
+        <v>463.5380000000004</v>
       </c>
       <c r="AY8" s="3">
-        <v>3.335280000000002</v>
+        <v>2.898100000000001</v>
       </c>
       <c r="AZ8" s="3">
-        <v>0.4341256933267933</v>
+        <v>0.2810214295341864</v>
       </c>
       <c r="BA8" s="3">
         <v>4</v>
       </c>
       <c r="BB8" s="3">
-        <v>3.622692963332944</v>
+        <v>3.529269259496221</v>
       </c>
       <c r="BC8" s="3">
-        <v>0.7085896707407839</v>
+        <v>0.7189700822781977</v>
       </c>
       <c r="BD8" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BE8" s="3">
         <v>0</v>
@@ -3440,22 +3364,22 @@
     <row r="9" ht="92" customHeight="1">
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>CCCC#Cc1cncc(N2CCC3(CCN(C(=O)c4cc(N)cc([N+](=O)[O-])c4)C3)C2)c1</t>
+          <t>CNC(=O)c1cc(CN2CC3(CCN(c4cncc(C#CC5CC5)c4)C3)C2)cc([N+](=O)[O-])c1</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
+          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(Cc4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="D9" s="3">
         <v>1</v>
       </c>
       <c r="E9" s="3">
-        <v>0.6551724137931034</v>
+        <v>0.5737704918032787</v>
       </c>
       <c r="F9" s="3">
-        <v>9.550000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="G9" s="3">
         <v>5</v>
@@ -3475,46 +3399,46 @@
         <v>5.579278766447801</v>
       </c>
       <c r="L9" s="3">
-        <v>1.132762662406212</v>
+        <v>1.024559043519542</v>
       </c>
       <c r="M9" s="3">
-        <v>0.633349876618885</v>
+        <v>0.7301358480980961</v>
       </c>
       <c r="N9" s="3">
-        <v>46.57444147848943</v>
+        <v>45.83703480046711</v>
       </c>
       <c r="O9" s="3">
-        <v>76.8017237462029</v>
+        <v>77.22251224145928</v>
       </c>
       <c r="P9" s="3">
-        <v>4.867237337593788</v>
+        <v>4.975440956480458</v>
       </c>
       <c r="Q9" s="3">
-        <v>0.633349876618885</v>
+        <v>0.7301358480980961</v>
       </c>
       <c r="R9" s="3">
-        <v>0.7787479281499307</v>
+        <v>0.3921866274337617</v>
       </c>
       <c r="S9" s="3">
-        <v>236.6619401756978</v>
+        <v>285.5126176655541</v>
       </c>
       <c r="T9" s="3">
-        <v>3.625871579420773</v>
+        <v>3.54437469420819</v>
       </c>
       <c r="U9" s="3">
-        <v>6.108603095766802</v>
+        <v>6.406507218752727</v>
       </c>
       <c r="V9" s="3">
-        <v>0.633349876618885</v>
+        <v>0.7301358480980961</v>
       </c>
       <c r="W9" s="3">
-        <v>3.466200000000002</v>
+        <v>2.823200000000001</v>
       </c>
       <c r="X9" s="3">
-        <v>-5.322814977705624</v>
+        <v>-4.91706271893505</v>
       </c>
       <c r="Y9" s="3">
-        <v>4.755377759510836E-06</v>
+        <v>1.210423316815337E-05</v>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
@@ -3522,94 +3446,94 @@
         </is>
       </c>
       <c r="AA9" s="3">
-        <v>33.0965461730957</v>
+        <v>14.707876</v>
       </c>
       <c r="AB9" s="3">
-        <v>27.93637084960938</v>
+        <v>8.443899</v>
       </c>
       <c r="AC9" s="3">
-        <v>42.59584808349609</v>
+        <v>51.974987</v>
       </c>
       <c r="AD9" s="3">
         <v>0</v>
       </c>
       <c r="AE9" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF9" s="3">
         <v>0</v>
       </c>
       <c r="AG9" s="3">
-        <v>0.5997940897941589</v>
+        <v>0.47795373</v>
       </c>
       <c r="AH9" s="3">
-        <v>0.2814794182777405</v>
+        <v>0.5108358</v>
       </c>
       <c r="AI9" s="3">
-        <v>0.9014803767204285</v>
+        <v>0.75849557</v>
       </c>
       <c r="AJ9" s="3">
-        <v>0.0644296407699585</v>
+        <v>0.15150039</v>
       </c>
       <c r="AK9" s="3">
-        <v>0.8834074735641479</v>
+        <v>0.90625966</v>
       </c>
       <c r="AL9" s="3">
-        <v>0.2646338045597076</v>
+        <v>0.10456894</v>
       </c>
       <c r="AM9" s="3">
-        <v>0.6678539514541626</v>
+        <v>0.39357784</v>
       </c>
       <c r="AN9" s="3">
-        <v>0.7659068703651428</v>
+        <v>0.5065527</v>
       </c>
       <c r="AO9" s="3">
-        <v>0.1535302549600601</v>
+        <v>0.37599203</v>
       </c>
       <c r="AP9" s="3">
-        <v>0.9828761219978333</v>
+        <v>0.9187897</v>
       </c>
       <c r="AQ9" s="3">
-        <v>0.9999557733535767</v>
+        <v>0.9990045</v>
       </c>
       <c r="AR9" s="3">
-        <v>0.7666479349136353</v>
+        <v>0.73420817</v>
       </c>
       <c r="AS9" s="3">
-        <v>0.9594799876213074</v>
+        <v>0.82743853</v>
       </c>
       <c r="AT9" s="3">
-        <v>0.8880171775817871</v>
+        <v>0.8205721</v>
       </c>
       <c r="AU9" s="3">
-        <v>-4.842582702636719</v>
+        <v>-5.1454906</v>
       </c>
       <c r="AV9" s="3">
-        <v>94.57997894287109</v>
+        <v>89.957855</v>
       </c>
       <c r="AW9" s="3">
-        <v>8.963028907775879</v>
+        <v>9.628456</v>
       </c>
       <c r="AX9" s="3">
-        <v>433.5120000000002</v>
+        <v>445.5230000000003</v>
       </c>
       <c r="AY9" s="3">
-        <v>3.466200000000002</v>
+        <v>2.823200000000001</v>
       </c>
       <c r="AZ9" s="3">
-        <v>0.3425547491471556</v>
+        <v>0.4323600902069877</v>
       </c>
       <c r="BA9" s="3">
         <v>4</v>
       </c>
       <c r="BB9" s="3">
-        <v>3.894879972146741</v>
+        <v>3.527289525746759</v>
       </c>
       <c r="BC9" s="3">
-        <v>0.6783466697614732</v>
+        <v>0.7191900526948045</v>
       </c>
       <c r="BD9" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BE9" s="3">
         <v>0</v>
@@ -3621,7 +3545,7 @@
     <row r="10" ht="92" customHeight="1">
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CNc1cc(C(=O)N2CC3(CCN(c4cncc(C#CCCCCO)c4)C3)C2)cc([N+](=O)[O-])c1</t>
+          <t>CCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc(N)cc([N+](=O)[O-])c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -3633,10 +3557,10 @@
         <v>1</v>
       </c>
       <c r="E10" s="3">
-        <v>0.7280701754385965</v>
+        <v>0.7685185185185185</v>
       </c>
       <c r="F10" s="3">
-        <v>9.84</v>
+        <v>9.26</v>
       </c>
       <c r="G10" s="3">
         <v>5</v>
@@ -3656,46 +3580,46 @@
         <v>5.579278766447801</v>
       </c>
       <c r="L10" s="3">
-        <v>1.21237860812196</v>
+        <v>1.041920275455228</v>
       </c>
       <c r="M10" s="3">
-        <v>0.6616915480785701</v>
+        <v>0.7651771522401469</v>
       </c>
       <c r="N10" s="3">
-        <v>50.52233649007206</v>
+        <v>47.29585719623411</v>
       </c>
       <c r="O10" s="3">
-        <v>75.29376864008364</v>
+        <v>76.68581794464112</v>
       </c>
       <c r="P10" s="3">
-        <v>4.78762139187804</v>
+        <v>4.958079724544771</v>
       </c>
       <c r="Q10" s="3">
-        <v>0.6616915480785701</v>
+        <v>0.7651771522401469</v>
       </c>
       <c r="R10" s="3">
-        <v>0.823120037287316</v>
+        <v>0.3484761476666538</v>
       </c>
       <c r="S10" s="3">
-        <v>323.0680738167517</v>
+        <v>348.0707217953223</v>
       </c>
       <c r="T10" s="3">
-        <v>3.490705957644042</v>
+        <v>3.458332506154083</v>
       </c>
       <c r="U10" s="3">
-        <v>6.084536826112037</v>
+        <v>6.457826942935459</v>
       </c>
       <c r="V10" s="3">
-        <v>0.6616915480785701</v>
+        <v>0.7651771522401469</v>
       </c>
       <c r="W10" s="3">
-        <v>2.898100000000001</v>
+        <v>3.466200000000001</v>
       </c>
       <c r="X10" s="3">
-        <v>-5.080301334570364</v>
+        <v>-5.319363432139666</v>
       </c>
       <c r="Y10" s="3">
-        <v>8.311868532362252E-06</v>
+        <v>4.793321595802333E-06</v>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
@@ -3703,94 +3627,94 @@
         </is>
       </c>
       <c r="AA10" s="3">
-        <v>26.09723281860352</v>
+        <v>38.25124</v>
       </c>
       <c r="AB10" s="3">
-        <v>27.4098014831543</v>
+        <v>34.25671</v>
       </c>
       <c r="AC10" s="3">
-        <v>41.99490356445312</v>
+        <v>42.674053</v>
       </c>
       <c r="AD10" s="3">
         <v>0</v>
       </c>
       <c r="AE10" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF10" s="3">
         <v>0</v>
       </c>
       <c r="AG10" s="3">
-        <v>0.5704540610313416</v>
+        <v>0.5682803400000001</v>
       </c>
       <c r="AH10" s="3">
-        <v>0.2688159346580505</v>
+        <v>0.23421836</v>
       </c>
       <c r="AI10" s="3">
-        <v>0.9120928645133972</v>
+        <v>0.9264919</v>
       </c>
       <c r="AJ10" s="3">
-        <v>0.08498738706111908</v>
+        <v>0.07704042</v>
       </c>
       <c r="AK10" s="3">
-        <v>0.8527701497077942</v>
+        <v>0.8519453</v>
       </c>
       <c r="AL10" s="3">
-        <v>0.0614149384200573</v>
+        <v>0.15603246</v>
       </c>
       <c r="AM10" s="3">
-        <v>0.5452275276184082</v>
+        <v>0.628715</v>
       </c>
       <c r="AN10" s="3">
-        <v>0.6899303793907166</v>
+        <v>0.75360346</v>
       </c>
       <c r="AO10" s="3">
-        <v>0.1329164654016495</v>
+        <v>0.11655255</v>
       </c>
       <c r="AP10" s="3">
-        <v>0.9694837331771851</v>
+        <v>0.9704455</v>
       </c>
       <c r="AQ10" s="3">
-        <v>0.9996320605278015</v>
+        <v>0.99988997</v>
       </c>
       <c r="AR10" s="3">
-        <v>0.7670266032218933</v>
+        <v>0.78353405</v>
       </c>
       <c r="AS10" s="3">
-        <v>0.9187334179878235</v>
+        <v>0.9519653300000001</v>
       </c>
       <c r="AT10" s="3">
-        <v>0.8780092000961304</v>
+        <v>0.8813807</v>
       </c>
       <c r="AU10" s="3">
-        <v>-5.157601356506348</v>
+        <v>-4.78674</v>
       </c>
       <c r="AV10" s="3">
-        <v>90.42839050292969</v>
+        <v>98.07588</v>
       </c>
       <c r="AW10" s="3">
-        <v>12.17444515228271</v>
+        <v>7.376075</v>
       </c>
       <c r="AX10" s="3">
-        <v>463.5380000000004</v>
+        <v>433.5120000000002</v>
       </c>
       <c r="AY10" s="3">
-        <v>2.898100000000001</v>
+        <v>3.466200000000001</v>
       </c>
       <c r="AZ10" s="3">
-        <v>0.2810214295341864</v>
+        <v>0.2544738696046525</v>
       </c>
       <c r="BA10" s="3">
         <v>4</v>
       </c>
       <c r="BB10" s="3">
-        <v>3.529269259496221</v>
+        <v>3.473177121007604</v>
       </c>
       <c r="BC10" s="3">
-        <v>0.7189700822781977</v>
+        <v>0.7252025421102662</v>
       </c>
       <c r="BD10" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BE10" s="3">
         <v>0</v>
@@ -3802,22 +3726,22 @@
     <row r="11" ht="92" customHeight="1">
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>CNC(=O)c1cc(CN2CC3(CCN(c4cncc(C#CC5CC5)c4)C3)C2)cc([N+](=O)[O-])c1</t>
+          <t>O=C(c1cc2c(cc1[N+](=O)[O-])OCO2)N1CC2(CCN(c3cncc(C#Cc4ccccc4)c3)C2)C1</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(Cc4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
+          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc5c(cc4[N+](=O)[O-])OCO5)C3)C2)c1</t>
         </is>
       </c>
       <c r="D11" s="3">
         <v>1</v>
       </c>
       <c r="E11" s="3">
-        <v>0.5737704918032787</v>
+        <v>0.6693548387096774</v>
       </c>
       <c r="F11" s="3">
-        <v>9.75</v>
+        <v>8.41</v>
       </c>
       <c r="G11" s="3">
         <v>5</v>
@@ -3828,55 +3752,55 @@
         </is>
       </c>
       <c r="I11" s="3">
-        <v>0.4207212335521989</v>
+        <v>0.4587392202455955</v>
       </c>
       <c r="J11" s="3">
-        <v>2.634639711281976</v>
+        <v>2.875671148922586</v>
       </c>
       <c r="K11" s="3">
-        <v>5.579278766447801</v>
+        <v>5.541260779754404</v>
       </c>
       <c r="L11" s="3">
-        <v>1.024559043519542</v>
+        <v>0.9656825076107368</v>
       </c>
       <c r="M11" s="3">
-        <v>0.7301358480980961</v>
+        <v>0.4144507565937986</v>
       </c>
       <c r="N11" s="3">
-        <v>45.83703480046711</v>
+        <v>13.85460863253116</v>
       </c>
       <c r="O11" s="3">
-        <v>77.22251224145928</v>
+        <v>10.82895052036266</v>
       </c>
       <c r="P11" s="3">
-        <v>4.975440956480458</v>
+        <v>5.034317492389263</v>
       </c>
       <c r="Q11" s="3">
-        <v>0.7301358480980961</v>
+        <v>0.4144507565937986</v>
       </c>
       <c r="R11" s="3">
-        <v>0.3921866274337618</v>
+        <v>1.423505090991994</v>
       </c>
       <c r="S11" s="3">
-        <v>285.5126176655541</v>
+        <v>59.97993496601116</v>
       </c>
       <c r="T11" s="3">
-        <v>3.54437469420819</v>
+        <v>4.221994009465418</v>
       </c>
       <c r="U11" s="3">
-        <v>6.406507218752727</v>
+        <v>5.846640975313108</v>
       </c>
       <c r="V11" s="3">
-        <v>0.7301358480980961</v>
+        <v>0.4144507565937986</v>
       </c>
       <c r="W11" s="3">
-        <v>2.823200000000001</v>
+        <v>3.470800000000002</v>
       </c>
       <c r="X11" s="3">
-        <v>-4.91706271893505</v>
+        <v>-5.706933805767084</v>
       </c>
       <c r="Y11" s="3">
-        <v>1.210423316815337E-05</v>
+        <v>1.963659550802752E-06</v>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
@@ -3884,13 +3808,13 @@
         </is>
       </c>
       <c r="AA11" s="3">
-        <v>14.70787620544434</v>
+        <v>61.197197</v>
       </c>
       <c r="AB11" s="3">
-        <v>8.443899154663086</v>
+        <v>57.89742</v>
       </c>
       <c r="AC11" s="3">
-        <v>51.9749870300293</v>
+        <v>52.037098</v>
       </c>
       <c r="AD11" s="3">
         <v>0</v>
@@ -3902,73 +3826,73 @@
         <v>0</v>
       </c>
       <c r="AG11" s="3">
-        <v>0.4779537320137024</v>
+        <v>0.49143618</v>
       </c>
       <c r="AH11" s="3">
-        <v>0.5108358263969421</v>
+        <v>0.24947155</v>
       </c>
       <c r="AI11" s="3">
-        <v>0.758495569229126</v>
+        <v>0.95616245</v>
       </c>
       <c r="AJ11" s="3">
-        <v>0.1515003889799118</v>
+        <v>0.10474871</v>
       </c>
       <c r="AK11" s="3">
-        <v>0.9062596559524536</v>
+        <v>0.8720348999999999</v>
       </c>
       <c r="AL11" s="3">
-        <v>0.1045689433813095</v>
+        <v>0.10152154</v>
       </c>
       <c r="AM11" s="3">
-        <v>0.3935778439044952</v>
+        <v>0.58805597</v>
       </c>
       <c r="AN11" s="3">
-        <v>0.5065526962280273</v>
+        <v>0.7895737</v>
       </c>
       <c r="AO11" s="3">
-        <v>0.3759920299053192</v>
+        <v>0.14743945</v>
       </c>
       <c r="AP11" s="3">
-        <v>0.9187896847724915</v>
+        <v>0.97765744</v>
       </c>
       <c r="AQ11" s="3">
-        <v>0.9990044832229614</v>
+        <v>0.9999398</v>
       </c>
       <c r="AR11" s="3">
-        <v>0.7342081665992737</v>
+        <v>0.7514311</v>
       </c>
       <c r="AS11" s="3">
-        <v>0.8274385333061218</v>
+        <v>0.9085928</v>
       </c>
       <c r="AT11" s="3">
-        <v>0.8205720782279968</v>
+        <v>0.9489415</v>
       </c>
       <c r="AU11" s="3">
-        <v>-5.145490646362305</v>
+        <v>-4.6429486</v>
       </c>
       <c r="AV11" s="3">
-        <v>89.95785522460938</v>
+        <v>102.82129</v>
       </c>
       <c r="AW11" s="3">
-        <v>9.628456115722656</v>
+        <v>1.4585049</v>
       </c>
       <c r="AX11" s="3">
-        <v>445.5230000000003</v>
+        <v>482.4960000000002</v>
       </c>
       <c r="AY11" s="3">
-        <v>2.823200000000001</v>
+        <v>3.470800000000002</v>
       </c>
       <c r="AZ11" s="3">
-        <v>0.4323600902069877</v>
+        <v>0.3202997029679085</v>
       </c>
       <c r="BA11" s="3">
         <v>4</v>
       </c>
       <c r="BB11" s="3">
-        <v>3.527289525746759</v>
+        <v>3.399065801684436</v>
       </c>
       <c r="BC11" s="3">
-        <v>0.7191900526948045</v>
+        <v>0.7334371331461738</v>
       </c>
       <c r="BD11" s="3">
         <v>3</v>
@@ -3983,7 +3907,7 @@
     <row r="12" ht="92" customHeight="1">
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc(N)cc([N+](=O)[O-])c4)C3)C2)c1</t>
+          <t>O=[N+]([O-])c1cccc(S(=O)(=O)N2CC3(CCN(c4cncc(C#Cc5ccccc5)c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -3995,10 +3919,10 @@
         <v>1</v>
       </c>
       <c r="E12" s="3">
-        <v>0.7685185185185185</v>
+        <v>0.4142857142857143</v>
       </c>
       <c r="F12" s="3">
-        <v>9.26</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="G12" s="3">
         <v>5</v>
@@ -4009,55 +3933,55 @@
         </is>
       </c>
       <c r="I12" s="3">
-        <v>0.4207212335521989</v>
+        <v>0.4587392202455955</v>
       </c>
       <c r="J12" s="3">
-        <v>2.634639711281976</v>
+        <v>2.875671148922586</v>
       </c>
       <c r="K12" s="3">
-        <v>5.579278766447801</v>
+        <v>5.541260779754404</v>
       </c>
       <c r="L12" s="3">
-        <v>1.041920275455228</v>
+        <v>1.244345676799701</v>
       </c>
       <c r="M12" s="3">
-        <v>0.7651771522401469</v>
+        <v>0.6628595708995422</v>
       </c>
       <c r="N12" s="3">
-        <v>47.29585719623411</v>
+        <v>52.02424052889556</v>
       </c>
       <c r="O12" s="3">
-        <v>76.68581794464112</v>
+        <v>74.70586769184766</v>
       </c>
       <c r="P12" s="3">
-        <v>4.958079724544771</v>
+        <v>4.755654323200298</v>
       </c>
       <c r="Q12" s="3">
-        <v>0.7651771522401469</v>
+        <v>0.6628595708995422</v>
       </c>
       <c r="R12" s="3">
-        <v>0.3484761476666539</v>
+        <v>0.8813347979994021</v>
       </c>
       <c r="S12" s="3">
-        <v>348.0707217953223</v>
+        <v>349.583105248683</v>
       </c>
       <c r="T12" s="3">
-        <v>3.458332506154083</v>
+        <v>3.456449564237196</v>
       </c>
       <c r="U12" s="3">
-        <v>6.457826942935459</v>
+        <v>6.054859082163402</v>
       </c>
       <c r="V12" s="3">
-        <v>0.7651771522401469</v>
+        <v>0.6628595708995422</v>
       </c>
       <c r="W12" s="3">
-        <v>3.466200000000002</v>
+        <v>3.290600000000002</v>
       </c>
       <c r="X12" s="3">
-        <v>-5.319363432139666</v>
+        <v>-5.529762492274818</v>
       </c>
       <c r="Y12" s="3">
-        <v>4.793321595802333E-06</v>
+        <v>2.952823630529195E-06</v>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
@@ -4065,94 +3989,94 @@
         </is>
       </c>
       <c r="AA12" s="3">
-        <v>38.25123977661133</v>
+        <v>61.55067</v>
       </c>
       <c r="AB12" s="3">
-        <v>34.25671005249023</v>
+        <v>58.72869</v>
       </c>
       <c r="AC12" s="3">
-        <v>42.67405319213867</v>
+        <v>58.906654</v>
       </c>
       <c r="AD12" s="3">
         <v>0</v>
       </c>
       <c r="AE12" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AF12" s="3">
         <v>0</v>
       </c>
       <c r="AG12" s="3">
-        <v>0.5682803392410278</v>
+        <v>0.73974264</v>
       </c>
       <c r="AH12" s="3">
-        <v>0.2342183589935303</v>
+        <v>0.19409972</v>
       </c>
       <c r="AI12" s="3">
-        <v>0.926491916179657</v>
+        <v>0.9423461</v>
       </c>
       <c r="AJ12" s="3">
-        <v>0.0770404189825058</v>
+        <v>0.19009365</v>
       </c>
       <c r="AK12" s="3">
-        <v>0.8519452810287476</v>
+        <v>0.8388074</v>
       </c>
       <c r="AL12" s="3">
-        <v>0.156032457947731</v>
+        <v>0.13074055</v>
       </c>
       <c r="AM12" s="3">
-        <v>0.6287149786949158</v>
+        <v>0.6069986000000001</v>
       </c>
       <c r="AN12" s="3">
-        <v>0.753603458404541</v>
+        <v>0.7154144</v>
       </c>
       <c r="AO12" s="3">
-        <v>0.116552546620369</v>
+        <v>0.15610202</v>
       </c>
       <c r="AP12" s="3">
-        <v>0.9704455137252808</v>
+        <v>0.935808</v>
       </c>
       <c r="AQ12" s="3">
-        <v>0.9998899698257446</v>
+        <v>0.99980676</v>
       </c>
       <c r="AR12" s="3">
-        <v>0.783534049987793</v>
+        <v>0.73569363</v>
       </c>
       <c r="AS12" s="3">
-        <v>0.95196533203125</v>
+        <v>0.8999283</v>
       </c>
       <c r="AT12" s="3">
-        <v>0.8813806772232056</v>
+        <v>0.9399322</v>
       </c>
       <c r="AU12" s="3">
-        <v>-4.786739826202393</v>
+        <v>-4.6946</v>
       </c>
       <c r="AV12" s="3">
-        <v>98.07588195800781</v>
+        <v>104.149704</v>
       </c>
       <c r="AW12" s="3">
-        <v>7.37607479095459</v>
+        <v>0.08050299</v>
       </c>
       <c r="AX12" s="3">
-        <v>433.5120000000002</v>
+        <v>474.5420000000002</v>
       </c>
       <c r="AY12" s="3">
-        <v>3.466200000000002</v>
+        <v>3.290600000000002</v>
       </c>
       <c r="AZ12" s="3">
-        <v>0.2544738696046526</v>
+        <v>0.3270867944484248</v>
       </c>
       <c r="BA12" s="3">
         <v>4</v>
       </c>
       <c r="BB12" s="3">
-        <v>3.473177121007604</v>
+        <v>3.250626907196461</v>
       </c>
       <c r="BC12" s="3">
-        <v>0.7252025421102662</v>
+        <v>0.7499303436448377</v>
       </c>
       <c r="BD12" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BE12" s="3">
         <v>0</v>
@@ -4164,22 +4088,22 @@
     <row r="13" ht="92" customHeight="1">
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>O=C(c1cc2c(cc1[N+](=O)[O-])OCO2)N1CC2(CCN(c3cncc(C#Cc4ccccc4)c3)C2)C1</t>
+          <t>CCCCCC#Cc1cncc(N2CCN(C(=O)c3cc(NCCO)cc([N+](=O)[O-])c3)CC2)c1</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc5c(cc4[N+](=O)[O-])OCO5)C3)C2)c1</t>
+          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="D13" s="3">
         <v>1</v>
       </c>
       <c r="E13" s="3">
-        <v>0.6693548387096774</v>
+        <v>0.5967741935483871</v>
       </c>
       <c r="F13" s="3">
-        <v>8.41</v>
+        <v>9.52</v>
       </c>
       <c r="G13" s="3">
         <v>5</v>
@@ -4190,55 +4114,55 @@
         </is>
       </c>
       <c r="I13" s="3">
-        <v>0.4587392202455955</v>
+        <v>0.501930417010947</v>
       </c>
       <c r="J13" s="3">
-        <v>2.875671148922586</v>
+        <v>3.176365110267067</v>
       </c>
       <c r="K13" s="3">
-        <v>5.541260779754404</v>
+        <v>5.498069582989053</v>
       </c>
       <c r="L13" s="3">
-        <v>0.9656825076107367</v>
+        <v>1.060308172541721</v>
       </c>
       <c r="M13" s="3">
-        <v>0.4144507565937986</v>
+        <v>0.4122089996960291</v>
       </c>
       <c r="N13" s="3">
-        <v>13.85460863253116</v>
+        <v>16.67186950472093</v>
       </c>
       <c r="O13" s="3">
-        <v>10.82895052036266</v>
+        <v>11.74070841002659</v>
       </c>
       <c r="P13" s="3">
-        <v>5.034317492389263</v>
+        <v>4.93969182745828</v>
       </c>
       <c r="Q13" s="3">
-        <v>0.4144507565937986</v>
+        <v>0.4122089996960291</v>
       </c>
       <c r="R13" s="3">
-        <v>1.423505090991994</v>
+        <v>1.788045364715204</v>
       </c>
       <c r="S13" s="3">
-        <v>59.97993496601116</v>
+        <v>73.83084040306868</v>
       </c>
       <c r="T13" s="3">
-        <v>4.221994009465418</v>
+        <v>4.131762188054061</v>
       </c>
       <c r="U13" s="3">
-        <v>5.846640975313108</v>
+        <v>5.747621466862496</v>
       </c>
       <c r="V13" s="3">
-        <v>0.4144507565937986</v>
+        <v>0.4122089996960291</v>
       </c>
       <c r="W13" s="3">
-        <v>3.470800000000002</v>
+        <v>3.288200000000002</v>
       </c>
       <c r="X13" s="3">
-        <v>-5.706933805767084</v>
+        <v>-5.376058843950747</v>
       </c>
       <c r="Y13" s="3">
-        <v>1.963659550802752E-06</v>
+        <v>4.206696266474002E-06</v>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
@@ -4246,94 +4170,94 @@
         </is>
       </c>
       <c r="AA13" s="3">
-        <v>61.19719696044922</v>
+        <v>56.144775</v>
       </c>
       <c r="AB13" s="3">
-        <v>57.89741897583008</v>
+        <v>50.989723</v>
       </c>
       <c r="AC13" s="3">
-        <v>52.0370979309082</v>
+        <v>53.791737</v>
       </c>
       <c r="AD13" s="3">
         <v>0</v>
       </c>
       <c r="AE13" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF13" s="3">
         <v>0</v>
       </c>
       <c r="AG13" s="3">
-        <v>0.4914361834526062</v>
+        <v>0.12132416</v>
       </c>
       <c r="AH13" s="3">
-        <v>0.2494715452194214</v>
+        <v>0.08011493</v>
       </c>
       <c r="AI13" s="3">
-        <v>0.9561624526977539</v>
+        <v>0.96437436</v>
       </c>
       <c r="AJ13" s="3">
-        <v>0.1047487109899521</v>
+        <v>0.16402815</v>
       </c>
       <c r="AK13" s="3">
-        <v>0.8720349073410034</v>
+        <v>0.73772377</v>
       </c>
       <c r="AL13" s="3">
-        <v>0.1015215367078781</v>
+        <v>0.12282292</v>
       </c>
       <c r="AM13" s="3">
-        <v>0.5880559682846069</v>
+        <v>0.9312116499999999</v>
       </c>
       <c r="AN13" s="3">
-        <v>0.7895737290382385</v>
+        <v>0.9595189</v>
       </c>
       <c r="AO13" s="3">
-        <v>0.1474394500255585</v>
+        <v>0.16751008</v>
       </c>
       <c r="AP13" s="3">
-        <v>0.9776574373245239</v>
+        <v>0.93706846</v>
       </c>
       <c r="AQ13" s="3">
-        <v>0.9999397993087769</v>
+        <v>0.99977875</v>
       </c>
       <c r="AR13" s="3">
-        <v>0.7514311075210571</v>
+        <v>0.66129273</v>
       </c>
       <c r="AS13" s="3">
-        <v>0.9085928201675415</v>
+        <v>0.89454573</v>
       </c>
       <c r="AT13" s="3">
-        <v>0.9489415287971497</v>
+        <v>0.92665577</v>
       </c>
       <c r="AU13" s="3">
-        <v>-4.642948627471924</v>
+        <v>-4.9017534</v>
       </c>
       <c r="AV13" s="3">
-        <v>102.8212890625</v>
+        <v>99.195885</v>
       </c>
       <c r="AW13" s="3">
-        <v>1.458504915237427</v>
+        <v>12.888103</v>
       </c>
       <c r="AX13" s="3">
-        <v>482.4960000000002</v>
+        <v>465.5540000000002</v>
       </c>
       <c r="AY13" s="3">
-        <v>3.470800000000002</v>
+        <v>3.288200000000002</v>
       </c>
       <c r="AZ13" s="3">
-        <v>0.3202997029679085</v>
+        <v>0.2529250093193272</v>
       </c>
       <c r="BA13" s="3">
         <v>4</v>
       </c>
       <c r="BB13" s="3">
-        <v>3.399065801684436</v>
+        <v>2.727069435008266</v>
       </c>
       <c r="BC13" s="3">
-        <v>0.7334371331461738</v>
+        <v>0.8081033961101927</v>
       </c>
       <c r="BD13" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BE13" s="3">
         <v>0</v>
@@ -4345,7 +4269,7 @@
     <row r="14" ht="92" customHeight="1">
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>O=[N+]([O-])c1cccc(S(=O)(=O)N2CC3(CCN(c4cncc(C#Cc5ccccc5)c4)C3)C2)c1</t>
+          <t>CCCCOCC#Cc1cncc(N2CCC3(CC2)CN(C(=O)c2cc([N+](=O)[O-])ccc2N)C3)c1</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -4357,10 +4281,10 @@
         <v>1</v>
       </c>
       <c r="E14" s="3">
-        <v>0.4142857142857143</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="F14" s="3">
-        <v>8.609999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="G14" s="3">
         <v>5</v>
@@ -4371,55 +4295,55 @@
         </is>
       </c>
       <c r="I14" s="3">
-        <v>0.4587392202455955</v>
+        <v>0.5327965792122313</v>
       </c>
       <c r="J14" s="3">
-        <v>2.875671148922586</v>
+        <v>3.410331364424373</v>
       </c>
       <c r="K14" s="3">
-        <v>5.541260779754404</v>
+        <v>5.467203420787769</v>
       </c>
       <c r="L14" s="3">
-        <v>1.244345676799701</v>
+        <v>1.081018066390045</v>
       </c>
       <c r="M14" s="3">
-        <v>0.6628595708995422</v>
+        <v>0.3364067816659609</v>
       </c>
       <c r="N14" s="3">
-        <v>52.02424052889556</v>
+        <v>15.67241622631086</v>
       </c>
       <c r="O14" s="3">
-        <v>74.70586769184766</v>
+        <v>10.36167406377702</v>
       </c>
       <c r="P14" s="3">
-        <v>4.755654323200298</v>
+        <v>4.918981933609954</v>
       </c>
       <c r="Q14" s="3">
-        <v>0.6628595708995422</v>
+        <v>0.3364067816659609</v>
       </c>
       <c r="R14" s="3">
-        <v>0.8813347979994021</v>
+        <v>2.640345588327656</v>
       </c>
       <c r="S14" s="3">
-        <v>349.583105248683</v>
+        <v>55.00160444825344</v>
       </c>
       <c r="T14" s="3">
-        <v>3.456449564237196</v>
+        <v>4.259624641544671</v>
       </c>
       <c r="U14" s="3">
-        <v>6.054859082163402</v>
+        <v>5.578339225675238</v>
       </c>
       <c r="V14" s="3">
-        <v>0.6628595708995422</v>
+        <v>0.3364067816659609</v>
       </c>
       <c r="W14" s="3">
-        <v>3.290600000000002</v>
+        <v>3.482800000000002</v>
       </c>
       <c r="X14" s="3">
-        <v>-5.529762492274818</v>
+        <v>-5.602432752989337</v>
       </c>
       <c r="Y14" s="3">
-        <v>2.952823630529195E-06</v>
+        <v>2.497855132006539E-06</v>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
@@ -4427,94 +4351,94 @@
         </is>
       </c>
       <c r="AA14" s="3">
-        <v>61.5506706237793</v>
+        <v>54.447063</v>
       </c>
       <c r="AB14" s="3">
-        <v>58.72869110107422</v>
+        <v>40.953976</v>
       </c>
       <c r="AC14" s="3">
-        <v>58.90665435791016</v>
+        <v>48.735115</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
       <c r="AE14" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
       <c r="AG14" s="3">
-        <v>0.739742636680603</v>
+        <v>0.47599682</v>
       </c>
       <c r="AH14" s="3">
-        <v>0.1940997242927551</v>
+        <v>0.20968123</v>
       </c>
       <c r="AI14" s="3">
-        <v>0.9423460960388184</v>
+        <v>0.9220096</v>
       </c>
       <c r="AJ14" s="3">
-        <v>0.1900936514139175</v>
+        <v>0.057270795</v>
       </c>
       <c r="AK14" s="3">
-        <v>0.8388074040412903</v>
+        <v>0.8728773</v>
       </c>
       <c r="AL14" s="3">
-        <v>0.1307405531406403</v>
+        <v>0.07988199</v>
       </c>
       <c r="AM14" s="3">
-        <v>0.60699862241745</v>
+        <v>0.62366295</v>
       </c>
       <c r="AN14" s="3">
-        <v>0.7154144048690796</v>
+        <v>0.768388</v>
       </c>
       <c r="AO14" s="3">
-        <v>0.1561020165681839</v>
+        <v>0.07673104</v>
       </c>
       <c r="AP14" s="3">
-        <v>0.935808002948761</v>
+        <v>0.9812447</v>
       </c>
       <c r="AQ14" s="3">
-        <v>0.9998067617416382</v>
+        <v>0.99994594</v>
       </c>
       <c r="AR14" s="3">
-        <v>0.735693633556366</v>
+        <v>0.75229734</v>
       </c>
       <c r="AS14" s="3">
-        <v>0.8999282717704773</v>
+        <v>0.9581814</v>
       </c>
       <c r="AT14" s="3">
-        <v>0.9399322271347046</v>
+        <v>0.9433463</v>
       </c>
       <c r="AU14" s="3">
-        <v>-4.694600105285645</v>
+        <v>-4.76779</v>
       </c>
       <c r="AV14" s="3">
-        <v>104.1497039794922</v>
+        <v>96.09022</v>
       </c>
       <c r="AW14" s="3">
-        <v>0.08050298690795898</v>
+        <v>10.923845</v>
       </c>
       <c r="AX14" s="3">
-        <v>474.5420000000002</v>
+        <v>477.5650000000003</v>
       </c>
       <c r="AY14" s="3">
-        <v>3.290600000000002</v>
+        <v>3.482800000000002</v>
       </c>
       <c r="AZ14" s="3">
-        <v>0.3270867944484248</v>
+        <v>0.2134025706227068</v>
       </c>
       <c r="BA14" s="3">
         <v>4</v>
       </c>
       <c r="BB14" s="3">
-        <v>3.250626907196461</v>
+        <v>3.426852098743651</v>
       </c>
       <c r="BC14" s="3">
-        <v>0.7499303436448377</v>
+        <v>0.7303497668062611</v>
       </c>
       <c r="BD14" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BE14" s="3">
         <v>0</v>
@@ -4526,22 +4450,22 @@
     <row r="15" ht="92" customHeight="1">
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CCCCCC#Cc1cncc(N2CCN(C(=O)c3cc(NCCO)cc([N+](=O)[O-])c3)CC2)c1</t>
+          <t>CC(C)OCC#Cc1cncc(N2CCC3(CC2)CN(Cc2cc(N)cc([N+](=O)[O-])c2)C3)c1</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
+          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(Cc4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="D15" s="3">
         <v>1</v>
       </c>
       <c r="E15" s="3">
-        <v>0.5967741935483871</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="F15" s="3">
-        <v>9.52</v>
+        <v>9.67</v>
       </c>
       <c r="G15" s="3">
         <v>5</v>
@@ -4552,55 +4476,55 @@
         </is>
       </c>
       <c r="I15" s="3">
-        <v>0.501930417010947</v>
+        <v>0.5327965792122313</v>
       </c>
       <c r="J15" s="3">
-        <v>3.176365110267067</v>
+        <v>3.410331364424373</v>
       </c>
       <c r="K15" s="3">
-        <v>5.498069582989053</v>
+        <v>5.467203420787769</v>
       </c>
       <c r="L15" s="3">
-        <v>1.060308172541721</v>
+        <v>0.971176449813876</v>
       </c>
       <c r="M15" s="3">
-        <v>0.4122089996960291</v>
+        <v>0.5103518930759067</v>
       </c>
       <c r="N15" s="3">
-        <v>16.67186950472093</v>
+        <v>15.76346938827487</v>
       </c>
       <c r="O15" s="3">
-        <v>11.74070841002659</v>
+        <v>12.16624335439029</v>
       </c>
       <c r="P15" s="3">
-        <v>4.93969182745828</v>
+        <v>5.028823550186124</v>
       </c>
       <c r="Q15" s="3">
-        <v>0.4122089996960291</v>
+        <v>0.5103518930759067</v>
       </c>
       <c r="R15" s="3">
-        <v>1.788045364715204</v>
+        <v>0.935161759447538</v>
       </c>
       <c r="S15" s="3">
-        <v>73.83084040306868</v>
+        <v>93.64102529752516</v>
       </c>
       <c r="T15" s="3">
-        <v>4.131762188054061</v>
+        <v>4.028533839757347</v>
       </c>
       <c r="U15" s="3">
-        <v>5.747621466862496</v>
+        <v>6.029113260614901</v>
       </c>
       <c r="V15" s="3">
-        <v>0.4122089996960291</v>
+        <v>0.5103518930759067</v>
       </c>
       <c r="W15" s="3">
-        <v>3.288200000000002</v>
+        <v>3.450900000000002</v>
       </c>
       <c r="X15" s="3">
-        <v>-5.376058843950747</v>
+        <v>-5.405827096661705</v>
       </c>
       <c r="Y15" s="3">
-        <v>4.206696266474002E-06</v>
+        <v>3.928012881486768E-06</v>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
@@ -4608,13 +4532,13 @@
         </is>
       </c>
       <c r="AA15" s="3">
-        <v>56.144775390625</v>
+        <v>27.34353</v>
       </c>
       <c r="AB15" s="3">
-        <v>50.98972320556641</v>
+        <v>20.438168</v>
       </c>
       <c r="AC15" s="3">
-        <v>53.7917366027832</v>
+        <v>55.069954</v>
       </c>
       <c r="AD15" s="3">
         <v>0</v>
@@ -4626,73 +4550,73 @@
         <v>0</v>
       </c>
       <c r="AG15" s="3">
-        <v>0.1213241592049599</v>
+        <v>0.53152555</v>
       </c>
       <c r="AH15" s="3">
-        <v>0.0801149308681488</v>
+        <v>0.6730733</v>
       </c>
       <c r="AI15" s="3">
-        <v>0.9643743634223938</v>
+        <v>0.77885133</v>
       </c>
       <c r="AJ15" s="3">
-        <v>0.1640281528234482</v>
+        <v>0.110830165</v>
       </c>
       <c r="AK15" s="3">
-        <v>0.7377237677574158</v>
+        <v>0.9728624</v>
       </c>
       <c r="AL15" s="3">
-        <v>0.1228229179978371</v>
+        <v>0.2244101</v>
       </c>
       <c r="AM15" s="3">
-        <v>0.9312116503715515</v>
+        <v>0.5238451</v>
       </c>
       <c r="AN15" s="3">
-        <v>0.9595189094543457</v>
+        <v>0.58437216</v>
       </c>
       <c r="AO15" s="3">
-        <v>0.1675100773572922</v>
+        <v>0.45984015</v>
       </c>
       <c r="AP15" s="3">
-        <v>0.9370684623718262</v>
+        <v>0.9567854</v>
       </c>
       <c r="AQ15" s="3">
-        <v>0.9997787475585938</v>
+        <v>0.9995303</v>
       </c>
       <c r="AR15" s="3">
-        <v>0.6612927317619324</v>
+        <v>0.786309</v>
       </c>
       <c r="AS15" s="3">
-        <v>0.8945457339286804</v>
+        <v>0.9379716</v>
       </c>
       <c r="AT15" s="3">
-        <v>0.9266557693481445</v>
+        <v>0.91014606</v>
       </c>
       <c r="AU15" s="3">
-        <v>-4.901753425598145</v>
+        <v>-5.119879</v>
       </c>
       <c r="AV15" s="3">
-        <v>99.19588470458984</v>
+        <v>86.744156</v>
       </c>
       <c r="AW15" s="3">
-        <v>12.88810253143311</v>
+        <v>16.604115</v>
       </c>
       <c r="AX15" s="3">
-        <v>465.5540000000002</v>
+        <v>449.5550000000002</v>
       </c>
       <c r="AY15" s="3">
-        <v>3.288200000000002</v>
+        <v>3.450900000000002</v>
       </c>
       <c r="AZ15" s="3">
-        <v>0.2529250093193272</v>
+        <v>0.3121353019163128</v>
       </c>
       <c r="BA15" s="3">
         <v>4</v>
       </c>
       <c r="BB15" s="3">
-        <v>2.727069435008266</v>
+        <v>3.549485059245518</v>
       </c>
       <c r="BC15" s="3">
-        <v>0.8081033961101927</v>
+        <v>0.7167238823060536</v>
       </c>
       <c r="BD15" s="3">
         <v>4</v>
@@ -4707,22 +4631,22 @@
     <row r="16" ht="92" customHeight="1">
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>CCCCOCC#Cc1cncc(N2CCC3(CC2)CN(C(=O)c2cc([N+](=O)[O-])ccc2N)C3)c1</t>
+          <t>C=CCOCC#Cc1cncc(N2CCC3(CC2)CN(Cc2cc(N)cc([N+](=O)[O-])c2)C3)c1</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
+          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(Cc4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="D16" s="3">
         <v>1</v>
       </c>
       <c r="E16" s="3">
-        <v>0.5384615384615384</v>
+        <v>0.544</v>
       </c>
       <c r="F16" s="3">
-        <v>9.42</v>
+        <v>8.67</v>
       </c>
       <c r="G16" s="3">
         <v>5</v>
@@ -4742,46 +4666,46 @@
         <v>5.467203420787769</v>
       </c>
       <c r="L16" s="3">
-        <v>1.081018066390045</v>
+        <v>0.9857909523812384</v>
       </c>
       <c r="M16" s="3">
-        <v>0.3364067816659609</v>
+        <v>0.5237856847877402</v>
       </c>
       <c r="N16" s="3">
-        <v>15.67241622631085</v>
+        <v>16.71682039167111</v>
       </c>
       <c r="O16" s="3">
-        <v>10.36167406377703</v>
+        <v>13.07123879593058</v>
       </c>
       <c r="P16" s="3">
-        <v>4.918981933609954</v>
+        <v>5.014209047618762</v>
       </c>
       <c r="Q16" s="3">
-        <v>0.3364067816659609</v>
+        <v>0.5237856847877402</v>
       </c>
       <c r="R16" s="3">
-        <v>2.640345588327656</v>
+        <v>0.9102716356660688</v>
       </c>
       <c r="S16" s="3">
-        <v>55.00160444825344</v>
+        <v>102.8989384854388</v>
       </c>
       <c r="T16" s="3">
-        <v>4.259624641544671</v>
+        <v>3.987589105434791</v>
       </c>
       <c r="U16" s="3">
-        <v>5.578339225675238</v>
+        <v>6.040828989802733</v>
       </c>
       <c r="V16" s="3">
-        <v>0.3364067816659609</v>
+        <v>0.5237856847877402</v>
       </c>
       <c r="W16" s="3">
-        <v>3.482800000000002</v>
+        <v>3.228500000000001</v>
       </c>
       <c r="X16" s="3">
-        <v>-5.602432752989337</v>
+        <v>-5.224093672391016</v>
       </c>
       <c r="Y16" s="3">
-        <v>2.497855132006539E-06</v>
+        <v>5.969065267346864E-06</v>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
@@ -4789,94 +4713,94 @@
         </is>
       </c>
       <c r="AA16" s="3">
-        <v>54.44706344604492</v>
+        <v>24.91099</v>
       </c>
       <c r="AB16" s="3">
-        <v>40.95397567749023</v>
+        <v>16.697508</v>
       </c>
       <c r="AC16" s="3">
-        <v>48.73511505126953</v>
+        <v>46.32699</v>
       </c>
       <c r="AD16" s="3">
         <v>0</v>
       </c>
       <c r="AE16" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF16" s="3">
         <v>0</v>
       </c>
       <c r="AG16" s="3">
-        <v>0.4759968221187592</v>
+        <v>0.44790655</v>
       </c>
       <c r="AH16" s="3">
-        <v>0.2096812278032303</v>
+        <v>0.66046464</v>
       </c>
       <c r="AI16" s="3">
-        <v>0.9220095872879028</v>
+        <v>0.7542521</v>
       </c>
       <c r="AJ16" s="3">
-        <v>0.05727079510688782</v>
+        <v>0.11469944</v>
       </c>
       <c r="AK16" s="3">
-        <v>0.872877299785614</v>
+        <v>0.97435457</v>
       </c>
       <c r="AL16" s="3">
-        <v>0.07988198846578598</v>
+        <v>0.26217464</v>
       </c>
       <c r="AM16" s="3">
-        <v>0.6236629486083984</v>
+        <v>0.59623706</v>
       </c>
       <c r="AN16" s="3">
-        <v>0.7683879733085632</v>
+        <v>0.66353244</v>
       </c>
       <c r="AO16" s="3">
-        <v>0.07673104107379913</v>
+        <v>0.5958261500000001</v>
       </c>
       <c r="AP16" s="3">
-        <v>0.981244683265686</v>
+        <v>0.97739315</v>
       </c>
       <c r="AQ16" s="3">
-        <v>0.9999459385871887</v>
+        <v>0.9997422</v>
       </c>
       <c r="AR16" s="3">
-        <v>0.7522973418235779</v>
+        <v>0.71399105</v>
       </c>
       <c r="AS16" s="3">
-        <v>0.9581813812255859</v>
+        <v>0.9213010700000001</v>
       </c>
       <c r="AT16" s="3">
-        <v>0.9433463215827942</v>
+        <v>0.9123934</v>
       </c>
       <c r="AU16" s="3">
-        <v>-4.767789840698242</v>
+        <v>-5.1444654</v>
       </c>
       <c r="AV16" s="3">
-        <v>96.09021759033203</v>
+        <v>88.25448</v>
       </c>
       <c r="AW16" s="3">
-        <v>10.9238452911377</v>
+        <v>13.374876</v>
       </c>
       <c r="AX16" s="3">
-        <v>477.5650000000003</v>
+        <v>447.5390000000002</v>
       </c>
       <c r="AY16" s="3">
-        <v>3.482800000000002</v>
+        <v>3.228500000000001</v>
       </c>
       <c r="AZ16" s="3">
-        <v>0.2134025706227068</v>
+        <v>0.1737647718090827</v>
       </c>
       <c r="BA16" s="3">
         <v>4</v>
       </c>
       <c r="BB16" s="3">
-        <v>3.426852098743651</v>
+        <v>3.610344116317478</v>
       </c>
       <c r="BC16" s="3">
-        <v>0.7303497668062611</v>
+        <v>0.7099617648536136</v>
       </c>
       <c r="BD16" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BE16" s="3">
         <v>0</v>
@@ -4888,22 +4812,22 @@
     <row r="17" ht="92" customHeight="1">
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>CC(C)OCC#Cc1cncc(N2CCC3(CC2)CN(Cc2cc(N)cc([N+](=O)[O-])c2)C3)c1</t>
+          <t>CCCCOCC#Cc1cncc(N2CCC3(CC2)CN(C(=O)c2cc(N)cc([N+](=O)[O-])c2)C3)c1</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(Cc4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
+          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="D17" s="3">
         <v>1</v>
       </c>
       <c r="E17" s="3">
-        <v>0.5483870967741935</v>
+        <v>0.6260162601626016</v>
       </c>
       <c r="F17" s="3">
-        <v>9.67</v>
+        <v>9.01</v>
       </c>
       <c r="G17" s="3">
         <v>5</v>
@@ -4923,46 +4847,46 @@
         <v>5.467203420787769</v>
       </c>
       <c r="L17" s="3">
-        <v>0.971176449813876</v>
+        <v>1.074102236343531</v>
       </c>
       <c r="M17" s="3">
-        <v>0.5103518930759067</v>
+        <v>0.7183100856681376</v>
       </c>
       <c r="N17" s="3">
-        <v>15.76346938827487</v>
+        <v>46.99938092625879</v>
       </c>
       <c r="O17" s="3">
-        <v>12.16624335439029</v>
+        <v>76.73964108056255</v>
       </c>
       <c r="P17" s="3">
-        <v>5.028823550186124</v>
+        <v>4.92589776365647</v>
       </c>
       <c r="Q17" s="3">
-        <v>0.5103518930759067</v>
+        <v>0.7183100856681376</v>
       </c>
       <c r="R17" s="3">
-        <v>0.935161759447538</v>
+        <v>0.4636758410913448</v>
       </c>
       <c r="S17" s="3">
-        <v>93.64102529752516</v>
+        <v>303.3821356782841</v>
       </c>
       <c r="T17" s="3">
-        <v>4.028533839757347</v>
+        <v>3.51800999574692</v>
       </c>
       <c r="U17" s="3">
-        <v>6.029113260614901</v>
+        <v>6.333785531566019</v>
       </c>
       <c r="V17" s="3">
-        <v>0.5103518930759067</v>
+        <v>0.7183100856681376</v>
       </c>
       <c r="W17" s="3">
-        <v>3.450900000000002</v>
+        <v>3.482800000000002</v>
       </c>
       <c r="X17" s="3">
-        <v>-5.405827096661705</v>
+        <v>-5.602432752989337</v>
       </c>
       <c r="Y17" s="3">
-        <v>3.928012881486768E-06</v>
+        <v>2.497855132006539E-06</v>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
@@ -4970,94 +4894,94 @@
         </is>
       </c>
       <c r="AA17" s="3">
-        <v>27.34353065490723</v>
+        <v>39.6137</v>
       </c>
       <c r="AB17" s="3">
-        <v>20.43816757202148</v>
+        <v>28.862335</v>
       </c>
       <c r="AC17" s="3">
-        <v>55.06995391845703</v>
+        <v>48.138588</v>
       </c>
       <c r="AD17" s="3">
         <v>0</v>
       </c>
       <c r="AE17" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF17" s="3">
         <v>0</v>
       </c>
       <c r="AG17" s="3">
-        <v>0.5315255522727966</v>
+        <v>0.48098594</v>
       </c>
       <c r="AH17" s="3">
-        <v>0.6730732917785645</v>
+        <v>0.25535274</v>
       </c>
       <c r="AI17" s="3">
-        <v>0.778851330280304</v>
+        <v>0.9284628</v>
       </c>
       <c r="AJ17" s="3">
-        <v>0.1108301654458046</v>
+        <v>0.06717495599999999</v>
       </c>
       <c r="AK17" s="3">
-        <v>0.9728624224662781</v>
+        <v>0.8941488</v>
       </c>
       <c r="AL17" s="3">
-        <v>0.2244101017713547</v>
+        <v>0.11530211</v>
       </c>
       <c r="AM17" s="3">
-        <v>0.5238450765609741</v>
+        <v>0.62505996</v>
       </c>
       <c r="AN17" s="3">
-        <v>0.5843721628189087</v>
+        <v>0.7560564</v>
       </c>
       <c r="AO17" s="3">
-        <v>0.4598401486873627</v>
+        <v>0.08851654</v>
       </c>
       <c r="AP17" s="3">
-        <v>0.9567853808403015</v>
+        <v>0.97979707</v>
       </c>
       <c r="AQ17" s="3">
-        <v>0.9995303153991699</v>
+        <v>0.9999034</v>
       </c>
       <c r="AR17" s="3">
-        <v>0.7863090038299561</v>
+        <v>0.7694201000000001</v>
       </c>
       <c r="AS17" s="3">
-        <v>0.9379715919494629</v>
+        <v>0.9559449</v>
       </c>
       <c r="AT17" s="3">
-        <v>0.9101460576057434</v>
+        <v>0.9374962</v>
       </c>
       <c r="AU17" s="3">
-        <v>-5.119878768920898</v>
+        <v>-4.9130955</v>
       </c>
       <c r="AV17" s="3">
-        <v>86.74415588378906</v>
+        <v>92.995125</v>
       </c>
       <c r="AW17" s="3">
-        <v>16.6041145324707</v>
+        <v>11.678904</v>
       </c>
       <c r="AX17" s="3">
-        <v>449.5550000000002</v>
+        <v>477.5650000000003</v>
       </c>
       <c r="AY17" s="3">
-        <v>3.450900000000002</v>
+        <v>3.482800000000002</v>
       </c>
       <c r="AZ17" s="3">
-        <v>0.3121353019163128</v>
+        <v>0.2134025706227068</v>
       </c>
       <c r="BA17" s="3">
         <v>4</v>
       </c>
       <c r="BB17" s="3">
-        <v>3.549485059245518</v>
+        <v>3.482053497345049</v>
       </c>
       <c r="BC17" s="3">
-        <v>0.7167238823060536</v>
+        <v>0.7242162780727723</v>
       </c>
       <c r="BD17" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BE17" s="3">
         <v>0</v>
@@ -5069,22 +4993,22 @@
     <row r="18" ht="92" customHeight="1">
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>C=CCOCC#Cc1cncc(N2CCC3(CC2)CN(Cc2cc(N)cc([N+](=O)[O-])c2)C3)c1</t>
+          <t>CCCC#Cc1cncc(N2CCC3(CC2)CN(C(=O)c2cc(N)cc([N+](=O)[O-])c2)C3)c1</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(Cc4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
+          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="D18" s="3">
         <v>1</v>
       </c>
       <c r="E18" s="3">
-        <v>0.544</v>
+        <v>0.646551724137931</v>
       </c>
       <c r="F18" s="3">
-        <v>8.67</v>
+        <v>8.65</v>
       </c>
       <c r="G18" s="3">
         <v>5</v>
@@ -5095,55 +5019,55 @@
         </is>
       </c>
       <c r="I18" s="3">
-        <v>0.5327965792122313</v>
+        <v>0.5799605174651357</v>
       </c>
       <c r="J18" s="3">
-        <v>3.410331364424373</v>
+        <v>3.801548341527018</v>
       </c>
       <c r="K18" s="3">
-        <v>5.467203420787769</v>
+        <v>5.420039482534865</v>
       </c>
       <c r="L18" s="3">
-        <v>0.9857909523812385</v>
+        <v>1.180284394536799</v>
       </c>
       <c r="M18" s="3">
-        <v>0.5237856847877402</v>
+        <v>0.5992675523730433</v>
       </c>
       <c r="N18" s="3">
-        <v>16.71682039167111</v>
+        <v>47.31815208211359</v>
       </c>
       <c r="O18" s="3">
-        <v>13.07123879593058</v>
+        <v>76.45037729542869</v>
       </c>
       <c r="P18" s="3">
-        <v>5.014209047618762</v>
+        <v>4.819715605463201</v>
       </c>
       <c r="Q18" s="3">
-        <v>0.5237856847877402</v>
+        <v>0.5992675523730433</v>
       </c>
       <c r="R18" s="3">
-        <v>0.9102716356660688</v>
+        <v>1.013257884657467</v>
       </c>
       <c r="S18" s="3">
-        <v>102.8989384854388</v>
+        <v>226.3855992289432</v>
       </c>
       <c r="T18" s="3">
-        <v>3.987589105434791</v>
+        <v>3.645151202812036</v>
       </c>
       <c r="U18" s="3">
-        <v>6.040828989802733</v>
+        <v>5.994280008114366</v>
       </c>
       <c r="V18" s="3">
-        <v>0.5237856847877402</v>
+        <v>0.5992675523730433</v>
       </c>
       <c r="W18" s="3">
-        <v>3.228500000000001</v>
+        <v>3.466200000000001</v>
       </c>
       <c r="X18" s="3">
-        <v>-5.224093672391016</v>
+        <v>-5.322814977705623</v>
       </c>
       <c r="Y18" s="3">
-        <v>5.969065267346864E-06</v>
+        <v>4.755377759510845E-06</v>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
@@ -5151,94 +5075,94 @@
         </is>
       </c>
       <c r="AA18" s="3">
-        <v>24.91098976135254</v>
+        <v>32.311653</v>
       </c>
       <c r="AB18" s="3">
-        <v>16.69750785827637</v>
+        <v>27.43801</v>
       </c>
       <c r="AC18" s="3">
-        <v>46.32698822021484</v>
+        <v>43.311306</v>
       </c>
       <c r="AD18" s="3">
         <v>0</v>
       </c>
       <c r="AE18" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AF18" s="3">
         <v>0</v>
       </c>
       <c r="AG18" s="3">
-        <v>0.4479065537452698</v>
+        <v>0.6011542</v>
       </c>
       <c r="AH18" s="3">
-        <v>0.6604646444320679</v>
+        <v>0.28777766</v>
       </c>
       <c r="AI18" s="3">
-        <v>0.7542520761489868</v>
+        <v>0.9109559</v>
       </c>
       <c r="AJ18" s="3">
-        <v>0.1146994382143021</v>
+        <v>0.07473515999999999</v>
       </c>
       <c r="AK18" s="3">
-        <v>0.9743545651435852</v>
+        <v>0.86281884</v>
       </c>
       <c r="AL18" s="3">
-        <v>0.2621746361255646</v>
+        <v>0.178799</v>
       </c>
       <c r="AM18" s="3">
-        <v>0.5962370634078979</v>
+        <v>0.52853626</v>
       </c>
       <c r="AN18" s="3">
-        <v>0.6635324358940125</v>
+        <v>0.66323686</v>
       </c>
       <c r="AO18" s="3">
-        <v>0.5958261489868164</v>
+        <v>0.11422368</v>
       </c>
       <c r="AP18" s="3">
-        <v>0.9773931503295898</v>
+        <v>0.9641881</v>
       </c>
       <c r="AQ18" s="3">
-        <v>0.9997422099113464</v>
+        <v>0.99985945</v>
       </c>
       <c r="AR18" s="3">
-        <v>0.7139910459518433</v>
+        <v>0.78965485</v>
       </c>
       <c r="AS18" s="3">
-        <v>0.9213010668754578</v>
+        <v>0.9479746999999999</v>
       </c>
       <c r="AT18" s="3">
-        <v>0.9123933911323547</v>
+        <v>0.8704244</v>
       </c>
       <c r="AU18" s="3">
-        <v>-5.144465446472168</v>
+        <v>-4.8440638</v>
       </c>
       <c r="AV18" s="3">
-        <v>88.25447845458984</v>
+        <v>94.9301</v>
       </c>
       <c r="AW18" s="3">
-        <v>13.37487602233887</v>
+        <v>8.724216999999999</v>
       </c>
       <c r="AX18" s="3">
-        <v>447.5390000000002</v>
+        <v>433.5120000000001</v>
       </c>
       <c r="AY18" s="3">
-        <v>3.228500000000001</v>
+        <v>3.466200000000001</v>
       </c>
       <c r="AZ18" s="3">
-        <v>0.1737647718090828</v>
+        <v>0.3425547491471555</v>
       </c>
       <c r="BA18" s="3">
         <v>4</v>
       </c>
       <c r="BB18" s="3">
-        <v>3.610344116317478</v>
+        <v>3.421184813315296</v>
       </c>
       <c r="BC18" s="3">
-        <v>0.7099617648536136</v>
+        <v>0.7309794651871895</v>
       </c>
       <c r="BD18" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BE18" s="3">
         <v>0</v>
@@ -5250,22 +5174,22 @@
     <row r="19" ht="92" customHeight="1">
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>CCCCOCC#Cc1cncc(N2CCC3(CC2)CN(C(=O)c2cc(N)cc([N+](=O)[O-])c2)C3)c1</t>
+          <t>CCC#Cc1cncc(N2CCC3(CC2)CN(Cc2cc(N)cc([N+](=O)[O-])c2)C3)c1</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
+          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(Cc4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="D19" s="3">
         <v>1</v>
       </c>
       <c r="E19" s="3">
-        <v>0.6260162601626016</v>
+        <v>0.6</v>
       </c>
       <c r="F19" s="3">
-        <v>9.01</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="G19" s="3">
         <v>5</v>
@@ -5276,55 +5200,55 @@
         </is>
       </c>
       <c r="I19" s="3">
-        <v>0.5327965792122313</v>
+        <v>0.5799605174651357</v>
       </c>
       <c r="J19" s="3">
-        <v>3.410331364424373</v>
+        <v>3.801548341527018</v>
       </c>
       <c r="K19" s="3">
-        <v>5.467203420787769</v>
+        <v>5.420039482534865</v>
       </c>
       <c r="L19" s="3">
-        <v>1.074102236343531</v>
+        <v>1.098600400826603</v>
       </c>
       <c r="M19" s="3">
-        <v>0.7183100856681376</v>
+        <v>0.7356550303972638</v>
       </c>
       <c r="N19" s="3">
-        <v>46.99938092625879</v>
+        <v>48.03957443095201</v>
       </c>
       <c r="O19" s="3">
-        <v>76.73964108056255</v>
+        <v>76.27873922900247</v>
       </c>
       <c r="P19" s="3">
-        <v>4.92589776365647</v>
+        <v>4.901399599173397</v>
       </c>
       <c r="Q19" s="3">
-        <v>0.7183100856681376</v>
+        <v>0.7356550303972638</v>
       </c>
       <c r="R19" s="3">
-        <v>0.4636758410913448</v>
+        <v>0.4536454311199809</v>
       </c>
       <c r="S19" s="3">
-        <v>303.3821356782841</v>
+        <v>347.1236952873692</v>
       </c>
       <c r="T19" s="3">
-        <v>3.51800999574692</v>
+        <v>3.45951573959476</v>
       </c>
       <c r="U19" s="3">
-        <v>6.333785531566019</v>
+        <v>6.343283458752034</v>
       </c>
       <c r="V19" s="3">
-        <v>0.7183100856681376</v>
+        <v>0.7356550303972638</v>
       </c>
       <c r="W19" s="3">
-        <v>3.482800000000002</v>
+        <v>3.435900000000001</v>
       </c>
       <c r="X19" s="3">
-        <v>-5.602432752989337</v>
+        <v>-5.125743554544017</v>
       </c>
       <c r="Y19" s="3">
-        <v>2.497855132006539E-06</v>
+        <v>7.486114156970538E-06</v>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
@@ -5332,94 +5256,94 @@
         </is>
       </c>
       <c r="AA19" s="3">
-        <v>39.61370086669922</v>
+        <v>21.485523</v>
       </c>
       <c r="AB19" s="3">
-        <v>28.86233520507812</v>
+        <v>19.234173</v>
       </c>
       <c r="AC19" s="3">
-        <v>48.13858795166016</v>
+        <v>52.027428</v>
       </c>
       <c r="AD19" s="3">
         <v>0</v>
       </c>
       <c r="AE19" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF19" s="3">
         <v>0</v>
       </c>
       <c r="AG19" s="3">
-        <v>0.4809859395027161</v>
+        <v>0.49942857</v>
       </c>
       <c r="AH19" s="3">
-        <v>0.2553527355194092</v>
+        <v>0.66403073</v>
       </c>
       <c r="AI19" s="3">
-        <v>0.9284628033638</v>
+        <v>0.74702656</v>
       </c>
       <c r="AJ19" s="3">
-        <v>0.06717495620250702</v>
+        <v>0.11464952</v>
       </c>
       <c r="AK19" s="3">
-        <v>0.8941488265991211</v>
+        <v>0.96694833</v>
       </c>
       <c r="AL19" s="3">
-        <v>0.1153021082282066</v>
+        <v>0.3430485</v>
       </c>
       <c r="AM19" s="3">
-        <v>0.625059962272644</v>
+        <v>0.5428937</v>
       </c>
       <c r="AN19" s="3">
-        <v>0.7560564279556274</v>
+        <v>0.5987871</v>
       </c>
       <c r="AO19" s="3">
-        <v>0.08851654082536697</v>
+        <v>0.5522696</v>
       </c>
       <c r="AP19" s="3">
-        <v>0.9797970652580261</v>
+        <v>0.9574511999999999</v>
       </c>
       <c r="AQ19" s="3">
-        <v>0.9999033808708191</v>
+        <v>0.99983466</v>
       </c>
       <c r="AR19" s="3">
-        <v>0.7694200873374939</v>
+        <v>0.77307653</v>
       </c>
       <c r="AS19" s="3">
-        <v>0.9559448957443237</v>
+        <v>0.9339366</v>
       </c>
       <c r="AT19" s="3">
-        <v>0.9374961853027344</v>
+        <v>0.88143605</v>
       </c>
       <c r="AU19" s="3">
-        <v>-4.913095474243164</v>
+        <v>-5.062598</v>
       </c>
       <c r="AV19" s="3">
-        <v>92.99512481689453</v>
+        <v>91.88523000000001</v>
       </c>
       <c r="AW19" s="3">
-        <v>11.67890357971191</v>
+        <v>13.114458</v>
       </c>
       <c r="AX19" s="3">
-        <v>477.5650000000003</v>
+        <v>405.5020000000001</v>
       </c>
       <c r="AY19" s="3">
-        <v>3.482800000000002</v>
+        <v>3.435900000000001</v>
       </c>
       <c r="AZ19" s="3">
-        <v>0.2134025706227068</v>
+        <v>0.3628100347579408</v>
       </c>
       <c r="BA19" s="3">
         <v>4</v>
       </c>
       <c r="BB19" s="3">
-        <v>3.482053497345049</v>
+        <v>3.443895655693749</v>
       </c>
       <c r="BC19" s="3">
-        <v>0.7242162780727723</v>
+        <v>0.72845603825625</v>
       </c>
       <c r="BD19" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BE19" s="3">
         <v>0</v>
@@ -5431,7 +5355,7 @@
     <row r="20" ht="92" customHeight="1">
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CCCC#Cc1cncc(N2CCC3(CC2)CN(C(=O)c2cc(N)cc([N+](=O)[O-])c2)C3)c1</t>
+          <t>CS(=O)(=O)c1cc(C(=O)N2CC3(CCN(c4cncc(C#CC5CC5)c4)C3)C2)cc([N+](=O)[O-])c1</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -5443,10 +5367,10 @@
         <v>1</v>
       </c>
       <c r="E20" s="3">
-        <v>0.646551724137931</v>
+        <v>0.5853658536585366</v>
       </c>
       <c r="F20" s="3">
-        <v>8.65</v>
+        <v>9.31</v>
       </c>
       <c r="G20" s="3">
         <v>5</v>
@@ -5457,55 +5381,55 @@
         </is>
       </c>
       <c r="I20" s="3">
-        <v>0.5799605174651357</v>
+        <v>0.5861720941724983</v>
       </c>
       <c r="J20" s="3">
-        <v>3.801548341527018</v>
+        <v>3.856311381573305</v>
       </c>
       <c r="K20" s="3">
-        <v>5.420039482534865</v>
+        <v>5.413827905827501</v>
       </c>
       <c r="L20" s="3">
-        <v>1.180284394536799</v>
+        <v>0.9422375137779044</v>
       </c>
       <c r="M20" s="3">
-        <v>0.5992675523730433</v>
+        <v>0.4029876655948264</v>
       </c>
       <c r="N20" s="3">
-        <v>47.31815208211359</v>
+        <v>12.49208611572615</v>
       </c>
       <c r="O20" s="3">
-        <v>76.45037729542869</v>
+        <v>8.790408665713716</v>
       </c>
       <c r="P20" s="3">
-        <v>4.819715605463201</v>
+        <v>5.057762486222096</v>
       </c>
       <c r="Q20" s="3">
-        <v>0.5992675523730433</v>
+        <v>0.4029876655948264</v>
       </c>
       <c r="R20" s="3">
-        <v>1.013257884657467</v>
+        <v>1.420305239666745</v>
       </c>
       <c r="S20" s="3">
-        <v>226.3855992289432</v>
+        <v>53.96265863180039</v>
       </c>
       <c r="T20" s="3">
-        <v>3.645151202812036</v>
+        <v>4.267906661656236</v>
       </c>
       <c r="U20" s="3">
-        <v>5.994280008114366</v>
+        <v>5.847618310787955</v>
       </c>
       <c r="V20" s="3">
-        <v>0.5992675523730433</v>
+        <v>0.4029876655948264</v>
       </c>
       <c r="W20" s="3">
-        <v>3.466200000000002</v>
+        <v>2.507300000000001</v>
       </c>
       <c r="X20" s="3">
-        <v>-5.322814977705623</v>
+        <v>-4.913298742927338</v>
       </c>
       <c r="Y20" s="3">
-        <v>4.755377759510845E-06</v>
+        <v>1.220959496378729E-05</v>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
@@ -5513,94 +5437,94 @@
         </is>
       </c>
       <c r="AA20" s="3">
-        <v>32.31165313720703</v>
+        <v>18.438541</v>
       </c>
       <c r="AB20" s="3">
-        <v>27.43800926208496</v>
+        <v>7.754645</v>
       </c>
       <c r="AC20" s="3">
-        <v>43.31130599975586</v>
+        <v>46.15148</v>
       </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
       <c r="AE20" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF20" s="3">
         <v>0</v>
       </c>
       <c r="AG20" s="3">
-        <v>0.6011542081832886</v>
+        <v>0.3609733</v>
       </c>
       <c r="AH20" s="3">
-        <v>0.2877776622772217</v>
+        <v>0.10870327</v>
       </c>
       <c r="AI20" s="3">
-        <v>0.9109559059143066</v>
+        <v>0.95704967</v>
       </c>
       <c r="AJ20" s="3">
-        <v>0.07473515719175339</v>
+        <v>0.16123754</v>
       </c>
       <c r="AK20" s="3">
-        <v>0.8628188371658325</v>
+        <v>0.5677575</v>
       </c>
       <c r="AL20" s="3">
-        <v>0.1787990033626556</v>
+        <v>0.039175797</v>
       </c>
       <c r="AM20" s="3">
-        <v>0.5285362601280212</v>
+        <v>0.24344108</v>
       </c>
       <c r="AN20" s="3">
-        <v>0.6632368564605713</v>
+        <v>0.4448568</v>
       </c>
       <c r="AO20" s="3">
-        <v>0.1142236813902855</v>
+        <v>0.066801734</v>
       </c>
       <c r="AP20" s="3">
-        <v>0.9641880989074707</v>
+        <v>0.8808093</v>
       </c>
       <c r="AQ20" s="3">
-        <v>0.9998594522476196</v>
+        <v>0.99958503</v>
       </c>
       <c r="AR20" s="3">
-        <v>0.7896548509597778</v>
+        <v>0.80475485</v>
       </c>
       <c r="AS20" s="3">
-        <v>0.947974681854248</v>
+        <v>0.8599375</v>
       </c>
       <c r="AT20" s="3">
-        <v>0.8704243898391724</v>
+        <v>0.72190976</v>
       </c>
       <c r="AU20" s="3">
-        <v>-4.844063758850098</v>
+        <v>-4.7375364</v>
       </c>
       <c r="AV20" s="3">
-        <v>94.93009948730469</v>
+        <v>90.65664</v>
       </c>
       <c r="AW20" s="3">
-        <v>8.724217414855957</v>
+        <v>2.88414</v>
       </c>
       <c r="AX20" s="3">
-        <v>433.5120000000001</v>
+        <v>480.5460000000003</v>
       </c>
       <c r="AY20" s="3">
-        <v>3.466200000000002</v>
+        <v>2.507300000000001</v>
       </c>
       <c r="AZ20" s="3">
-        <v>0.3425547491471556</v>
+        <v>0.3752512149049585</v>
       </c>
       <c r="BA20" s="3">
         <v>4</v>
       </c>
       <c r="BB20" s="3">
-        <v>3.421184813315295</v>
+        <v>3.556180726353832</v>
       </c>
       <c r="BC20" s="3">
-        <v>0.7309794651871895</v>
+        <v>0.7159799192940187</v>
       </c>
       <c r="BD20" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BE20" s="3">
         <v>0</v>
@@ -5612,7 +5536,7 @@
     <row r="21" ht="92" customHeight="1">
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CCC#Cc1cncc(N2CCC3(CC2)CN(Cc2cc(N)cc([N+](=O)[O-])c2)C3)c1</t>
+          <t>CC(C)(C)OC(=O)N1CCC2(C1)CN(c1cncc(C#CC3CC3)c1)C2</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -5624,10 +5548,10 @@
         <v>1</v>
       </c>
       <c r="E21" s="3">
-        <v>0.6</v>
+        <v>0.3565891472868217</v>
       </c>
       <c r="F21" s="3">
-        <v>9.619999999999999</v>
+        <v>9.82</v>
       </c>
       <c r="G21" s="3">
         <v>5</v>
@@ -5638,55 +5562,55 @@
         </is>
       </c>
       <c r="I21" s="3">
-        <v>0.5799605174651357</v>
+        <v>0.6051538968907209</v>
       </c>
       <c r="J21" s="3">
-        <v>3.801548341527018</v>
+        <v>4.028597666980577</v>
       </c>
       <c r="K21" s="3">
-        <v>5.420039482534865</v>
+        <v>5.394846103109279</v>
       </c>
       <c r="L21" s="3">
-        <v>1.098600400826603</v>
+        <v>0.8824989854002624</v>
       </c>
       <c r="M21" s="3">
-        <v>0.7356550303972638</v>
+        <v>0.3228250251742512</v>
       </c>
       <c r="N21" s="3">
-        <v>48.03957443095201</v>
+        <v>10.34297534030582</v>
       </c>
       <c r="O21" s="3">
-        <v>76.27873922900247</v>
+        <v>8.855951904205119</v>
       </c>
       <c r="P21" s="3">
-        <v>4.901399599173397</v>
+        <v>5.117501014599737</v>
       </c>
       <c r="Q21" s="3">
-        <v>0.7356550303972638</v>
+        <v>0.3228250251742512</v>
       </c>
       <c r="R21" s="3">
-        <v>0.453645431119981</v>
+        <v>1.777304891104969</v>
       </c>
       <c r="S21" s="3">
-        <v>347.1236952873692</v>
+        <v>32.75186496525397</v>
       </c>
       <c r="T21" s="3">
-        <v>3.45951573959476</v>
+        <v>4.484763965258205</v>
       </c>
       <c r="U21" s="3">
-        <v>6.343283458752034</v>
+        <v>5.750238063941271</v>
       </c>
       <c r="V21" s="3">
-        <v>0.7356550303972638</v>
+        <v>0.3228250251742512</v>
       </c>
       <c r="W21" s="3">
-        <v>3.435900000000001</v>
+        <v>3.290300000000002</v>
       </c>
       <c r="X21" s="3">
-        <v>-5.125743554544017</v>
+        <v>-4.6118160103259</v>
       </c>
       <c r="Y21" s="3">
-        <v>7.486114156970538E-06</v>
+        <v>2.444465935948885E-05</v>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
@@ -5694,94 +5618,94 @@
         </is>
       </c>
       <c r="AA21" s="3">
-        <v>21.48552322387695</v>
+        <v>56.564648</v>
       </c>
       <c r="AB21" s="3">
-        <v>19.23417282104492</v>
+        <v>51.992332</v>
       </c>
       <c r="AC21" s="3">
-        <v>52.02742767333984</v>
+        <v>40.707268</v>
       </c>
       <c r="AD21" s="3">
         <v>0</v>
       </c>
       <c r="AE21" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AF21" s="3">
         <v>0</v>
       </c>
       <c r="AG21" s="3">
-        <v>0.4994285702705383</v>
+        <v>0.17725909</v>
       </c>
       <c r="AH21" s="3">
-        <v>0.6640307307243347</v>
+        <v>0.22454533</v>
       </c>
       <c r="AI21" s="3">
-        <v>0.7470265626907349</v>
+        <v>0.69295204</v>
       </c>
       <c r="AJ21" s="3">
-        <v>0.1146495193243027</v>
+        <v>0.088378675</v>
       </c>
       <c r="AK21" s="3">
-        <v>0.9669483304023743</v>
+        <v>0.6438459</v>
       </c>
       <c r="AL21" s="3">
-        <v>0.3430485129356384</v>
+        <v>0.2338467</v>
       </c>
       <c r="AM21" s="3">
-        <v>0.5428937077522278</v>
+        <v>0.5687932</v>
       </c>
       <c r="AN21" s="3">
-        <v>0.5987871289253235</v>
+        <v>0.5209888</v>
       </c>
       <c r="AO21" s="3">
-        <v>0.5522695779800415</v>
+        <v>0.08753231</v>
       </c>
       <c r="AP21" s="3">
-        <v>0.9574512243270874</v>
+        <v>0.7143261</v>
       </c>
       <c r="AQ21" s="3">
-        <v>0.9998346567153931</v>
+        <v>0.9997827</v>
       </c>
       <c r="AR21" s="3">
-        <v>0.7730765342712402</v>
+        <v>0.7694125000000001</v>
       </c>
       <c r="AS21" s="3">
-        <v>0.933936595916748</v>
+        <v>0.9653592</v>
       </c>
       <c r="AT21" s="3">
-        <v>0.8814360499382019</v>
+        <v>0.596781</v>
       </c>
       <c r="AU21" s="3">
-        <v>-5.06259822845459</v>
+        <v>-4.5518446</v>
       </c>
       <c r="AV21" s="3">
-        <v>91.88523101806641</v>
+        <v>94.36017</v>
       </c>
       <c r="AW21" s="3">
-        <v>13.11445808410645</v>
+        <v>8.904188</v>
       </c>
       <c r="AX21" s="3">
-        <v>405.5020000000001</v>
+        <v>353.4660000000002</v>
       </c>
       <c r="AY21" s="3">
-        <v>3.435900000000001</v>
+        <v>3.290300000000002</v>
       </c>
       <c r="AZ21" s="3">
-        <v>0.3628100347579408</v>
+        <v>0.7270065061949308</v>
       </c>
       <c r="BA21" s="3">
         <v>4</v>
       </c>
       <c r="BB21" s="3">
-        <v>3.443895655693749</v>
+        <v>3.444288329613787</v>
       </c>
       <c r="BC21" s="3">
-        <v>0.72845603825625</v>
+        <v>0.7284124078206904</v>
       </c>
       <c r="BD21" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BE21" s="3">
         <v>0</v>
@@ -5793,22 +5717,22 @@
     <row r="22" ht="92" customHeight="1">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CS(=O)(=O)c1cc(C(=O)N2CC3(CCN(c4cncc(C#CC5CC5)c4)C3)C2)cc([N+](=O)[O-])c1</t>
+          <t>CC(C)(C)OC(=O)N1CC2(CCN(c3cncc(C#CC4CC4)c3)C2)C1</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
+          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(Cc4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="D22" s="3">
         <v>1</v>
       </c>
       <c r="E22" s="3">
-        <v>0.5853658536585366</v>
+        <v>0.3779527559055118</v>
       </c>
       <c r="F22" s="3">
-        <v>9.31</v>
+        <v>7.29</v>
       </c>
       <c r="G22" s="3">
         <v>5</v>
@@ -5819,55 +5743,55 @@
         </is>
       </c>
       <c r="I22" s="3">
-        <v>0.5861720941724983</v>
+        <v>0.6051538968907209</v>
       </c>
       <c r="J22" s="3">
-        <v>3.856311381573305</v>
+        <v>4.028597666980577</v>
       </c>
       <c r="K22" s="3">
-        <v>5.413827905827501</v>
+        <v>5.394846103109279</v>
       </c>
       <c r="L22" s="3">
-        <v>0.9422375137779045</v>
+        <v>0.8957491087190782</v>
       </c>
       <c r="M22" s="3">
-        <v>0.4029876655948264</v>
+        <v>0.3281876103103728</v>
       </c>
       <c r="N22" s="3">
-        <v>12.49208611572615</v>
+        <v>10.6493487168374</v>
       </c>
       <c r="O22" s="3">
-        <v>8.790408665713716</v>
+        <v>8.772131703379241</v>
       </c>
       <c r="P22" s="3">
-        <v>5.057762486222096</v>
+        <v>5.104250891280921</v>
       </c>
       <c r="Q22" s="3">
-        <v>0.4029876655948264</v>
+        <v>0.3281876103103728</v>
       </c>
       <c r="R22" s="3">
-        <v>1.420305239666745</v>
+        <v>1.788551263863722</v>
       </c>
       <c r="S22" s="3">
-        <v>53.96265863180039</v>
+        <v>34.59368487158814</v>
       </c>
       <c r="T22" s="3">
-        <v>4.267906661656236</v>
+        <v>4.461003175072591</v>
       </c>
       <c r="U22" s="3">
-        <v>5.847618310787955</v>
+        <v>5.747498607489253</v>
       </c>
       <c r="V22" s="3">
-        <v>0.4029876655948264</v>
+        <v>0.3281876103103728</v>
       </c>
       <c r="W22" s="3">
-        <v>2.507300000000001</v>
+        <v>3.290300000000002</v>
       </c>
       <c r="X22" s="3">
-        <v>-4.913298742927338</v>
+        <v>-4.6118160103259</v>
       </c>
       <c r="Y22" s="3">
-        <v>1.220959496378729E-05</v>
+        <v>2.444465935948885E-05</v>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
@@ -5875,94 +5799,94 @@
         </is>
       </c>
       <c r="AA22" s="3">
-        <v>18.43854141235352</v>
+        <v>60.528114</v>
       </c>
       <c r="AB22" s="3">
-        <v>7.754644870758057</v>
+        <v>54.043926</v>
       </c>
       <c r="AC22" s="3">
-        <v>46.15148162841797</v>
+        <v>41.54251</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
       </c>
       <c r="AE22" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF22" s="3">
         <v>0</v>
       </c>
       <c r="AG22" s="3">
-        <v>0.3609732985496521</v>
+        <v>0.18171215</v>
       </c>
       <c r="AH22" s="3">
-        <v>0.1087032705545425</v>
+        <v>0.22591284</v>
       </c>
       <c r="AI22" s="3">
-        <v>0.9570496678352356</v>
+        <v>0.69511676</v>
       </c>
       <c r="AJ22" s="3">
-        <v>0.1612375378608704</v>
+        <v>0.09010277999999999</v>
       </c>
       <c r="AK22" s="3">
-        <v>0.5677574872970581</v>
+        <v>0.6656471</v>
       </c>
       <c r="AL22" s="3">
-        <v>0.03917579725384712</v>
+        <v>0.2871345</v>
       </c>
       <c r="AM22" s="3">
-        <v>0.2434410750865936</v>
+        <v>0.58677197</v>
       </c>
       <c r="AN22" s="3">
-        <v>0.4448567926883698</v>
+        <v>0.5658632</v>
       </c>
       <c r="AO22" s="3">
-        <v>0.06680173426866531</v>
+        <v>0.09989244</v>
       </c>
       <c r="AP22" s="3">
-        <v>0.8808093070983887</v>
+        <v>0.767943</v>
       </c>
       <c r="AQ22" s="3">
-        <v>0.9995850324630737</v>
+        <v>0.9997622</v>
       </c>
       <c r="AR22" s="3">
-        <v>0.8047548532485962</v>
+        <v>0.76465195</v>
       </c>
       <c r="AS22" s="3">
-        <v>0.8599374890327454</v>
+        <v>0.967028</v>
       </c>
       <c r="AT22" s="3">
-        <v>0.721909761428833</v>
+        <v>0.6451166</v>
       </c>
       <c r="AU22" s="3">
-        <v>-4.737536430358887</v>
+        <v>-4.5823603</v>
       </c>
       <c r="AV22" s="3">
-        <v>90.65663909912109</v>
+        <v>95.09493999999999</v>
       </c>
       <c r="AW22" s="3">
-        <v>2.884140014648438</v>
+        <v>8.923327</v>
       </c>
       <c r="AX22" s="3">
-        <v>480.5460000000003</v>
+        <v>353.4660000000002</v>
       </c>
       <c r="AY22" s="3">
-        <v>2.507300000000001</v>
+        <v>3.290300000000002</v>
       </c>
       <c r="AZ22" s="3">
-        <v>0.3752512149049585</v>
+        <v>0.7270065061949308</v>
       </c>
       <c r="BA22" s="3">
         <v>4</v>
       </c>
       <c r="BB22" s="3">
-        <v>3.556180726353832</v>
+        <v>3.459755637306096</v>
       </c>
       <c r="BC22" s="3">
-        <v>0.7159799192940187</v>
+        <v>0.7266938180771005</v>
       </c>
       <c r="BD22" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BE22" s="3">
         <v>0</v>
@@ -5974,7 +5898,7 @@
     <row r="23" ht="92" customHeight="1">
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>CC(C)(C)OC(=O)N1CCC2(C1)CN(c1cncc(C#CC3CC3)c1)C2</t>
+          <t>O=[N+]([O-])c1cc(F)cc(CN2CC3(CCN(c4cncc(Cl)c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -5986,10 +5910,10 @@
         <v>1</v>
       </c>
       <c r="E23" s="3">
-        <v>0.3565891472868217</v>
+        <v>0.5495495495495496</v>
       </c>
       <c r="F23" s="3">
-        <v>9.82</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="G23" s="3">
         <v>5</v>
@@ -6009,46 +5933,46 @@
         <v>5.394846103109279</v>
       </c>
       <c r="L23" s="3">
-        <v>0.8824989854002624</v>
+        <v>1.056317392714866</v>
       </c>
       <c r="M23" s="3">
-        <v>0.3228250251742513</v>
+        <v>0.4098909832966713</v>
       </c>
       <c r="N23" s="3">
-        <v>10.34297534030582</v>
+        <v>16.68169616968234</v>
       </c>
       <c r="O23" s="3">
-        <v>8.855951904205119</v>
+        <v>12.29164682923438</v>
       </c>
       <c r="P23" s="3">
-        <v>5.117501014599737</v>
+        <v>4.943682607285134</v>
       </c>
       <c r="Q23" s="3">
-        <v>0.3228250251742513</v>
+        <v>0.4098909832966713</v>
       </c>
       <c r="R23" s="3">
-        <v>1.777304891104969</v>
+        <v>1.790321657914635</v>
       </c>
       <c r="S23" s="3">
-        <v>32.75186496525397</v>
+        <v>72.39419111851227</v>
       </c>
       <c r="T23" s="3">
-        <v>4.484763965258205</v>
+        <v>4.140296280023659</v>
       </c>
       <c r="U23" s="3">
-        <v>5.75023806394127</v>
+        <v>5.747068934546609</v>
       </c>
       <c r="V23" s="3">
-        <v>0.3228250251742513</v>
+        <v>0.4098909832966713</v>
       </c>
       <c r="W23" s="3">
-        <v>3.290300000000002</v>
+        <v>3.494600000000002</v>
       </c>
       <c r="X23" s="3">
-        <v>-4.6118160103259</v>
+        <v>-5.005804429618419</v>
       </c>
       <c r="Y23" s="3">
-        <v>2.444465935948885E-05</v>
+        <v>9.867237245062414E-06</v>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
@@ -6056,94 +5980,94 @@
         </is>
       </c>
       <c r="AA23" s="3">
-        <v>56.56464767456055</v>
+        <v>44.201073</v>
       </c>
       <c r="AB23" s="3">
-        <v>51.99233245849609</v>
+        <v>49.483833</v>
       </c>
       <c r="AC23" s="3">
-        <v>40.70726776123047</v>
+        <v>41.97674</v>
       </c>
       <c r="AD23" s="3">
         <v>0</v>
       </c>
       <c r="AE23" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF23" s="3">
         <v>0</v>
       </c>
       <c r="AG23" s="3">
-        <v>0.177259087562561</v>
+        <v>0.373483</v>
       </c>
       <c r="AH23" s="3">
-        <v>0.2245453298091888</v>
+        <v>0.5763953000000001</v>
       </c>
       <c r="AI23" s="3">
-        <v>0.692952036857605</v>
+        <v>0.6303479</v>
       </c>
       <c r="AJ23" s="3">
-        <v>0.0883786752820015</v>
+        <v>0.17717503</v>
       </c>
       <c r="AK23" s="3">
-        <v>0.6438459157943726</v>
+        <v>0.95487565</v>
       </c>
       <c r="AL23" s="3">
-        <v>0.2338466942310333</v>
+        <v>0.45091638</v>
       </c>
       <c r="AM23" s="3">
-        <v>0.5687931776046753</v>
+        <v>0.622636</v>
       </c>
       <c r="AN23" s="3">
-        <v>0.5209888219833374</v>
+        <v>0.44566232</v>
       </c>
       <c r="AO23" s="3">
-        <v>0.08753231167793274</v>
+        <v>0.7572044999999999</v>
       </c>
       <c r="AP23" s="3">
-        <v>0.7143260836601257</v>
+        <v>0.83970654</v>
       </c>
       <c r="AQ23" s="3">
-        <v>0.9997826814651489</v>
+        <v>0.9999773</v>
       </c>
       <c r="AR23" s="3">
-        <v>0.7694125175476074</v>
+        <v>0.8410287</v>
       </c>
       <c r="AS23" s="3">
-        <v>0.9653592109680176</v>
+        <v>0.9607558</v>
       </c>
       <c r="AT23" s="3">
-        <v>0.5967810153961182</v>
+        <v>0.7064048000000001</v>
       </c>
       <c r="AU23" s="3">
-        <v>-4.551844596862793</v>
+        <v>-4.7113543</v>
       </c>
       <c r="AV23" s="3">
-        <v>94.36016845703125</v>
+        <v>86.044235</v>
       </c>
       <c r="AW23" s="3">
-        <v>8.90418815612793</v>
+        <v>9.752675999999999</v>
       </c>
       <c r="AX23" s="3">
-        <v>353.4660000000002</v>
+        <v>376.8190000000001</v>
       </c>
       <c r="AY23" s="3">
-        <v>3.290300000000002</v>
+        <v>3.494600000000002</v>
       </c>
       <c r="AZ23" s="3">
-        <v>0.7270065061949308</v>
+        <v>0.6033991626381087</v>
       </c>
       <c r="BA23" s="3">
         <v>4</v>
       </c>
       <c r="BB23" s="3">
-        <v>3.444288329613787</v>
+        <v>3.197696943944662</v>
       </c>
       <c r="BC23" s="3">
-        <v>0.7284124078206904</v>
+        <v>0.7558114506728154</v>
       </c>
       <c r="BD23" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE23" s="3">
         <v>0</v>
@@ -6155,22 +6079,22 @@
     <row r="24" ht="92" customHeight="1">
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CC(C)(C)OC(=O)N1CC2(CCN(c3cncc(C#CC4CC4)c3)C2)C1</t>
+          <t>CC(C)(O)CC(=O)N1CC2(CCN(c3cncc(C#Cc4ccccc4)c3)C2)C1</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(Cc4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
+          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="D24" s="3">
         <v>1</v>
       </c>
       <c r="E24" s="3">
-        <v>0.3779527559055118</v>
+        <v>0.3969465648854962</v>
       </c>
       <c r="F24" s="3">
-        <v>7.29</v>
+        <v>9.77</v>
       </c>
       <c r="G24" s="3">
         <v>5</v>
@@ -6190,46 +6114,46 @@
         <v>5.394846103109279</v>
       </c>
       <c r="L24" s="3">
-        <v>0.8957491087190782</v>
+        <v>1.071027324227294</v>
       </c>
       <c r="M24" s="3">
-        <v>0.3281876103103729</v>
+        <v>0.4534855701030449</v>
       </c>
       <c r="N24" s="3">
-        <v>10.6493487168374</v>
+        <v>17.84268628492911</v>
       </c>
       <c r="O24" s="3">
-        <v>8.772131703379241</v>
+        <v>11.89399715379812</v>
       </c>
       <c r="P24" s="3">
-        <v>5.104250891280921</v>
+        <v>4.928972675772706</v>
       </c>
       <c r="Q24" s="3">
-        <v>0.3281876103103729</v>
+        <v>0.4534855701030449</v>
       </c>
       <c r="R24" s="3">
-        <v>1.788551263863722</v>
+        <v>1.521232540661306</v>
       </c>
       <c r="S24" s="3">
-        <v>34.59368487158814</v>
+        <v>91.17148772678068</v>
       </c>
       <c r="T24" s="3">
-        <v>4.461003175072591</v>
+        <v>4.040140958370738</v>
       </c>
       <c r="U24" s="3">
-        <v>5.747498607489253</v>
+        <v>5.817804393174674</v>
       </c>
       <c r="V24" s="3">
-        <v>0.3281876103103729</v>
+        <v>0.4534855701030449</v>
       </c>
       <c r="W24" s="3">
-        <v>3.290300000000002</v>
+        <v>2.681100000000002</v>
       </c>
       <c r="X24" s="3">
-        <v>-4.6118160103259</v>
+        <v>-4.469416891183609</v>
       </c>
       <c r="Y24" s="3">
-        <v>2.444465935948885E-05</v>
+        <v>3.39299413402709E-05</v>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
@@ -6237,13 +6161,13 @@
         </is>
       </c>
       <c r="AA24" s="3">
-        <v>60.52811431884766</v>
+        <v>16.769434</v>
       </c>
       <c r="AB24" s="3">
-        <v>54.04392623901367</v>
+        <v>33.807205</v>
       </c>
       <c r="AC24" s="3">
-        <v>41.54251098632812</v>
+        <v>41.897144</v>
       </c>
       <c r="AD24" s="3">
         <v>0</v>
@@ -6255,73 +6179,73 @@
         <v>0</v>
       </c>
       <c r="AG24" s="3">
-        <v>0.1817121505737305</v>
+        <v>0.2616261</v>
       </c>
       <c r="AH24" s="3">
-        <v>0.2259128391742706</v>
+        <v>0.2681746</v>
       </c>
       <c r="AI24" s="3">
-        <v>0.6951167583465576</v>
+        <v>0.7960621</v>
       </c>
       <c r="AJ24" s="3">
-        <v>0.09010277688503265</v>
+        <v>0.071016595</v>
       </c>
       <c r="AK24" s="3">
-        <v>0.6656470894813538</v>
+        <v>0.6336732</v>
       </c>
       <c r="AL24" s="3">
-        <v>0.2871344983577728</v>
+        <v>0.07451101</v>
       </c>
       <c r="AM24" s="3">
-        <v>0.5867719650268555</v>
+        <v>0.22414437</v>
       </c>
       <c r="AN24" s="3">
-        <v>0.5658631920814514</v>
+        <v>0.2897435</v>
       </c>
       <c r="AO24" s="3">
-        <v>0.09989243745803833</v>
+        <v>0.03194589</v>
       </c>
       <c r="AP24" s="3">
-        <v>0.7679430246353149</v>
+        <v>0.65793216</v>
       </c>
       <c r="AQ24" s="3">
-        <v>0.9997621774673462</v>
+        <v>0.9988958</v>
       </c>
       <c r="AR24" s="3">
-        <v>0.7646519541740417</v>
+        <v>0.8549616</v>
       </c>
       <c r="AS24" s="3">
-        <v>0.967028021812439</v>
+        <v>0.8917742</v>
       </c>
       <c r="AT24" s="3">
-        <v>0.6451166272163391</v>
+        <v>0.54440176</v>
       </c>
       <c r="AU24" s="3">
-        <v>-4.58236026763916</v>
+        <v>-4.5918508</v>
       </c>
       <c r="AV24" s="3">
-        <v>95.09494018554688</v>
+        <v>92.46042</v>
       </c>
       <c r="AW24" s="3">
-        <v>8.923327445983887</v>
+        <v>9.764013</v>
       </c>
       <c r="AX24" s="3">
-        <v>353.4660000000002</v>
+        <v>389.4990000000001</v>
       </c>
       <c r="AY24" s="3">
-        <v>3.290300000000002</v>
+        <v>2.681100000000002</v>
       </c>
       <c r="AZ24" s="3">
-        <v>0.7270065061949308</v>
+        <v>0.8204014514733262</v>
       </c>
       <c r="BA24" s="3">
         <v>4</v>
       </c>
       <c r="BB24" s="3">
-        <v>3.459755637306095</v>
+        <v>3.349548292628201</v>
       </c>
       <c r="BC24" s="3">
-        <v>0.7266938180771005</v>
+        <v>0.7389390785968666</v>
       </c>
       <c r="BD24" s="3">
         <v>1</v>
@@ -6336,7 +6260,7 @@
     <row r="25" ht="92" customHeight="1">
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>O=[N+]([O-])c1cc(F)cc(CN2CC3(CCN(c4cncc(Cl)c4)C3)C2)c1</t>
+          <t>C=CCOCC#Cc1cncc(N2CCC3(CN(Cc4cc(N)cc([N+](=O)[O-])c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -6348,10 +6272,10 @@
         <v>1</v>
       </c>
       <c r="E25" s="3">
-        <v>0.5495495495495496</v>
+        <v>0.6101694915254238</v>
       </c>
       <c r="F25" s="3">
-        <v>9.880000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G25" s="3">
         <v>5</v>
@@ -6362,55 +6286,55 @@
         </is>
       </c>
       <c r="I25" s="3">
-        <v>0.6051538968907209</v>
+        <v>0.605153896890721</v>
       </c>
       <c r="J25" s="3">
-        <v>4.028597666980577</v>
+        <v>4.028597666980578</v>
       </c>
       <c r="K25" s="3">
         <v>5.394846103109279</v>
       </c>
       <c r="L25" s="3">
-        <v>1.056317392714866</v>
+        <v>1.02219781688997</v>
       </c>
       <c r="M25" s="3">
-        <v>0.4098909832966713</v>
+        <v>0.5213612527927117</v>
       </c>
       <c r="N25" s="3">
-        <v>16.68169616968234</v>
+        <v>17.70183678414323</v>
       </c>
       <c r="O25" s="3">
-        <v>12.29164682923438</v>
+        <v>12.91837547033532</v>
       </c>
       <c r="P25" s="3">
-        <v>4.943682607285134</v>
+        <v>4.977802183110031</v>
       </c>
       <c r="Q25" s="3">
-        <v>0.4098909832966713</v>
+        <v>0.5213612527927117</v>
       </c>
       <c r="R25" s="3">
-        <v>1.790321657914636</v>
+        <v>1.000759592065358</v>
       </c>
       <c r="S25" s="3">
-        <v>72.39419111851227</v>
+        <v>110.6791645776479</v>
       </c>
       <c r="T25" s="3">
-        <v>4.140296280023659</v>
+        <v>3.955934127636316</v>
       </c>
       <c r="U25" s="3">
-        <v>5.747068934546609</v>
+        <v>5.999670238583746</v>
       </c>
       <c r="V25" s="3">
-        <v>0.4098909832966713</v>
+        <v>0.5213612527927117</v>
       </c>
       <c r="W25" s="3">
-        <v>3.494600000000002</v>
+        <v>2.838400000000001</v>
       </c>
       <c r="X25" s="3">
-        <v>-5.005804429618419</v>
+        <v>-4.846837433728133</v>
       </c>
       <c r="Y25" s="3">
-        <v>9.867237245062414E-06</v>
+        <v>1.422861296697028E-05</v>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
@@ -6418,94 +6342,94 @@
         </is>
       </c>
       <c r="AA25" s="3">
-        <v>44.20107269287109</v>
+        <v>26.041409</v>
       </c>
       <c r="AB25" s="3">
-        <v>49.48383331298828</v>
+        <v>22.022608</v>
       </c>
       <c r="AC25" s="3">
-        <v>41.97674179077148</v>
+        <v>40.02241</v>
       </c>
       <c r="AD25" s="3">
         <v>0</v>
       </c>
       <c r="AE25" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AF25" s="3">
         <v>0</v>
       </c>
       <c r="AG25" s="3">
-        <v>0.3734830021858215</v>
+        <v>0.5326417</v>
       </c>
       <c r="AH25" s="3">
-        <v>0.5763952732086182</v>
+        <v>0.5765063</v>
       </c>
       <c r="AI25" s="3">
-        <v>0.6303479075431824</v>
+        <v>0.7700569</v>
       </c>
       <c r="AJ25" s="3">
-        <v>0.1771750301122665</v>
+        <v>0.12985083</v>
       </c>
       <c r="AK25" s="3">
-        <v>0.954875648021698</v>
+        <v>0.9637526</v>
       </c>
       <c r="AL25" s="3">
-        <v>0.4509163796901703</v>
+        <v>0.2207165</v>
       </c>
       <c r="AM25" s="3">
-        <v>0.6226360201835632</v>
+        <v>0.62614244</v>
       </c>
       <c r="AN25" s="3">
-        <v>0.4456623196601868</v>
+        <v>0.6694334</v>
       </c>
       <c r="AO25" s="3">
-        <v>0.7572044730186462</v>
+        <v>0.51075876</v>
       </c>
       <c r="AP25" s="3">
-        <v>0.8397065401077271</v>
+        <v>0.9712572</v>
       </c>
       <c r="AQ25" s="3">
-        <v>0.9999772906303406</v>
+        <v>0.9996597</v>
       </c>
       <c r="AR25" s="3">
-        <v>0.8410286903381348</v>
+        <v>0.7218364</v>
       </c>
       <c r="AS25" s="3">
-        <v>0.9607558250427246</v>
+        <v>0.8955619</v>
       </c>
       <c r="AT25" s="3">
-        <v>0.7064048051834106</v>
+        <v>0.8538926</v>
       </c>
       <c r="AU25" s="3">
-        <v>-4.71135425567627</v>
+        <v>-5.0899143</v>
       </c>
       <c r="AV25" s="3">
-        <v>86.04423522949219</v>
+        <v>89.09255</v>
       </c>
       <c r="AW25" s="3">
-        <v>9.752676010131836</v>
+        <v>11.33769</v>
       </c>
       <c r="AX25" s="3">
-        <v>376.8190000000001</v>
+        <v>433.5120000000002</v>
       </c>
       <c r="AY25" s="3">
-        <v>3.494600000000002</v>
+        <v>2.838400000000001</v>
       </c>
       <c r="AZ25" s="3">
-        <v>0.6033991626381087</v>
+        <v>0.1790398587584678</v>
       </c>
       <c r="BA25" s="3">
         <v>4</v>
       </c>
       <c r="BB25" s="3">
-        <v>3.197696943944662</v>
+        <v>3.690009699198642</v>
       </c>
       <c r="BC25" s="3">
-        <v>0.7558114506728154</v>
+        <v>0.7011100334223731</v>
       </c>
       <c r="BD25" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BE25" s="3">
         <v>0</v>
@@ -6517,22 +6441,22 @@
     <row r="26" ht="92" customHeight="1">
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>CC(C)(O)CC(=O)N1CC2(CCN(c3cncc(C#Cc4ccccc4)c3)C2)C1</t>
+          <t>O=[N+]([O-])c1cccc(CN2CC3(CCN(c4cncc(C#CC5CC5)c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
+          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(Cc4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="D26" s="3">
         <v>1</v>
       </c>
       <c r="E26" s="3">
-        <v>0.3969465648854962</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="F26" s="3">
-        <v>9.77</v>
+        <v>6.45</v>
       </c>
       <c r="G26" s="3">
         <v>5</v>
@@ -6543,55 +6467,55 @@
         </is>
       </c>
       <c r="I26" s="3">
-        <v>0.6051538968907209</v>
+        <v>0.605153896890721</v>
       </c>
       <c r="J26" s="3">
-        <v>4.028597666980577</v>
+        <v>4.028597666980578</v>
       </c>
       <c r="K26" s="3">
         <v>5.394846103109279</v>
       </c>
       <c r="L26" s="3">
-        <v>1.071027324227294</v>
+        <v>1.229899653813125</v>
       </c>
       <c r="M26" s="3">
-        <v>0.453485570103045</v>
+        <v>0.5716495724331544</v>
       </c>
       <c r="N26" s="3">
-        <v>17.84268628492911</v>
+        <v>48.23611695647652</v>
       </c>
       <c r="O26" s="3">
-        <v>11.89399715379812</v>
+        <v>75.98525758125187</v>
       </c>
       <c r="P26" s="3">
-        <v>4.928972675772706</v>
+        <v>4.770100346186876</v>
       </c>
       <c r="Q26" s="3">
-        <v>0.453485570103045</v>
+        <v>0.5716495724331544</v>
       </c>
       <c r="R26" s="3">
-        <v>1.521232540661306</v>
+        <v>1.286667975843005</v>
       </c>
       <c r="S26" s="3">
-        <v>91.17148772678067</v>
+        <v>224.0437410182128</v>
       </c>
       <c r="T26" s="3">
-        <v>4.040140958370738</v>
+        <v>3.649667184217893</v>
       </c>
       <c r="U26" s="3">
-        <v>5.817804393174674</v>
+        <v>5.890533508155858</v>
       </c>
       <c r="V26" s="3">
-        <v>0.453485570103045</v>
+        <v>0.5716495724331544</v>
       </c>
       <c r="W26" s="3">
-        <v>2.681100000000002</v>
+        <v>3.463600000000002</v>
       </c>
       <c r="X26" s="3">
-        <v>-4.469416891183609</v>
+        <v>-5.03952613977687</v>
       </c>
       <c r="Y26" s="3">
-        <v>3.39299413402709E-05</v>
+        <v>9.130064806370084E-06</v>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
@@ -6599,94 +6523,94 @@
         </is>
       </c>
       <c r="AA26" s="3">
-        <v>16.76943397521973</v>
+        <v>31.044586</v>
       </c>
       <c r="AB26" s="3">
-        <v>33.80720520019531</v>
+        <v>33.906563</v>
       </c>
       <c r="AC26" s="3">
-        <v>41.89714431762695</v>
+        <v>44.778027</v>
       </c>
       <c r="AD26" s="3">
         <v>0</v>
       </c>
       <c r="AE26" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF26" s="3">
         <v>0</v>
       </c>
       <c r="AG26" s="3">
-        <v>0.2616260945796967</v>
+        <v>0.5036823</v>
       </c>
       <c r="AH26" s="3">
-        <v>0.2681745886802673</v>
+        <v>0.5502492</v>
       </c>
       <c r="AI26" s="3">
-        <v>0.7960621118545532</v>
+        <v>0.66556084</v>
       </c>
       <c r="AJ26" s="3">
-        <v>0.0710165947675705</v>
+        <v>0.14622062</v>
       </c>
       <c r="AK26" s="3">
-        <v>0.6336731910705566</v>
+        <v>0.94503534</v>
       </c>
       <c r="AL26" s="3">
-        <v>0.07451100647449493</v>
+        <v>0.28596717</v>
       </c>
       <c r="AM26" s="3">
-        <v>0.2241443693637848</v>
+        <v>0.6296526</v>
       </c>
       <c r="AN26" s="3">
-        <v>0.2897435128688812</v>
+        <v>0.6005701</v>
       </c>
       <c r="AO26" s="3">
-        <v>0.03194589167833328</v>
+        <v>0.5947238</v>
       </c>
       <c r="AP26" s="3">
-        <v>0.6579321622848511</v>
+        <v>0.9328672</v>
       </c>
       <c r="AQ26" s="3">
-        <v>0.9988958239555359</v>
+        <v>0.9998994</v>
       </c>
       <c r="AR26" s="3">
-        <v>0.8549615740776062</v>
+        <v>0.6961879</v>
       </c>
       <c r="AS26" s="3">
-        <v>0.8917741775512695</v>
+        <v>0.9249900599999999</v>
       </c>
       <c r="AT26" s="3">
-        <v>0.5444017648696899</v>
+        <v>0.87948763</v>
       </c>
       <c r="AU26" s="3">
-        <v>-4.591850757598877</v>
+        <v>-4.779565</v>
       </c>
       <c r="AV26" s="3">
-        <v>92.46041870117188</v>
+        <v>95.791405</v>
       </c>
       <c r="AW26" s="3">
-        <v>9.764013290405273</v>
+        <v>8.270416000000001</v>
       </c>
       <c r="AX26" s="3">
-        <v>389.4990000000001</v>
+        <v>388.4710000000002</v>
       </c>
       <c r="AY26" s="3">
-        <v>2.681100000000002</v>
+        <v>3.463600000000002</v>
       </c>
       <c r="AZ26" s="3">
-        <v>0.8204014514733262</v>
+        <v>0.4559767816251628</v>
       </c>
       <c r="BA26" s="3">
         <v>4</v>
       </c>
       <c r="BB26" s="3">
-        <v>3.349548292628201</v>
+        <v>3.371766324229277</v>
       </c>
       <c r="BC26" s="3">
-        <v>0.7389390785968666</v>
+        <v>0.7364704084189693</v>
       </c>
       <c r="BD26" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BE26" s="3">
         <v>0</v>
@@ -6698,22 +6622,22 @@
     <row r="27" ht="92" customHeight="1">
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>C=CCOCC#Cc1cncc(N2CCC3(CN(Cc4cc(N)cc([N+](=O)[O-])c4)C3)C2)c1</t>
+          <t>O=[N+]([O-])c1cccc(N2CC3(CCN(c4cncc(C#CC5CC5)c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(Cc4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
+          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="D27" s="3">
         <v>1</v>
       </c>
       <c r="E27" s="3">
-        <v>0.6101694915254238</v>
+        <v>0.4435483870967742</v>
       </c>
       <c r="F27" s="3">
-        <v>8.199999999999999</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="G27" s="3">
         <v>5</v>
@@ -6733,46 +6657,46 @@
         <v>5.394846103109279</v>
       </c>
       <c r="L27" s="3">
-        <v>1.022197816889969</v>
+        <v>1.192950724073724</v>
       </c>
       <c r="M27" s="3">
-        <v>0.5213612527927117</v>
+        <v>0.5833828858610765</v>
       </c>
       <c r="N27" s="3">
-        <v>17.70183678414323</v>
+        <v>47.30732291295684</v>
       </c>
       <c r="O27" s="3">
-        <v>12.91837547033532</v>
+        <v>76.42732002187439</v>
       </c>
       <c r="P27" s="3">
-        <v>4.977802183110031</v>
+        <v>4.807049275926276</v>
       </c>
       <c r="Q27" s="3">
-        <v>0.5213612527927117</v>
+        <v>0.5833828858610765</v>
       </c>
       <c r="R27" s="3">
-        <v>1.000759592065358</v>
+        <v>1.120779729803021</v>
       </c>
       <c r="S27" s="3">
-        <v>110.6791645776479</v>
+        <v>216.9607534383089</v>
       </c>
       <c r="T27" s="3">
-        <v>3.955934127636316</v>
+        <v>3.663618819638566</v>
       </c>
       <c r="U27" s="3">
-        <v>5.999670238583746</v>
+        <v>5.950479732213985</v>
       </c>
       <c r="V27" s="3">
-        <v>0.5213612527927117</v>
+        <v>0.5833828858610765</v>
       </c>
       <c r="W27" s="3">
-        <v>2.838400000000001</v>
+        <v>3.468000000000002</v>
       </c>
       <c r="X27" s="3">
-        <v>-4.846837433728133</v>
+        <v>-4.959767326513743</v>
       </c>
       <c r="Y27" s="3">
-        <v>1.422861296697028E-05</v>
+        <v>1.097065792274501E-05</v>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
@@ -6780,94 +6704,94 @@
         </is>
       </c>
       <c r="AA27" s="3">
-        <v>26.04140853881836</v>
+        <v>40.591316</v>
       </c>
       <c r="AB27" s="3">
-        <v>22.02260780334473</v>
+        <v>39.459892</v>
       </c>
       <c r="AC27" s="3">
-        <v>40.02241134643555</v>
+        <v>52.558495</v>
       </c>
       <c r="AD27" s="3">
         <v>0</v>
       </c>
       <c r="AE27" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AF27" s="3">
         <v>0</v>
       </c>
       <c r="AG27" s="3">
-        <v>0.5326417088508606</v>
+        <v>0.47395635</v>
       </c>
       <c r="AH27" s="3">
-        <v>0.5765063166618347</v>
+        <v>0.21846513</v>
       </c>
       <c r="AI27" s="3">
-        <v>0.7700569033622742</v>
+        <v>0.8594055</v>
       </c>
       <c r="AJ27" s="3">
-        <v>0.129850834608078</v>
+        <v>0.10667469</v>
       </c>
       <c r="AK27" s="3">
-        <v>0.9637526273727417</v>
+        <v>0.8168548</v>
       </c>
       <c r="AL27" s="3">
-        <v>0.2207165062427521</v>
+        <v>0.37949526</v>
       </c>
       <c r="AM27" s="3">
-        <v>0.6261424422264099</v>
+        <v>0.7945511</v>
       </c>
       <c r="AN27" s="3">
-        <v>0.6694334149360657</v>
+        <v>0.7989143</v>
       </c>
       <c r="AO27" s="3">
-        <v>0.5107587575912476</v>
+        <v>0.2269319</v>
       </c>
       <c r="AP27" s="3">
-        <v>0.971257209777832</v>
+        <v>0.9279784</v>
       </c>
       <c r="AQ27" s="3">
-        <v>0.9996597170829773</v>
+        <v>0.9999197</v>
       </c>
       <c r="AR27" s="3">
-        <v>0.7218363881111145</v>
+        <v>0.76822734</v>
       </c>
       <c r="AS27" s="3">
-        <v>0.8955618739128113</v>
+        <v>0.96072465</v>
       </c>
       <c r="AT27" s="3">
-        <v>0.8538926243782043</v>
+        <v>0.8529946</v>
       </c>
       <c r="AU27" s="3">
-        <v>-5.089914321899414</v>
+        <v>-4.6578918</v>
       </c>
       <c r="AV27" s="3">
-        <v>89.09255218505859</v>
+        <v>99.10216</v>
       </c>
       <c r="AW27" s="3">
-        <v>11.33769035339355</v>
+        <v>7.2833505</v>
       </c>
       <c r="AX27" s="3">
-        <v>433.5120000000002</v>
+        <v>374.4440000000002</v>
       </c>
       <c r="AY27" s="3">
-        <v>2.838400000000001</v>
+        <v>3.468000000000002</v>
       </c>
       <c r="AZ27" s="3">
-        <v>0.1790398587584679</v>
+        <v>0.4676614626676107</v>
       </c>
       <c r="BA27" s="3">
         <v>4</v>
       </c>
       <c r="BB27" s="3">
-        <v>3.690009699198642</v>
+        <v>3.41131465404356</v>
       </c>
       <c r="BC27" s="3">
-        <v>0.7011100334223731</v>
+        <v>0.7320761495507155</v>
       </c>
       <c r="BD27" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BE27" s="3">
         <v>0</v>
@@ -6879,7 +6803,7 @@
     <row r="28" ht="92" customHeight="1">
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>O=[N+]([O-])c1cccc(CN2CC3(CCN(c4cncc(C#CC5CC5)c4)C3)C2)c1</t>
+          <t>O=[N+]([O-])c1cc(Cl)cc(CN2CC3(CCN(c4cncc(C#CCO)c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -6891,10 +6815,10 @@
         <v>1</v>
       </c>
       <c r="E28" s="3">
-        <v>0.5294117647058824</v>
+        <v>0.6454545454545455</v>
       </c>
       <c r="F28" s="3">
-        <v>6.45</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="G28" s="3">
         <v>5</v>
@@ -6914,46 +6838,46 @@
         <v>5.394846103109279</v>
       </c>
       <c r="L28" s="3">
-        <v>1.229899653813125</v>
+        <v>1.226530873068342</v>
       </c>
       <c r="M28" s="3">
-        <v>0.5716495724331544</v>
+        <v>0.6627873134903723</v>
       </c>
       <c r="N28" s="3">
-        <v>48.23611695647652</v>
+        <v>51.15112772663909</v>
       </c>
       <c r="O28" s="3">
-        <v>75.98525758125187</v>
+        <v>75.01752877430543</v>
       </c>
       <c r="P28" s="3">
-        <v>4.770100346186876</v>
+        <v>4.773469126931658</v>
       </c>
       <c r="Q28" s="3">
-        <v>0.5716495724331544</v>
+        <v>0.6627873134903723</v>
       </c>
       <c r="R28" s="3">
-        <v>1.286667975843005</v>
+        <v>0.8461897076457157</v>
       </c>
       <c r="S28" s="3">
-        <v>224.0437410182127</v>
+        <v>335.4239025481729</v>
       </c>
       <c r="T28" s="3">
-        <v>3.649667184217892</v>
+        <v>3.474405992490528</v>
       </c>
       <c r="U28" s="3">
-        <v>5.890533508155858</v>
+        <v>6.072532261372788</v>
       </c>
       <c r="V28" s="3">
-        <v>0.5716495724331544</v>
+        <v>0.6627873134903723</v>
       </c>
       <c r="W28" s="3">
-        <v>3.463600000000002</v>
+        <v>2.6993</v>
       </c>
       <c r="X28" s="3">
-        <v>-5.03952613977687</v>
+        <v>-4.63408320979371</v>
       </c>
       <c r="Y28" s="3">
-        <v>9.130064806370084E-06</v>
+        <v>2.322291808121153E-05</v>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
@@ -6961,13 +6885,13 @@
         </is>
       </c>
       <c r="AA28" s="3">
-        <v>31.04458618164062</v>
+        <v>19.25222</v>
       </c>
       <c r="AB28" s="3">
-        <v>33.90656280517578</v>
+        <v>18.426123</v>
       </c>
       <c r="AC28" s="3">
-        <v>44.77802658081055</v>
+        <v>54.20034</v>
       </c>
       <c r="AD28" s="3">
         <v>0</v>
@@ -6979,73 +6903,73 @@
         <v>0</v>
       </c>
       <c r="AG28" s="3">
-        <v>0.5036823153495789</v>
+        <v>0.43069807</v>
       </c>
       <c r="AH28" s="3">
-        <v>0.5502492189407349</v>
+        <v>0.52221876</v>
       </c>
       <c r="AI28" s="3">
-        <v>0.6655608415603638</v>
+        <v>0.7640978</v>
       </c>
       <c r="AJ28" s="3">
-        <v>0.1462206244468689</v>
+        <v>0.22649309</v>
       </c>
       <c r="AK28" s="3">
-        <v>0.9450353384017944</v>
+        <v>0.8920779</v>
       </c>
       <c r="AL28" s="3">
-        <v>0.2859671711921692</v>
+        <v>0.1791437</v>
       </c>
       <c r="AM28" s="3">
-        <v>0.6296526193618774</v>
+        <v>0.45671004</v>
       </c>
       <c r="AN28" s="3">
-        <v>0.6005700826644897</v>
+        <v>0.5429973</v>
       </c>
       <c r="AO28" s="3">
-        <v>0.5947238206863403</v>
+        <v>0.43546423</v>
       </c>
       <c r="AP28" s="3">
-        <v>0.9328672289848328</v>
+        <v>0.8428651700000001</v>
       </c>
       <c r="AQ28" s="3">
-        <v>0.9998993873596191</v>
+        <v>0.9978201</v>
       </c>
       <c r="AR28" s="3">
-        <v>0.6961879134178162</v>
+        <v>0.7996895000000001</v>
       </c>
       <c r="AS28" s="3">
-        <v>0.9249900579452515</v>
+        <v>0.81072533</v>
       </c>
       <c r="AT28" s="3">
-        <v>0.8794876337051392</v>
+        <v>0.75153416</v>
       </c>
       <c r="AU28" s="3">
-        <v>-4.77956485748291</v>
+        <v>-4.9804993</v>
       </c>
       <c r="AV28" s="3">
-        <v>95.79140472412109</v>
+        <v>91.262924</v>
       </c>
       <c r="AW28" s="3">
-        <v>8.270416259765625</v>
+        <v>12.055227</v>
       </c>
       <c r="AX28" s="3">
-        <v>388.4710000000002</v>
+        <v>412.8770000000002</v>
       </c>
       <c r="AY28" s="3">
-        <v>3.463600000000002</v>
+        <v>2.6993</v>
       </c>
       <c r="AZ28" s="3">
-        <v>0.4559767816251629</v>
+        <v>0.4720306189535823</v>
       </c>
       <c r="BA28" s="3">
         <v>4</v>
       </c>
       <c r="BB28" s="3">
-        <v>3.371766324229277</v>
+        <v>3.441957861108501</v>
       </c>
       <c r="BC28" s="3">
-        <v>0.7364704084189693</v>
+        <v>0.7286713487657221</v>
       </c>
       <c r="BD28" s="3">
         <v>3</v>
@@ -7060,22 +6984,22 @@
     <row r="29" ht="92" customHeight="1">
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>O=[N+]([O-])c1cccc(N2CC3(CCN(c4cncc(C#CC5CC5)c4)C3)C2)c1</t>
+          <t>C=CCOC(=O)N1CC2(CCN(c3cncc(C#Cc4ccccc4)c3)C2)C1</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
+          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc5c(cc4[N+](=O)[O-])OCO5)C3)C2)c1</t>
         </is>
       </c>
       <c r="D29" s="3">
         <v>1</v>
       </c>
       <c r="E29" s="3">
-        <v>0.4435483870967742</v>
+        <v>0.3893129770992366</v>
       </c>
       <c r="F29" s="3">
-        <v>8.119999999999999</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G29" s="3">
         <v>5</v>
@@ -7086,55 +7010,55 @@
         </is>
       </c>
       <c r="I29" s="3">
-        <v>0.605153896890721</v>
+        <v>0.6269673230267181</v>
       </c>
       <c r="J29" s="3">
-        <v>4.028597666980578</v>
+        <v>4.236110917115642</v>
       </c>
       <c r="K29" s="3">
-        <v>5.394846103109279</v>
+        <v>5.373032676973282</v>
       </c>
       <c r="L29" s="3">
-        <v>1.192950724073724</v>
+        <v>0.8742033556651265</v>
       </c>
       <c r="M29" s="3">
-        <v>0.5833828858610765</v>
+        <v>0.3438296648732025</v>
       </c>
       <c r="N29" s="3">
-        <v>47.30732291295684</v>
+        <v>10.15776370613573</v>
       </c>
       <c r="O29" s="3">
-        <v>76.42732002187439</v>
+        <v>7.669484797807399</v>
       </c>
       <c r="P29" s="3">
-        <v>4.807049275926276</v>
+        <v>5.125796644334874</v>
       </c>
       <c r="Q29" s="3">
-        <v>0.5833828858610765</v>
+        <v>0.3438296648732025</v>
       </c>
       <c r="R29" s="3">
-        <v>1.120779729803021</v>
+        <v>1.585978196598272</v>
       </c>
       <c r="S29" s="3">
-        <v>216.9607534383089</v>
+        <v>35.32722292124513</v>
       </c>
       <c r="T29" s="3">
-        <v>3.663618819638566</v>
+        <v>4.451890501183397</v>
       </c>
       <c r="U29" s="3">
-        <v>5.950479732213985</v>
+        <v>5.799702787486351</v>
       </c>
       <c r="V29" s="3">
-        <v>0.5833828858610765</v>
+        <v>0.3438296648732025</v>
       </c>
       <c r="W29" s="3">
-        <v>3.468000000000003</v>
+        <v>3.316100000000002</v>
       </c>
       <c r="X29" s="3">
-        <v>-4.959767326513743</v>
+        <v>-4.840572534996578</v>
       </c>
       <c r="Y29" s="3">
-        <v>1.097065792274501E-05</v>
+        <v>1.443535487743144E-05</v>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
@@ -7142,94 +7066,94 @@
         </is>
       </c>
       <c r="AA29" s="3">
-        <v>40.59131622314453</v>
+        <v>60.20294</v>
       </c>
       <c r="AB29" s="3">
-        <v>39.45989227294922</v>
+        <v>61.034718</v>
       </c>
       <c r="AC29" s="3">
-        <v>52.55849456787109</v>
+        <v>46.73542</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
       </c>
       <c r="AE29" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF29" s="3">
         <v>0</v>
       </c>
       <c r="AG29" s="3">
-        <v>0.4739563465118408</v>
+        <v>0.20313144</v>
       </c>
       <c r="AH29" s="3">
-        <v>0.2184651345014572</v>
+        <v>0.2511689</v>
       </c>
       <c r="AI29" s="3">
-        <v>0.859405517578125</v>
+        <v>0.8450652400000001</v>
       </c>
       <c r="AJ29" s="3">
-        <v>0.1066746935248375</v>
+        <v>0.1027115</v>
       </c>
       <c r="AK29" s="3">
-        <v>0.8168547749519348</v>
+        <v>0.6776825</v>
       </c>
       <c r="AL29" s="3">
-        <v>0.3794952630996704</v>
+        <v>0.49718076</v>
       </c>
       <c r="AM29" s="3">
-        <v>0.7945510745048523</v>
+        <v>0.5462124</v>
       </c>
       <c r="AN29" s="3">
-        <v>0.7989143133163452</v>
+        <v>0.6626512</v>
       </c>
       <c r="AO29" s="3">
-        <v>0.2269318997859955</v>
+        <v>0.08121007</v>
       </c>
       <c r="AP29" s="3">
-        <v>0.9279783964157104</v>
+        <v>0.86473036</v>
       </c>
       <c r="AQ29" s="3">
-        <v>0.9999197125434875</v>
+        <v>0.9997215</v>
       </c>
       <c r="AR29" s="3">
-        <v>0.7682273387908936</v>
+        <v>0.82279646</v>
       </c>
       <c r="AS29" s="3">
-        <v>0.9607246518135071</v>
+        <v>0.9525008</v>
       </c>
       <c r="AT29" s="3">
-        <v>0.8529946208000183</v>
+        <v>0.68568385</v>
       </c>
       <c r="AU29" s="3">
-        <v>-4.657891750335693</v>
+        <v>-4.631179</v>
       </c>
       <c r="AV29" s="3">
-        <v>99.10215759277344</v>
+        <v>98.99516</v>
       </c>
       <c r="AW29" s="3">
-        <v>7.283350467681885</v>
+        <v>5.8764067</v>
       </c>
       <c r="AX29" s="3">
-        <v>374.4440000000002</v>
+        <v>373.4560000000001</v>
       </c>
       <c r="AY29" s="3">
-        <v>3.468000000000003</v>
+        <v>3.316100000000002</v>
       </c>
       <c r="AZ29" s="3">
-        <v>0.4676614626676108</v>
+        <v>0.6116733295874957</v>
       </c>
       <c r="BA29" s="3">
         <v>4</v>
       </c>
       <c r="BB29" s="3">
-        <v>3.41131465404356</v>
+        <v>3.29505762412903</v>
       </c>
       <c r="BC29" s="3">
-        <v>0.7320761495507155</v>
+        <v>0.7449935973189967</v>
       </c>
       <c r="BD29" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BE29" s="3">
         <v>0</v>
@@ -7241,7 +7165,7 @@
     <row r="30" ht="92" customHeight="1">
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>O=[N+]([O-])c1cc(Cl)cc(CN2CC3(CCN(c4cncc(C#CCO)c4)C3)C2)c1</t>
+          <t>CC#Cc1cncc(N2CCC3(CC2)CN(Cc2cc(N)cc([N+](=O)[O-])c2)C3)c1</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -7253,10 +7177,10 @@
         <v>1</v>
       </c>
       <c r="E30" s="3">
-        <v>0.6454545454545455</v>
+        <v>0.5603448275862069</v>
       </c>
       <c r="F30" s="3">
-        <v>9.640000000000001</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="G30" s="3">
         <v>5</v>
@@ -7267,55 +7191,55 @@
         </is>
       </c>
       <c r="I30" s="3">
-        <v>0.605153896890721</v>
+        <v>0.6957116320978487</v>
       </c>
       <c r="J30" s="3">
-        <v>4.028597666980578</v>
+        <v>4.962626977497846</v>
       </c>
       <c r="K30" s="3">
-        <v>5.394846103109279</v>
+        <v>5.304288367902151</v>
       </c>
       <c r="L30" s="3">
-        <v>1.226530873068342</v>
+        <v>1.182392532757563</v>
       </c>
       <c r="M30" s="3">
-        <v>0.6627873134903723</v>
+        <v>0.7061776806019121</v>
       </c>
       <c r="N30" s="3">
-        <v>51.15112772663909</v>
+        <v>50.38716384411406</v>
       </c>
       <c r="O30" s="3">
-        <v>75.01752877430543</v>
+        <v>75.33898298692728</v>
       </c>
       <c r="P30" s="3">
-        <v>4.773469126931658</v>
+        <v>4.817607467242436</v>
       </c>
       <c r="Q30" s="3">
-        <v>0.6627873134903723</v>
+        <v>0.7061776806019121</v>
       </c>
       <c r="R30" s="3">
-        <v>0.8461897076457157</v>
+        <v>0.628469605370757</v>
       </c>
       <c r="S30" s="3">
-        <v>335.4239025481729</v>
+        <v>368.5537094978305</v>
       </c>
       <c r="T30" s="3">
-        <v>3.474405992490528</v>
+        <v>3.433499213262689</v>
       </c>
       <c r="U30" s="3">
-        <v>6.072532261372788</v>
+        <v>6.201715721222184</v>
       </c>
       <c r="V30" s="3">
-        <v>0.6627873134903723</v>
+        <v>0.7061776806019121</v>
       </c>
       <c r="W30" s="3">
-        <v>2.6993</v>
+        <v>3.045800000000001</v>
       </c>
       <c r="X30" s="3">
-        <v>-4.63408320979371</v>
+        <v>-4.749522872349536</v>
       </c>
       <c r="Y30" s="3">
-        <v>2.322291808121153E-05</v>
+        <v>1.780234149407876E-05</v>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
@@ -7323,94 +7247,94 @@
         </is>
       </c>
       <c r="AA30" s="3">
-        <v>19.25222015380859</v>
+        <v>20.982674</v>
       </c>
       <c r="AB30" s="3">
-        <v>18.42612266540527</v>
+        <v>18.471134</v>
       </c>
       <c r="AC30" s="3">
-        <v>54.20034027099609</v>
+        <v>47.59323</v>
       </c>
       <c r="AD30" s="3">
         <v>0</v>
       </c>
       <c r="AE30" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF30" s="3">
         <v>0</v>
       </c>
       <c r="AG30" s="3">
-        <v>0.4306980669498444</v>
+        <v>0.46245393</v>
       </c>
       <c r="AH30" s="3">
-        <v>0.5222187638282776</v>
+        <v>0.6622716</v>
       </c>
       <c r="AI30" s="3">
-        <v>0.7640978097915649</v>
+        <v>0.73940563</v>
       </c>
       <c r="AJ30" s="3">
-        <v>0.2264930903911591</v>
+        <v>0.09740668</v>
       </c>
       <c r="AK30" s="3">
-        <v>0.8920779228210449</v>
+        <v>0.96325225</v>
       </c>
       <c r="AL30" s="3">
-        <v>0.1791436970233917</v>
+        <v>0.2788904</v>
       </c>
       <c r="AM30" s="3">
-        <v>0.4567100405693054</v>
+        <v>0.43796816</v>
       </c>
       <c r="AN30" s="3">
-        <v>0.5429973006248474</v>
+        <v>0.5160941</v>
       </c>
       <c r="AO30" s="3">
-        <v>0.4354642331600189</v>
+        <v>0.47388944</v>
       </c>
       <c r="AP30" s="3">
-        <v>0.8428651690483093</v>
+        <v>0.9478034</v>
       </c>
       <c r="AQ30" s="3">
-        <v>0.9978200793266296</v>
+        <v>0.9998349</v>
       </c>
       <c r="AR30" s="3">
-        <v>0.7996894717216492</v>
+        <v>0.8220931</v>
       </c>
       <c r="AS30" s="3">
-        <v>0.8107253313064575</v>
+        <v>0.9365412</v>
       </c>
       <c r="AT30" s="3">
-        <v>0.7515341639518738</v>
+        <v>0.8178027</v>
       </c>
       <c r="AU30" s="3">
-        <v>-4.980499267578125</v>
+        <v>-5.0506964</v>
       </c>
       <c r="AV30" s="3">
-        <v>91.26292419433594</v>
+        <v>88.46577499999999</v>
       </c>
       <c r="AW30" s="3">
-        <v>12.05522727966309</v>
+        <v>12.356457</v>
       </c>
       <c r="AX30" s="3">
-        <v>412.8770000000002</v>
+        <v>391.4750000000001</v>
       </c>
       <c r="AY30" s="3">
-        <v>2.6993</v>
+        <v>3.045800000000001</v>
       </c>
       <c r="AZ30" s="3">
-        <v>0.4720306189535823</v>
+        <v>0.3729667366404932</v>
       </c>
       <c r="BA30" s="3">
         <v>4</v>
       </c>
       <c r="BB30" s="3">
-        <v>3.441957861108501</v>
+        <v>3.43255767349124</v>
       </c>
       <c r="BC30" s="3">
-        <v>0.7286713487657221</v>
+        <v>0.729715814056529</v>
       </c>
       <c r="BD30" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BE30" s="3">
         <v>0</v>
@@ -7422,22 +7346,22 @@
     <row r="31" ht="92" customHeight="1">
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>C=CCOC(=O)N1CC2(CCN(c3cncc(C#Cc4ccccc4)c3)C2)C1</t>
+          <t>CCCCCC#Cc1cncc(N2CCC3(CN(C(=O)C4CCOCC4)C3)C2)c1</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc5c(cc4[N+](=O)[O-])OCO5)C3)C2)c1</t>
+          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="D31" s="3">
         <v>1</v>
       </c>
       <c r="E31" s="3">
-        <v>0.3893129770992366</v>
+        <v>0.5327868852459017</v>
       </c>
       <c r="F31" s="3">
-        <v>8.619999999999999</v>
+        <v>9.43</v>
       </c>
       <c r="G31" s="3">
         <v>5</v>
@@ -7448,55 +7372,55 @@
         </is>
       </c>
       <c r="I31" s="3">
-        <v>0.6269673230267181</v>
+        <v>0.6976196075069574</v>
       </c>
       <c r="J31" s="3">
-        <v>4.236110917115642</v>
+        <v>4.984477127902903</v>
       </c>
       <c r="K31" s="3">
-        <v>5.373032676973282</v>
+        <v>5.302380392493043</v>
       </c>
       <c r="L31" s="3">
-        <v>0.8742033556651265</v>
+        <v>0.8953558571396633</v>
       </c>
       <c r="M31" s="3">
-        <v>0.3438296648732025</v>
+        <v>0.1873493021644952</v>
       </c>
       <c r="N31" s="3">
-        <v>10.15776370613573</v>
+        <v>8.599463762035141</v>
       </c>
       <c r="O31" s="3">
-        <v>7.669484797807399</v>
+        <v>3.534988500955276</v>
       </c>
       <c r="P31" s="3">
-        <v>5.125796644334874</v>
+        <v>5.104644142860336</v>
       </c>
       <c r="Q31" s="3">
-        <v>0.3438296648732025</v>
+        <v>0.1873493021644952</v>
       </c>
       <c r="R31" s="3">
-        <v>1.585978196598272</v>
+        <v>3.3740477531375</v>
       </c>
       <c r="S31" s="3">
-        <v>35.32722292124513</v>
+        <v>18.30461038738765</v>
       </c>
       <c r="T31" s="3">
-        <v>4.451890501183397</v>
+        <v>4.737439510617926</v>
       </c>
       <c r="U31" s="3">
-        <v>5.799702787486351</v>
+        <v>5.471848775102748</v>
       </c>
       <c r="V31" s="3">
-        <v>0.3438296648732025</v>
+        <v>0.1873493021644952</v>
       </c>
       <c r="W31" s="3">
-        <v>3.316100000000002</v>
+        <v>3.478700000000003</v>
       </c>
       <c r="X31" s="3">
-        <v>-4.840572534996578</v>
+        <v>-5.005884394500141</v>
       </c>
       <c r="Y31" s="3">
-        <v>1.443535487743144E-05</v>
+        <v>9.865420597934993E-06</v>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
@@ -7504,13 +7428,13 @@
         </is>
       </c>
       <c r="AA31" s="3">
-        <v>60.20294189453125</v>
+        <v>45.217934</v>
       </c>
       <c r="AB31" s="3">
-        <v>61.03471755981445</v>
+        <v>49.328346</v>
       </c>
       <c r="AC31" s="3">
-        <v>46.73542022705078</v>
+        <v>40.188557</v>
       </c>
       <c r="AD31" s="3">
         <v>0</v>
@@ -7522,73 +7446,73 @@
         <v>0</v>
       </c>
       <c r="AG31" s="3">
-        <v>0.2031314373016357</v>
+        <v>0.117601715</v>
       </c>
       <c r="AH31" s="3">
-        <v>0.2511689066886902</v>
+        <v>0.2769882</v>
       </c>
       <c r="AI31" s="3">
-        <v>0.8450652360916138</v>
+        <v>0.6194231</v>
       </c>
       <c r="AJ31" s="3">
-        <v>0.1027114987373352</v>
+        <v>0.040371433</v>
       </c>
       <c r="AK31" s="3">
-        <v>0.6776825189590454</v>
+        <v>0.6872637</v>
       </c>
       <c r="AL31" s="3">
-        <v>0.4971807599067688</v>
+        <v>0.06891922</v>
       </c>
       <c r="AM31" s="3">
-        <v>0.546212375164032</v>
+        <v>0.23162445</v>
       </c>
       <c r="AN31" s="3">
-        <v>0.6626511812210083</v>
+        <v>0.24135622</v>
       </c>
       <c r="AO31" s="3">
-        <v>0.08121006935834885</v>
+        <v>0.03940945</v>
       </c>
       <c r="AP31" s="3">
-        <v>0.8647303581237793</v>
+        <v>0.7943634000000001</v>
       </c>
       <c r="AQ31" s="3">
-        <v>0.9997215270996094</v>
+        <v>0.9999027</v>
       </c>
       <c r="AR31" s="3">
-        <v>0.8227964639663696</v>
+        <v>0.8274047</v>
       </c>
       <c r="AS31" s="3">
-        <v>0.9525008201599121</v>
+        <v>0.96171296</v>
       </c>
       <c r="AT31" s="3">
-        <v>0.6856838464736938</v>
+        <v>0.57263577</v>
       </c>
       <c r="AU31" s="3">
-        <v>-4.631178855895996</v>
+        <v>-4.615781</v>
       </c>
       <c r="AV31" s="3">
-        <v>98.99516296386719</v>
+        <v>93.75774</v>
       </c>
       <c r="AW31" s="3">
-        <v>5.876406669616699</v>
+        <v>10.074145</v>
       </c>
       <c r="AX31" s="3">
-        <v>373.4560000000001</v>
+        <v>395.5470000000003</v>
       </c>
       <c r="AY31" s="3">
-        <v>3.316100000000002</v>
+        <v>3.478700000000003</v>
       </c>
       <c r="AZ31" s="3">
-        <v>0.6116733295874957</v>
+        <v>0.5656513031600198</v>
       </c>
       <c r="BA31" s="3">
         <v>4</v>
       </c>
       <c r="BB31" s="3">
-        <v>3.29505762412903</v>
+        <v>3.398238871561463</v>
       </c>
       <c r="BC31" s="3">
-        <v>0.7449935973189967</v>
+        <v>0.7335290142709485</v>
       </c>
       <c r="BD31" s="3">
         <v>2</v>
@@ -7603,22 +7527,22 @@
     <row r="32" ht="92" customHeight="1">
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>CC#Cc1cncc(N2CCC3(CC2)CN(Cc2cc(N)cc([N+](=O)[O-])c2)C3)c1</t>
+          <t>COc1cc2[nH]ncc2cc1C(=O)N1CC2(CCN(c3cncc(C#CC4CC4)c3)C2)C1</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(Cc4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
+          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc5c(cc4[N+](=O)[O-])OCO5)C3)C2)c1</t>
         </is>
       </c>
       <c r="D32" s="3">
         <v>1</v>
       </c>
       <c r="E32" s="3">
-        <v>0.5603448275862069</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="F32" s="3">
-        <v>9.949999999999999</v>
+        <v>9.01</v>
       </c>
       <c r="G32" s="3">
         <v>5</v>
@@ -7629,55 +7553,55 @@
         </is>
       </c>
       <c r="I32" s="3">
-        <v>0.6957116320978487</v>
+        <v>0.6976196075069575</v>
       </c>
       <c r="J32" s="3">
-        <v>4.962626977497846</v>
+        <v>4.984477127902903</v>
       </c>
       <c r="K32" s="3">
-        <v>5.304288367902151</v>
+        <v>5.302380392493043</v>
       </c>
       <c r="L32" s="3">
-        <v>1.182392532757563</v>
+        <v>1.219938036588334</v>
       </c>
       <c r="M32" s="3">
-        <v>0.7061776806019121</v>
+        <v>0.3677264463853308</v>
       </c>
       <c r="N32" s="3">
-        <v>50.38716384411406</v>
+        <v>22.34409214041806</v>
       </c>
       <c r="O32" s="3">
-        <v>75.33898298692728</v>
+        <v>14.0908323934721</v>
       </c>
       <c r="P32" s="3">
-        <v>4.817607467242436</v>
+        <v>4.780061963411666</v>
       </c>
       <c r="Q32" s="3">
-        <v>0.7061776806019121</v>
+        <v>0.3677264463853308</v>
       </c>
       <c r="R32" s="3">
-        <v>0.628469605370757</v>
+        <v>3.156415749265656</v>
       </c>
       <c r="S32" s="3">
-        <v>368.5537094978305</v>
+        <v>87.23321353587414</v>
       </c>
       <c r="T32" s="3">
-        <v>3.433499213262689</v>
+        <v>4.059318128496417</v>
       </c>
       <c r="U32" s="3">
-        <v>6.201715721222184</v>
+        <v>5.500805798326915</v>
       </c>
       <c r="V32" s="3">
-        <v>0.7061776806019121</v>
+        <v>0.3677264463853308</v>
       </c>
       <c r="W32" s="3">
-        <v>3.045800000000001</v>
+        <v>3.080500000000002</v>
       </c>
       <c r="X32" s="3">
-        <v>-4.749522872349536</v>
+        <v>-5.040453903585137</v>
       </c>
       <c r="Y32" s="3">
-        <v>1.780234149407876E-05</v>
+        <v>9.1105814768203E-06</v>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
@@ -7685,94 +7609,94 @@
         </is>
       </c>
       <c r="AA32" s="3">
-        <v>20.98267364501953</v>
+        <v>31.945576</v>
       </c>
       <c r="AB32" s="3">
-        <v>18.47113418579102</v>
+        <v>25.616272</v>
       </c>
       <c r="AC32" s="3">
-        <v>47.59323120117188</v>
+        <v>50.804012</v>
       </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
       <c r="AE32" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AF32" s="3">
         <v>0</v>
       </c>
       <c r="AG32" s="3">
-        <v>0.4624539315700531</v>
+        <v>0.11818117</v>
       </c>
       <c r="AH32" s="3">
-        <v>0.6622716188430786</v>
+        <v>0.28831378</v>
       </c>
       <c r="AI32" s="3">
-        <v>0.739405632019043</v>
+        <v>0.8626954999999999</v>
       </c>
       <c r="AJ32" s="3">
-        <v>0.09740667790174484</v>
+        <v>0.029384658</v>
       </c>
       <c r="AK32" s="3">
-        <v>0.9632522463798523</v>
+        <v>0.79312974</v>
       </c>
       <c r="AL32" s="3">
-        <v>0.2788904011249542</v>
+        <v>0.1443173</v>
       </c>
       <c r="AM32" s="3">
-        <v>0.4379681646823883</v>
+        <v>0.4411754</v>
       </c>
       <c r="AN32" s="3">
-        <v>0.5160940885543823</v>
+        <v>0.63680875</v>
       </c>
       <c r="AO32" s="3">
-        <v>0.4738894402980804</v>
+        <v>0.0775267</v>
       </c>
       <c r="AP32" s="3">
-        <v>0.9478033781051636</v>
+        <v>0.958148</v>
       </c>
       <c r="AQ32" s="3">
-        <v>0.9998348951339722</v>
+        <v>0.9999772300000001</v>
       </c>
       <c r="AR32" s="3">
-        <v>0.82209312915802</v>
+        <v>0.76773345</v>
       </c>
       <c r="AS32" s="3">
-        <v>0.9365411996841431</v>
+        <v>0.91656953</v>
       </c>
       <c r="AT32" s="3">
-        <v>0.8178027272224426</v>
+        <v>0.59797406</v>
       </c>
       <c r="AU32" s="3">
-        <v>-5.05069637298584</v>
+        <v>-5.045365</v>
       </c>
       <c r="AV32" s="3">
-        <v>88.46577453613281</v>
+        <v>96.46507</v>
       </c>
       <c r="AW32" s="3">
-        <v>12.3564567565918</v>
+        <v>7.689546</v>
       </c>
       <c r="AX32" s="3">
-        <v>391.4750000000001</v>
+        <v>427.5080000000003</v>
       </c>
       <c r="AY32" s="3">
-        <v>3.045800000000001</v>
+        <v>3.080500000000002</v>
       </c>
       <c r="AZ32" s="3">
-        <v>0.3729667366404932</v>
+        <v>0.6505517843454918</v>
       </c>
       <c r="BA32" s="3">
         <v>4</v>
       </c>
       <c r="BB32" s="3">
-        <v>3.43255767349124</v>
+        <v>3.580375515656432</v>
       </c>
       <c r="BC32" s="3">
-        <v>0.729715814056529</v>
+        <v>0.7132916093715076</v>
       </c>
       <c r="BD32" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BE32" s="3">
         <v>0</v>
@@ -7784,22 +7708,22 @@
     <row r="33" ht="92" customHeight="1">
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>CCCCCC#Cc1cncc(N2CCC3(CN(C(=O)C4CCOCC4)C3)C2)c1</t>
+          <t>O=[N+]([O-])c1cc(Cl)cc(CN2CC3(CCN(c4cncc(C#CCCO)c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
+          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(Cc4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="D33" s="3">
         <v>1</v>
       </c>
       <c r="E33" s="3">
-        <v>0.5327868852459017</v>
+        <v>0.6727272727272727</v>
       </c>
       <c r="F33" s="3">
-        <v>9.43</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="G33" s="3">
         <v>5</v>
@@ -7810,7 +7734,7 @@
         </is>
       </c>
       <c r="I33" s="3">
-        <v>0.6976196075069574</v>
+        <v>0.6976196075069575</v>
       </c>
       <c r="J33" s="3">
         <v>4.984477127902903</v>
@@ -7819,46 +7743,46 @@
         <v>5.302380392493043</v>
       </c>
       <c r="L33" s="3">
-        <v>0.8953558571396633</v>
+        <v>1.06226083109585</v>
       </c>
       <c r="M33" s="3">
-        <v>0.1873493021644952</v>
+        <v>0.4125988265036419</v>
       </c>
       <c r="N33" s="3">
-        <v>8.599463762035141</v>
+        <v>16.558585056522</v>
       </c>
       <c r="O33" s="3">
-        <v>3.534988500955275</v>
+        <v>11.21335080786132</v>
       </c>
       <c r="P33" s="3">
-        <v>5.104644142860336</v>
+        <v>4.937739168904151</v>
       </c>
       <c r="Q33" s="3">
-        <v>0.1873493021644952</v>
+        <v>0.4125988265036419</v>
       </c>
       <c r="R33" s="3">
-        <v>3.3740477531375</v>
+        <v>1.792945675851465</v>
       </c>
       <c r="S33" s="3">
-        <v>18.30461038738765</v>
+        <v>74.29413507311568</v>
       </c>
       <c r="T33" s="3">
-        <v>4.737439510617926</v>
+        <v>4.129045468957012</v>
       </c>
       <c r="U33" s="3">
-        <v>5.471848775102748</v>
+        <v>5.746432868851288</v>
       </c>
       <c r="V33" s="3">
-        <v>0.1873493021644952</v>
+        <v>0.4125988265036419</v>
       </c>
       <c r="W33" s="3">
-        <v>3.478700000000003</v>
+        <v>3.089400000000001</v>
       </c>
       <c r="X33" s="3">
-        <v>-5.005884394500141</v>
+        <v>-5.006852346422233</v>
       </c>
       <c r="Y33" s="3">
-        <v>9.865420597934993E-06</v>
+        <v>9.84345711582429E-06</v>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
@@ -7866,94 +7790,94 @@
         </is>
       </c>
       <c r="AA33" s="3">
-        <v>45.21793365478516</v>
+        <v>23.244576</v>
       </c>
       <c r="AB33" s="3">
-        <v>49.32834625244141</v>
+        <v>29.92458</v>
       </c>
       <c r="AC33" s="3">
-        <v>40.18855667114258</v>
+        <v>50.81125</v>
       </c>
       <c r="AD33" s="3">
         <v>0</v>
       </c>
       <c r="AE33" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF33" s="3">
         <v>0</v>
       </c>
       <c r="AG33" s="3">
-        <v>0.117601715028286</v>
+        <v>0.5003911</v>
       </c>
       <c r="AH33" s="3">
-        <v>0.2769882082939148</v>
+        <v>0.5445336</v>
       </c>
       <c r="AI33" s="3">
-        <v>0.6194230914115906</v>
+        <v>0.73466825</v>
       </c>
       <c r="AJ33" s="3">
-        <v>0.04037143290042877</v>
+        <v>0.20745921</v>
       </c>
       <c r="AK33" s="3">
-        <v>0.6872637271881104</v>
+        <v>0.91319907</v>
       </c>
       <c r="AL33" s="3">
-        <v>0.06891921907663345</v>
+        <v>0.18178257</v>
       </c>
       <c r="AM33" s="3">
-        <v>0.2316244542598724</v>
+        <v>0.46289325</v>
       </c>
       <c r="AN33" s="3">
-        <v>0.24135622382164</v>
+        <v>0.50498104</v>
       </c>
       <c r="AO33" s="3">
-        <v>0.03940945118665695</v>
+        <v>0.46681458</v>
       </c>
       <c r="AP33" s="3">
-        <v>0.7943633794784546</v>
+        <v>0.8825364</v>
       </c>
       <c r="AQ33" s="3">
-        <v>0.9999027252197266</v>
+        <v>0.9983719</v>
       </c>
       <c r="AR33" s="3">
-        <v>0.8274046778678894</v>
+        <v>0.7647208</v>
       </c>
       <c r="AS33" s="3">
-        <v>0.9617129564285278</v>
+        <v>0.8417557</v>
       </c>
       <c r="AT33" s="3">
-        <v>0.5726357698440552</v>
+        <v>0.79578036</v>
       </c>
       <c r="AU33" s="3">
-        <v>-4.615780830383301</v>
+        <v>-5.010187</v>
       </c>
       <c r="AV33" s="3">
-        <v>93.75773620605469</v>
+        <v>92.98042</v>
       </c>
       <c r="AW33" s="3">
-        <v>10.07414531707764</v>
+        <v>12.466297</v>
       </c>
       <c r="AX33" s="3">
-        <v>395.5470000000003</v>
+        <v>426.9040000000002</v>
       </c>
       <c r="AY33" s="3">
-        <v>3.478700000000003</v>
+        <v>3.089400000000001</v>
       </c>
       <c r="AZ33" s="3">
-        <v>0.5656513031600198</v>
+        <v>0.4491484300349904</v>
       </c>
       <c r="BA33" s="3">
         <v>4</v>
       </c>
       <c r="BB33" s="3">
-        <v>3.398238871561463</v>
+        <v>3.467582352526327</v>
       </c>
       <c r="BC33" s="3">
-        <v>0.7335290142709485</v>
+        <v>0.7258241830526304</v>
       </c>
       <c r="BD33" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BE33" s="3">
         <v>0</v>
@@ -7965,22 +7889,22 @@
     <row r="34" ht="92" customHeight="1">
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>COc1cc2[nH]ncc2cc1C(=O)N1CC2(CCN(c3cncc(C#CC4CC4)c3)C2)C1</t>
+          <t>CC(=O)Nc1cc(CN2CC3(CCN(c4cncc(C#CCCCCO)c4)C3)C2)cc([N+](=O)[O-])c1</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc5c(cc4[N+](=O)[O-])OCO5)C3)C2)c1</t>
+          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(Cc4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="D34" s="3">
         <v>1</v>
       </c>
       <c r="E34" s="3">
-        <v>0.4444444444444444</v>
+        <v>0.7068965517241379</v>
       </c>
       <c r="F34" s="3">
-        <v>9.01</v>
+        <v>8.76</v>
       </c>
       <c r="G34" s="3">
         <v>5</v>
@@ -8000,46 +7924,46 @@
         <v>5.302380392493043</v>
       </c>
       <c r="L34" s="3">
-        <v>1.219938036588334</v>
+        <v>1.213489947315162</v>
       </c>
       <c r="M34" s="3">
-        <v>0.3677264463853309</v>
+        <v>0.6408203128000844</v>
       </c>
       <c r="N34" s="3">
-        <v>22.34409214041806</v>
+        <v>49.74693099819075</v>
       </c>
       <c r="O34" s="3">
-        <v>14.0908323934721</v>
+        <v>75.50182551945244</v>
       </c>
       <c r="P34" s="3">
-        <v>4.780061963411666</v>
+        <v>4.786510052684839</v>
       </c>
       <c r="Q34" s="3">
-        <v>0.3677264463853309</v>
+        <v>0.6408203128000844</v>
       </c>
       <c r="R34" s="3">
-        <v>3.156415749265656</v>
+        <v>0.9067386628888348</v>
       </c>
       <c r="S34" s="3">
-        <v>87.23321353587414</v>
+        <v>294.7798275178673</v>
       </c>
       <c r="T34" s="3">
-        <v>4.059318128496417</v>
+        <v>3.530502239596673</v>
       </c>
       <c r="U34" s="3">
-        <v>5.500805798326915</v>
+        <v>6.042517865773004</v>
       </c>
       <c r="V34" s="3">
-        <v>0.3677264463853309</v>
+        <v>0.6408203128000844</v>
       </c>
       <c r="W34" s="3">
-        <v>3.080500000000002</v>
+        <v>3.174600000000002</v>
       </c>
       <c r="X34" s="3">
-        <v>-5.040453903585137</v>
+        <v>-5.370397295311915</v>
       </c>
       <c r="Y34" s="3">
-        <v>9.1105814768203E-06</v>
+        <v>4.261894596277298E-06</v>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
@@ -8047,94 +7971,94 @@
         </is>
       </c>
       <c r="AA34" s="3">
-        <v>31.94557571411133</v>
+        <v>19.360205</v>
       </c>
       <c r="AB34" s="3">
-        <v>25.61627197265625</v>
+        <v>24.128887</v>
       </c>
       <c r="AC34" s="3">
-        <v>50.80401229858398</v>
+        <v>41.917274</v>
       </c>
       <c r="AD34" s="3">
         <v>0</v>
       </c>
       <c r="AE34" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AF34" s="3">
         <v>0</v>
       </c>
       <c r="AG34" s="3">
-        <v>0.1181811690330505</v>
+        <v>0.48455563</v>
       </c>
       <c r="AH34" s="3">
-        <v>0.2883137762546539</v>
+        <v>0.5641221</v>
       </c>
       <c r="AI34" s="3">
-        <v>0.8626955151557922</v>
+        <v>0.77562433</v>
       </c>
       <c r="AJ34" s="3">
-        <v>0.02938465774059296</v>
+        <v>0.16926353</v>
       </c>
       <c r="AK34" s="3">
-        <v>0.7931297421455383</v>
+        <v>0.93693984</v>
       </c>
       <c r="AL34" s="3">
-        <v>0.1443172991275787</v>
+        <v>0.08385519</v>
       </c>
       <c r="AM34" s="3">
-        <v>0.4411754012107849</v>
+        <v>0.4842155</v>
       </c>
       <c r="AN34" s="3">
-        <v>0.6368087530136108</v>
+        <v>0.58984864</v>
       </c>
       <c r="AO34" s="3">
-        <v>0.07752670347690582</v>
+        <v>0.4257349</v>
       </c>
       <c r="AP34" s="3">
-        <v>0.9581480026245117</v>
+        <v>0.9308893</v>
       </c>
       <c r="AQ34" s="3">
-        <v>0.9999772310256958</v>
+        <v>0.9982343</v>
       </c>
       <c r="AR34" s="3">
-        <v>0.7677334547042847</v>
+        <v>0.72059023</v>
       </c>
       <c r="AS34" s="3">
-        <v>0.9165695309638977</v>
+        <v>0.7928723</v>
       </c>
       <c r="AT34" s="3">
-        <v>0.5979740619659424</v>
+        <v>0.8762406</v>
       </c>
       <c r="AU34" s="3">
-        <v>-5.045364856719971</v>
+        <v>-5.3400598</v>
       </c>
       <c r="AV34" s="3">
-        <v>96.46507263183594</v>
+        <v>89.52366000000001</v>
       </c>
       <c r="AW34" s="3">
-        <v>7.68954610824585</v>
+        <v>11.357931</v>
       </c>
       <c r="AX34" s="3">
-        <v>427.5080000000003</v>
+        <v>477.5650000000003</v>
       </c>
       <c r="AY34" s="3">
-        <v>3.080500000000002</v>
+        <v>3.174600000000002</v>
       </c>
       <c r="AZ34" s="3">
-        <v>0.6505517843454918</v>
+        <v>0.2599232630531107</v>
       </c>
       <c r="BA34" s="3">
         <v>4</v>
       </c>
       <c r="BB34" s="3">
-        <v>3.580375515656432</v>
+        <v>3.492189161680715</v>
       </c>
       <c r="BC34" s="3">
-        <v>0.7132916093715076</v>
+        <v>0.7230900931465872</v>
       </c>
       <c r="BD34" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BE34" s="3">
         <v>0</v>
@@ -8146,22 +8070,22 @@
     <row r="35" ht="92" customHeight="1">
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>O=[N+]([O-])c1cc(Cl)cc(CN2CC3(CCN(c4cncc(C#CCCO)c4)C3)C2)c1</t>
+          <t>CCCCCC#Cc1cncc(N2CC3(CN(C(=O)c4cc(N)cc([N+](=O)[O-])c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(Cc4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
+          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="D35" s="3">
         <v>1</v>
       </c>
       <c r="E35" s="3">
-        <v>0.6727272727272727</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="F35" s="3">
-        <v>9.859999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="G35" s="3">
         <v>5</v>
@@ -8181,46 +8105,46 @@
         <v>5.302380392493043</v>
       </c>
       <c r="L35" s="3">
-        <v>1.062260831095849</v>
+        <v>1.124907977073436</v>
       </c>
       <c r="M35" s="3">
-        <v>0.4125988265036419</v>
+        <v>0.6624425040785792</v>
       </c>
       <c r="N35" s="3">
-        <v>16.558585056522</v>
+        <v>47.16277928658973</v>
       </c>
       <c r="O35" s="3">
-        <v>11.21335080786132</v>
+        <v>76.6162216468185</v>
       </c>
       <c r="P35" s="3">
-        <v>4.937739168904151</v>
+        <v>4.875092022926564</v>
       </c>
       <c r="Q35" s="3">
-        <v>0.4125988265036419</v>
+        <v>0.6624425040785792</v>
       </c>
       <c r="R35" s="3">
-        <v>1.792945675851465</v>
+        <v>0.6706882055465081</v>
       </c>
       <c r="S35" s="3">
-        <v>74.29413507311568</v>
+        <v>265.0301516483987</v>
       </c>
       <c r="T35" s="3">
-        <v>4.129045468957012</v>
+        <v>3.576704714932549</v>
       </c>
       <c r="U35" s="3">
-        <v>5.746432868851288</v>
+        <v>6.173479330920579</v>
       </c>
       <c r="V35" s="3">
-        <v>0.4125988265036419</v>
+        <v>0.6624425040785792</v>
       </c>
       <c r="W35" s="3">
-        <v>3.089400000000001</v>
+        <v>3.466200000000001</v>
       </c>
       <c r="X35" s="3">
-        <v>-5.006852346422233</v>
+        <v>-5.315911886573709</v>
       </c>
       <c r="Y35" s="3">
-        <v>9.84345711582429E-06</v>
+        <v>4.831568191366663E-06</v>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
@@ -8228,94 +8152,94 @@
         </is>
       </c>
       <c r="AA35" s="3">
-        <v>23.24457550048828</v>
+        <v>43.044075</v>
       </c>
       <c r="AB35" s="3">
-        <v>29.92457962036133</v>
+        <v>36.494442</v>
       </c>
       <c r="AC35" s="3">
-        <v>50.81124877929688</v>
+        <v>46.336185</v>
       </c>
       <c r="AD35" s="3">
         <v>0</v>
       </c>
       <c r="AE35" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF35" s="3">
         <v>0</v>
       </c>
       <c r="AG35" s="3">
-        <v>0.5003911256790161</v>
+        <v>0.30792525</v>
       </c>
       <c r="AH35" s="3">
-        <v>0.5445336103439331</v>
+        <v>0.13168208</v>
       </c>
       <c r="AI35" s="3">
-        <v>0.7346682548522949</v>
+        <v>0.96059144</v>
       </c>
       <c r="AJ35" s="3">
-        <v>0.2074592113494873</v>
+        <v>0.111994386</v>
       </c>
       <c r="AK35" s="3">
-        <v>0.9131990671157837</v>
+        <v>0.7882549</v>
       </c>
       <c r="AL35" s="3">
-        <v>0.1817825734615326</v>
+        <v>0.11986522</v>
       </c>
       <c r="AM35" s="3">
-        <v>0.4628932476043701</v>
+        <v>0.79162675</v>
       </c>
       <c r="AN35" s="3">
-        <v>0.5049810409545898</v>
+        <v>0.8817321</v>
       </c>
       <c r="AO35" s="3">
-        <v>0.4668145775794983</v>
+        <v>0.099365495</v>
       </c>
       <c r="AP35" s="3">
-        <v>0.8825364112854004</v>
+        <v>0.92478675</v>
       </c>
       <c r="AQ35" s="3">
-        <v>0.9983718991279602</v>
+        <v>0.9994672</v>
       </c>
       <c r="AR35" s="3">
-        <v>0.7647207975387573</v>
+        <v>0.76791435</v>
       </c>
       <c r="AS35" s="3">
-        <v>0.8417556881904602</v>
+        <v>0.93173516</v>
       </c>
       <c r="AT35" s="3">
-        <v>0.7957803606987</v>
+        <v>0.8923608</v>
       </c>
       <c r="AU35" s="3">
-        <v>-5.010187149047852</v>
+        <v>-4.8423815</v>
       </c>
       <c r="AV35" s="3">
-        <v>92.98042297363281</v>
+        <v>99.70733</v>
       </c>
       <c r="AW35" s="3">
-        <v>12.4662971496582</v>
+        <v>6.8345594</v>
       </c>
       <c r="AX35" s="3">
-        <v>426.9040000000002</v>
+        <v>433.5120000000002</v>
       </c>
       <c r="AY35" s="3">
-        <v>3.089400000000001</v>
+        <v>3.466200000000001</v>
       </c>
       <c r="AZ35" s="3">
-        <v>0.4491484300349904</v>
+        <v>0.2458526377153969</v>
       </c>
       <c r="BA35" s="3">
         <v>4</v>
       </c>
       <c r="BB35" s="3">
-        <v>3.467582352526327</v>
+        <v>3.423066196202072</v>
       </c>
       <c r="BC35" s="3">
-        <v>0.7258241830526304</v>
+        <v>0.7307704226442142</v>
       </c>
       <c r="BD35" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BE35" s="3">
         <v>0</v>
@@ -8327,7 +8251,7 @@
     <row r="36" ht="92" customHeight="1">
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>CC(=O)Nc1cc(CN2CC3(CCN(c4cncc(C#CCCCCO)c4)C3)C2)cc([N+](=O)[O-])c1</t>
+          <t>CCCCCC#Cc1cncc(N2CC3(CN(Cc4cc(C(N)=O)cc([N+](=O)[O-])c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -8339,10 +8263,10 @@
         <v>1</v>
       </c>
       <c r="E36" s="3">
-        <v>0.7068965517241379</v>
+        <v>0.7053571428571429</v>
       </c>
       <c r="F36" s="3">
-        <v>8.76</v>
+        <v>9.67</v>
       </c>
       <c r="G36" s="3">
         <v>5</v>
@@ -8362,46 +8286,46 @@
         <v>5.302380392493043</v>
       </c>
       <c r="L36" s="3">
-        <v>1.213489947315162</v>
+        <v>1.151794561238185</v>
       </c>
       <c r="M36" s="3">
-        <v>0.6408203128000844</v>
+        <v>0.7005664127115778</v>
       </c>
       <c r="N36" s="3">
-        <v>49.74693099819075</v>
+        <v>48.98484068669714</v>
       </c>
       <c r="O36" s="3">
-        <v>75.50182551945244</v>
+        <v>75.88300062150282</v>
       </c>
       <c r="P36" s="3">
-        <v>4.786510052684839</v>
+        <v>4.848205438761815</v>
       </c>
       <c r="Q36" s="3">
-        <v>0.6408203128000844</v>
+        <v>0.7005664127115778</v>
       </c>
       <c r="R36" s="3">
-        <v>0.9067386628888349</v>
+        <v>0.6007370150989234</v>
       </c>
       <c r="S36" s="3">
-        <v>294.7798275178673</v>
+        <v>334.8919668768408</v>
       </c>
       <c r="T36" s="3">
-        <v>3.530502239596673</v>
+        <v>3.475095269847122</v>
       </c>
       <c r="U36" s="3">
-        <v>6.042517865773004</v>
+        <v>6.221315607676507</v>
       </c>
       <c r="V36" s="3">
-        <v>0.6408203128000844</v>
+        <v>0.7005664127115778</v>
       </c>
       <c r="W36" s="3">
-        <v>3.174600000000002</v>
+        <v>3.342700000000002</v>
       </c>
       <c r="X36" s="3">
-        <v>-5.370397295311915</v>
+        <v>-5.305341292182389</v>
       </c>
       <c r="Y36" s="3">
-        <v>4.261894596277298E-06</v>
+        <v>4.950609920928786E-06</v>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
@@ -8409,13 +8333,13 @@
         </is>
       </c>
       <c r="AA36" s="3">
-        <v>19.36020469665527</v>
+        <v>42.298126</v>
       </c>
       <c r="AB36" s="3">
-        <v>24.12888717651367</v>
+        <v>35.72743</v>
       </c>
       <c r="AC36" s="3">
-        <v>41.91727447509766</v>
+        <v>44.062798</v>
       </c>
       <c r="AD36" s="3">
         <v>0</v>
@@ -8427,73 +8351,73 @@
         <v>0</v>
       </c>
       <c r="AG36" s="3">
-        <v>0.4845556318759918</v>
+        <v>0.34965914</v>
       </c>
       <c r="AH36" s="3">
-        <v>0.5641220808029175</v>
+        <v>0.4067471</v>
       </c>
       <c r="AI36" s="3">
-        <v>0.7756243348121643</v>
+        <v>0.85083884</v>
       </c>
       <c r="AJ36" s="3">
-        <v>0.1692635267972946</v>
+        <v>0.25309736</v>
       </c>
       <c r="AK36" s="3">
-        <v>0.9369398355484009</v>
+        <v>0.8583584</v>
       </c>
       <c r="AL36" s="3">
-        <v>0.08385518938302994</v>
+        <v>0.089677334</v>
       </c>
       <c r="AM36" s="3">
-        <v>0.4842154979705811</v>
+        <v>0.52661836</v>
       </c>
       <c r="AN36" s="3">
-        <v>0.5898486375808716</v>
+        <v>0.5924958</v>
       </c>
       <c r="AO36" s="3">
-        <v>0.4257349073886871</v>
+        <v>0.3018612</v>
       </c>
       <c r="AP36" s="3">
-        <v>0.9308893084526062</v>
+        <v>0.7214672</v>
       </c>
       <c r="AQ36" s="3">
-        <v>0.9982342720031738</v>
+        <v>0.99586517</v>
       </c>
       <c r="AR36" s="3">
-        <v>0.7205902338027954</v>
+        <v>0.7781409</v>
       </c>
       <c r="AS36" s="3">
-        <v>0.7928723096847534</v>
+        <v>0.7356981</v>
       </c>
       <c r="AT36" s="3">
-        <v>0.876240611076355</v>
+        <v>0.7920691</v>
       </c>
       <c r="AU36" s="3">
-        <v>-5.340059757232666</v>
+        <v>-5.0568304</v>
       </c>
       <c r="AV36" s="3">
-        <v>89.52365875244141</v>
+        <v>98.50418999999999</v>
       </c>
       <c r="AW36" s="3">
-        <v>11.35793113708496</v>
+        <v>7.267268</v>
       </c>
       <c r="AX36" s="3">
-        <v>477.5650000000003</v>
+        <v>447.5390000000002</v>
       </c>
       <c r="AY36" s="3">
-        <v>3.174600000000002</v>
+        <v>3.342700000000002</v>
       </c>
       <c r="AZ36" s="3">
-        <v>0.2599232630531108</v>
+        <v>0.2879435993170225</v>
       </c>
       <c r="BA36" s="3">
         <v>4</v>
       </c>
       <c r="BB36" s="3">
-        <v>3.492189161680715</v>
+        <v>3.410029400598416</v>
       </c>
       <c r="BC36" s="3">
-        <v>0.7230900931465872</v>
+        <v>0.732218955489065</v>
       </c>
       <c r="BD36" s="3">
         <v>4</v>
@@ -8508,22 +8432,22 @@
     <row r="37" ht="92" customHeight="1">
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>CCCCCC#Cc1cncc(N2CC3(CN(C(=O)c4cc(N)cc([N+](=O)[O-])c4)C3)C2)c1</t>
+          <t>C#CCCCC#Cc1cncc(N2CCC3(CN(Cc4cc(N)cc([N+](=O)[O-])c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(C(=O)c4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
+          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(Cc4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
         </is>
       </c>
       <c r="D37" s="3">
         <v>1</v>
       </c>
       <c r="E37" s="3">
-        <v>0.7272727272727273</v>
+        <v>0.6814159292035398</v>
       </c>
       <c r="F37" s="3">
-        <v>8.56</v>
+        <v>9.85</v>
       </c>
       <c r="G37" s="3">
         <v>5</v>
@@ -8543,46 +8467,46 @@
         <v>5.302380392493043</v>
       </c>
       <c r="L37" s="3">
-        <v>1.124907977073436</v>
+        <v>1.149298137908804</v>
       </c>
       <c r="M37" s="3">
-        <v>0.6624425040785792</v>
+        <v>0.7092630941813362</v>
       </c>
       <c r="N37" s="3">
-        <v>47.16277928658973</v>
+        <v>49.02987551844111</v>
       </c>
       <c r="O37" s="3">
-        <v>76.6162216468185</v>
+        <v>75.83765605699486</v>
       </c>
       <c r="P37" s="3">
-        <v>4.875092022926564</v>
+        <v>4.850701862091196</v>
       </c>
       <c r="Q37" s="3">
-        <v>0.6624425040785792</v>
+        <v>0.7092630941813362</v>
       </c>
       <c r="R37" s="3">
-        <v>0.6706882055465081</v>
+        <v>0.574304835986948</v>
       </c>
       <c r="S37" s="3">
-        <v>265.0301516483987</v>
+        <v>346.3010453375262</v>
       </c>
       <c r="T37" s="3">
-        <v>3.576704714932549</v>
+        <v>3.460546197495777</v>
       </c>
       <c r="U37" s="3">
-        <v>6.173479330920579</v>
+        <v>6.240857526686614</v>
       </c>
       <c r="V37" s="3">
-        <v>0.6624425040785792</v>
+        <v>0.7092630941813362</v>
       </c>
       <c r="W37" s="3">
-        <v>3.466200000000002</v>
+        <v>3.439300000000001</v>
       </c>
       <c r="X37" s="3">
-        <v>-5.315911886573709</v>
+        <v>-5.269584684777557</v>
       </c>
       <c r="Y37" s="3">
-        <v>4.831568191366663E-06</v>
+        <v>5.375456047847939E-06</v>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
@@ -8590,13 +8514,13 @@
         </is>
       </c>
       <c r="AA37" s="3">
-        <v>43.04407501220703</v>
+        <v>26.07542</v>
       </c>
       <c r="AB37" s="3">
-        <v>36.49444198608398</v>
+        <v>29.592224</v>
       </c>
       <c r="AC37" s="3">
-        <v>46.33618545532227</v>
+        <v>46.372997</v>
       </c>
       <c r="AD37" s="3">
         <v>0</v>
@@ -8608,73 +8532,73 @@
         <v>0</v>
       </c>
       <c r="AG37" s="3">
-        <v>0.3079252541065216</v>
+        <v>0.5606238</v>
       </c>
       <c r="AH37" s="3">
-        <v>0.1316820830106735</v>
+        <v>0.6120497</v>
       </c>
       <c r="AI37" s="3">
-        <v>0.9605914354324341</v>
+        <v>0.773284</v>
       </c>
       <c r="AJ37" s="3">
-        <v>0.1119943857192993</v>
+        <v>0.15395537</v>
       </c>
       <c r="AK37" s="3">
-        <v>0.7882549166679382</v>
+        <v>0.9692583</v>
       </c>
       <c r="AL37" s="3">
-        <v>0.1198652163147926</v>
+        <v>0.3575864</v>
       </c>
       <c r="AM37" s="3">
-        <v>0.7916267514228821</v>
+        <v>0.732784</v>
       </c>
       <c r="AN37" s="3">
-        <v>0.8817321062088013</v>
+        <v>0.7925714</v>
       </c>
       <c r="AO37" s="3">
-        <v>0.09936549514532089</v>
+        <v>0.6342771</v>
       </c>
       <c r="AP37" s="3">
-        <v>0.9247867465019226</v>
+        <v>0.9829602</v>
       </c>
       <c r="AQ37" s="3">
-        <v>0.9994671940803528</v>
+        <v>0.9997198</v>
       </c>
       <c r="AR37" s="3">
-        <v>0.767914354801178</v>
+        <v>0.64141804</v>
       </c>
       <c r="AS37" s="3">
-        <v>0.9317351579666138</v>
+        <v>0.89626026</v>
       </c>
       <c r="AT37" s="3">
-        <v>0.8923608064651489</v>
+        <v>0.9199284</v>
       </c>
       <c r="AU37" s="3">
-        <v>-4.842381477355957</v>
+        <v>-5.0240126</v>
       </c>
       <c r="AV37" s="3">
-        <v>99.70732879638672</v>
+        <v>96.75920000000001</v>
       </c>
       <c r="AW37" s="3">
-        <v>6.834559440612793</v>
+        <v>9.903665999999999</v>
       </c>
       <c r="AX37" s="3">
-        <v>433.5120000000002</v>
+        <v>429.5240000000002</v>
       </c>
       <c r="AY37" s="3">
-        <v>3.466200000000002</v>
+        <v>3.439300000000001</v>
       </c>
       <c r="AZ37" s="3">
-        <v>0.2458526377153969</v>
+        <v>0.2488090905746542</v>
       </c>
       <c r="BA37" s="3">
         <v>4</v>
       </c>
       <c r="BB37" s="3">
-        <v>3.423066196202072</v>
+        <v>3.703095075360942</v>
       </c>
       <c r="BC37" s="3">
-        <v>0.7307704226442142</v>
+        <v>0.6996561027376731</v>
       </c>
       <c r="BD37" s="3">
         <v>5</v>
@@ -8683,368 +8607,6 @@
         <v>0</v>
       </c>
       <c r="BF37" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" ht="92" customHeight="1">
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>CCCCCC#Cc1cncc(N2CC3(CN(Cc4cc(C(N)=O)cc([N+](=O)[O-])c4)C3)C2)c1</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(Cc4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
-        </is>
-      </c>
-      <c r="D38" s="3">
-        <v>1</v>
-      </c>
-      <c r="E38" s="3">
-        <v>0.7053571428571429</v>
-      </c>
-      <c r="F38" s="3">
-        <v>9.67</v>
-      </c>
-      <c r="G38" s="3">
-        <v>5</v>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>KNN | KNN | DT | LGBM | ET</t>
-        </is>
-      </c>
-      <c r="I38" s="3">
-        <v>0.6976196075069575</v>
-      </c>
-      <c r="J38" s="3">
-        <v>4.984477127902903</v>
-      </c>
-      <c r="K38" s="3">
-        <v>5.302380392493043</v>
-      </c>
-      <c r="L38" s="3">
-        <v>1.151794561238185</v>
-      </c>
-      <c r="M38" s="3">
-        <v>0.7005664127115778</v>
-      </c>
-      <c r="N38" s="3">
-        <v>48.98484068669714</v>
-      </c>
-      <c r="O38" s="3">
-        <v>75.88300062150282</v>
-      </c>
-      <c r="P38" s="3">
-        <v>4.848205438761815</v>
-      </c>
-      <c r="Q38" s="3">
-        <v>0.7005664127115778</v>
-      </c>
-      <c r="R38" s="3">
-        <v>0.6007370150989234</v>
-      </c>
-      <c r="S38" s="3">
-        <v>334.8919668768408</v>
-      </c>
-      <c r="T38" s="3">
-        <v>3.475095269847122</v>
-      </c>
-      <c r="U38" s="3">
-        <v>6.221315607676507</v>
-      </c>
-      <c r="V38" s="3">
-        <v>0.7005664127115778</v>
-      </c>
-      <c r="W38" s="3">
-        <v>3.342700000000002</v>
-      </c>
-      <c r="X38" s="3">
-        <v>-5.305341292182389</v>
-      </c>
-      <c r="Y38" s="3">
-        <v>4.950609920928786E-06</v>
-      </c>
-      <c r="Z38" s="2" t="inlineStr">
-        <is>
-          <t>Moderately Soluble</t>
-        </is>
-      </c>
-      <c r="AA38" s="3">
-        <v>42.29812622070312</v>
-      </c>
-      <c r="AB38" s="3">
-        <v>35.7274284362793</v>
-      </c>
-      <c r="AC38" s="3">
-        <v>44.06279754638672</v>
-      </c>
-      <c r="AD38" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE38" s="3">
-        <v>4</v>
-      </c>
-      <c r="AF38" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG38" s="3">
-        <v>0.3496591448783875</v>
-      </c>
-      <c r="AH38" s="3">
-        <v>0.4067471027374268</v>
-      </c>
-      <c r="AI38" s="3">
-        <v>0.850838840007782</v>
-      </c>
-      <c r="AJ38" s="3">
-        <v>0.2530973553657532</v>
-      </c>
-      <c r="AK38" s="3">
-        <v>0.8583583831787109</v>
-      </c>
-      <c r="AL38" s="3">
-        <v>0.08967733383178711</v>
-      </c>
-      <c r="AM38" s="3">
-        <v>0.5266183614730835</v>
-      </c>
-      <c r="AN38" s="3">
-        <v>0.5924957990646362</v>
-      </c>
-      <c r="AO38" s="3">
-        <v>0.3018611967563629</v>
-      </c>
-      <c r="AP38" s="3">
-        <v>0.7214671969413757</v>
-      </c>
-      <c r="AQ38" s="3">
-        <v>0.9958651661872864</v>
-      </c>
-      <c r="AR38" s="3">
-        <v>0.7781409025192261</v>
-      </c>
-      <c r="AS38" s="3">
-        <v>0.7356981039047241</v>
-      </c>
-      <c r="AT38" s="3">
-        <v>0.7920690774917603</v>
-      </c>
-      <c r="AU38" s="3">
-        <v>-5.056830406188965</v>
-      </c>
-      <c r="AV38" s="3">
-        <v>98.50418853759766</v>
-      </c>
-      <c r="AW38" s="3">
-        <v>7.267268180847168</v>
-      </c>
-      <c r="AX38" s="3">
-        <v>447.5390000000002</v>
-      </c>
-      <c r="AY38" s="3">
-        <v>3.342700000000002</v>
-      </c>
-      <c r="AZ38" s="3">
-        <v>0.2879435993170226</v>
-      </c>
-      <c r="BA38" s="3">
-        <v>4</v>
-      </c>
-      <c r="BB38" s="3">
-        <v>3.410029400598416</v>
-      </c>
-      <c r="BC38" s="3">
-        <v>0.732218955489065</v>
-      </c>
-      <c r="BD38" s="3">
-        <v>4</v>
-      </c>
-      <c r="BE38" s="3">
-        <v>0</v>
-      </c>
-      <c r="BF38" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" ht="92" customHeight="1">
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>C#CCCCC#Cc1cncc(N2CCC3(CN(Cc4cc(N)cc([N+](=O)[O-])c4)C3)C2)c1</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>CCCCCCC#Cc1cncc(N2CCC3(CN(Cc4cc([N+](=O)[O-])cc([N+](=O)[O-])c4)C3)C2)c1</t>
-        </is>
-      </c>
-      <c r="D39" s="3">
-        <v>1</v>
-      </c>
-      <c r="E39" s="3">
-        <v>0.6814159292035398</v>
-      </c>
-      <c r="F39" s="3">
-        <v>9.85</v>
-      </c>
-      <c r="G39" s="3">
-        <v>5</v>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>KNN | KNN | DT | LGBM | ET</t>
-        </is>
-      </c>
-      <c r="I39" s="3">
-        <v>0.6976196075069575</v>
-      </c>
-      <c r="J39" s="3">
-        <v>4.984477127902903</v>
-      </c>
-      <c r="K39" s="3">
-        <v>5.302380392493043</v>
-      </c>
-      <c r="L39" s="3">
-        <v>1.149298137908804</v>
-      </c>
-      <c r="M39" s="3">
-        <v>0.7092630941813362</v>
-      </c>
-      <c r="N39" s="3">
-        <v>49.02987551844111</v>
-      </c>
-      <c r="O39" s="3">
-        <v>75.83765605699486</v>
-      </c>
-      <c r="P39" s="3">
-        <v>4.850701862091196</v>
-      </c>
-      <c r="Q39" s="3">
-        <v>0.7092630941813362</v>
-      </c>
-      <c r="R39" s="3">
-        <v>0.574304835986948</v>
-      </c>
-      <c r="S39" s="3">
-        <v>346.3010453375262</v>
-      </c>
-      <c r="T39" s="3">
-        <v>3.460546197495777</v>
-      </c>
-      <c r="U39" s="3">
-        <v>6.240857526686614</v>
-      </c>
-      <c r="V39" s="3">
-        <v>0.7092630941813362</v>
-      </c>
-      <c r="W39" s="3">
-        <v>3.439300000000001</v>
-      </c>
-      <c r="X39" s="3">
-        <v>-5.269584684777557</v>
-      </c>
-      <c r="Y39" s="3">
-        <v>5.375456047847939E-06</v>
-      </c>
-      <c r="Z39" s="2" t="inlineStr">
-        <is>
-          <t>Moderately Soluble</t>
-        </is>
-      </c>
-      <c r="AA39" s="3">
-        <v>26.07542037963867</v>
-      </c>
-      <c r="AB39" s="3">
-        <v>29.59222412109375</v>
-      </c>
-      <c r="AC39" s="3">
-        <v>46.37299728393555</v>
-      </c>
-      <c r="AD39" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE39" s="3">
-        <v>5</v>
-      </c>
-      <c r="AF39" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG39" s="3">
-        <v>0.560623824596405</v>
-      </c>
-      <c r="AH39" s="3">
-        <v>0.6120496988296509</v>
-      </c>
-      <c r="AI39" s="3">
-        <v>0.7732840180397034</v>
-      </c>
-      <c r="AJ39" s="3">
-        <v>0.1539553701877594</v>
-      </c>
-      <c r="AK39" s="3">
-        <v>0.9692583084106445</v>
-      </c>
-      <c r="AL39" s="3">
-        <v>0.3575864136219025</v>
-      </c>
-      <c r="AM39" s="3">
-        <v>0.7327839732170105</v>
-      </c>
-      <c r="AN39" s="3">
-        <v>0.7925714254379272</v>
-      </c>
-      <c r="AO39" s="3">
-        <v>0.6342771053314209</v>
-      </c>
-      <c r="AP39" s="3">
-        <v>0.9829602241516113</v>
-      </c>
-      <c r="AQ39" s="3">
-        <v>0.9997197985649109</v>
-      </c>
-      <c r="AR39" s="3">
-        <v>0.6414180397987366</v>
-      </c>
-      <c r="AS39" s="3">
-        <v>0.8962602615356445</v>
-      </c>
-      <c r="AT39" s="3">
-        <v>0.9199283719062805</v>
-      </c>
-      <c r="AU39" s="3">
-        <v>-5.024012565612793</v>
-      </c>
-      <c r="AV39" s="3">
-        <v>96.75920104980469</v>
-      </c>
-      <c r="AW39" s="3">
-        <v>9.903665542602539</v>
-      </c>
-      <c r="AX39" s="3">
-        <v>429.5240000000002</v>
-      </c>
-      <c r="AY39" s="3">
-        <v>3.439300000000001</v>
-      </c>
-      <c r="AZ39" s="3">
-        <v>0.2488090905746543</v>
-      </c>
-      <c r="BA39" s="3">
-        <v>4</v>
-      </c>
-      <c r="BB39" s="3">
-        <v>3.703095075360942</v>
-      </c>
-      <c r="BC39" s="3">
-        <v>0.6996561027376731</v>
-      </c>
-      <c r="BD39" s="3">
-        <v>5</v>
-      </c>
-      <c r="BE39" s="3">
-        <v>0</v>
-      </c>
-      <c r="BF39" s="3">
         <v>1</v>
       </c>
     </row>
